--- a/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
+++ b/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BC42846-D27B-41F9-ACD4-4D98C37AAD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1950E20-AFC9-41B5-AC47-392C4C797030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report register" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="165">
-  <si>
-    <t>VLSFO CONSUMPTION IN MT</t>
-  </si>
-  <si>
-    <t>MGO CONSUMPTION IN MT</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="165">
   <si>
     <t>voyageId</t>
   </si>
@@ -89,16 +83,7 @@
     <t>otherIfo</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>DAILY COSUMTION</t>
-  </si>
-  <si>
     <t>bunkeringIfo</t>
-  </si>
-  <si>
-    <t>ROB</t>
   </si>
   <si>
     <t>mplaMgo</t>
@@ -511,26 +496,35 @@
     <t>nextActivityPerformed</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>TOTAL_IFO</t>
+  </si>
+  <si>
+    <t>DAILY_COSUMTION_IFO</t>
+  </si>
+  <si>
+    <t>ROB_IFO</t>
+  </si>
+  <si>
+    <t>TOTAL_MGO</t>
+  </si>
+  <si>
+    <t>DAILY_COSUMTION_MGO</t>
+  </si>
+  <si>
+    <t>ROB_MGO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFFCD06"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -547,17 +541,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF001556"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -572,12 +561,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,42 +595,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FFF3F3F3"/>
-      </left>
-      <right style="double">
-        <color rgb="FFF3F3F3"/>
-      </right>
-      <top style="double">
-        <color rgb="FFF3F3F3"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FFF3F3F3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF3F3F3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF3F3F3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF3F3F3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF3F3F3"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -699,38 +652,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:CM56"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="4" customWidth="1"/>
@@ -1085,222 +1031,563 @@
     <col min="13" max="13" width="22.109375" customWidth="1"/>
     <col min="14" max="14" width="24.21875" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="38" width="13.21875" customWidth="1"/>
-    <col min="39" max="62" width="8" customWidth="1"/>
-    <col min="63" max="93" width="4" customWidth="1"/>
+    <col min="16" max="34" width="13.21875" customWidth="1"/>
+    <col min="35" max="35" width="25.109375" customWidth="1"/>
+    <col min="36" max="38" width="13.21875" customWidth="1"/>
+    <col min="39" max="47" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:91" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="T3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="16" t="s">
+    <row r="1" spans="1:47" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AC3" s="16"/>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="16"/>
-      <c r="AF3" s="16"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="16"/>
-      <c r="AI3" s="16"/>
-      <c r="AJ3" s="16"/>
-      <c r="AK3" s="16"/>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" spans="1:91" ht="21.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>2025</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2">
+        <v>0.9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2">
+        <v>6</v>
+      </c>
+      <c r="Q2">
+        <f>IFERROR((I2 -#REF!)*24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f t="shared" ref="R2:R49" si="0">IF(ISERROR(P2/Q2),0,P2/Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:X49" si="1">SUM(T2:W2)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" ref="Y2:Y49" si="2">IF(ISERROR(X2*24/Q2),0,X2*24/Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>2143.33</v>
+      </c>
+      <c r="AA2">
+        <v>2143.33</v>
+      </c>
+      <c r="AB2">
+        <v>0.45</v>
+      </c>
+      <c r="AC2">
+        <v>0.2</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AH49" si="3">SUM(AB2:AG2)</f>
+        <v>0.65</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:AI49" si="4">IF(ISERROR(AH2*24/Q2),0,AH2*24/Q2)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f>331.95+AH2</f>
+        <v>332.59999999999997</v>
+      </c>
+      <c r="AK2">
+        <v>331.95</v>
+      </c>
+      <c r="AL2" s="12">
+        <v>8</v>
+      </c>
+      <c r="AM2" s="12">
+        <v>20.7</v>
+      </c>
+      <c r="AN2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO2" s="12">
+        <v>79</v>
+      </c>
+      <c r="AP2" s="12">
+        <v>27.1</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>2025</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>1.3</v>
+      </c>
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q49" si="5">IFERROR((I3 - I2)*24,0)</f>
+        <v>1.3000000000465661</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>1.6923076922470739</v>
+      </c>
+      <c r="S3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3">
+        <v>1.75</v>
+      </c>
+      <c r="U3">
+        <v>0.35</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="1"/>
+        <v>2.1</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="2"/>
+        <v>38.769230767842053</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA49" si="6">AA2-X3+Z3</f>
+        <v>2141.23</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" ref="AK3:AK49" si="7">AK2-AH3+AJ3</f>
+        <v>331.95</v>
+      </c>
+      <c r="AL3" s="12">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="X4" s="7" t="s">
+      <c r="AM3" s="12">
+        <v>20.7</v>
+      </c>
+      <c r="AN3" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO3" s="12">
+        <v>79</v>
+      </c>
+      <c r="AP3" s="12">
+        <v>27.1</v>
+      </c>
+      <c r="AQ3" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>2025</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
         <v>24</v>
       </c>
-      <c r="Y4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE4" s="3" t="s">
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4">
+        <v>313</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="0"/>
+        <v>13.041666666666666</v>
+      </c>
+      <c r="S4" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4">
+        <v>35.5</v>
+      </c>
+      <c r="U4">
+        <v>7.2</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="1"/>
+        <v>42.7</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="2"/>
+        <v>42.70000000000001</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="6"/>
+        <v>2098.5300000000002</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="7"/>
+        <v>331.95</v>
+      </c>
+      <c r="AL4">
+        <v>8</v>
+      </c>
+      <c r="AM4">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO4">
+        <v>84</v>
+      </c>
+      <c r="AP4">
+        <v>11.4</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS4">
         <v>31</v>
       </c>
-      <c r="AF4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AO4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AP4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AR4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AU4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AW4" s="9"/>
-      <c r="AX4" s="10"/>
-      <c r="AY4" s="9"/>
-      <c r="AZ4" s="10"/>
-      <c r="BA4" s="9"/>
-      <c r="BB4" s="10"/>
-      <c r="BC4" s="9"/>
-      <c r="BD4" s="10"/>
-      <c r="BE4" s="9"/>
-      <c r="BF4" s="10"/>
-      <c r="BG4" s="9"/>
-      <c r="BH4" s="10"/>
-      <c r="BI4" s="9"/>
-      <c r="BJ4" s="10"/>
-      <c r="BK4" s="9"/>
-      <c r="BL4" s="10"/>
-      <c r="BM4" s="9"/>
-      <c r="BN4" s="10"/>
-      <c r="BO4" s="9"/>
-      <c r="BP4" s="10"/>
-      <c r="BQ4" s="9"/>
-      <c r="BR4" s="10"/>
-      <c r="BS4" s="9"/>
-      <c r="BT4" s="10"/>
-      <c r="BU4" s="9"/>
-      <c r="BV4" s="10"/>
-      <c r="BW4" s="9"/>
-      <c r="BX4" s="10"/>
-      <c r="BY4" s="9"/>
-      <c r="BZ4" s="10"/>
-      <c r="CA4" s="9"/>
-      <c r="CB4" s="10"/>
-      <c r="CC4" s="9"/>
-      <c r="CD4" s="9"/>
-      <c r="CE4" s="9"/>
-      <c r="CF4" s="9"/>
-      <c r="CG4" s="9"/>
-      <c r="CH4" s="9"/>
-      <c r="CI4" s="9"/>
-      <c r="CJ4" s="9"/>
-      <c r="CK4" s="9"/>
-      <c r="CL4" s="9"/>
-      <c r="CM4" s="9"/>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D5">
         <v>2025</v>
       </c>
@@ -1311,51 +1598,51 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="K5">
-        <v>0.9</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P5">
-        <v>6</v>
+        <v>366</v>
       </c>
       <c r="Q5">
-        <f>IFERROR((I5 -#REF!)*24,0)</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>24</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R52" si="0">IF(ISERROR(P5/Q5),0,P5/Q5)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>15.25</v>
       </c>
       <c r="S5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>38.75</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1364,24 +1651,25 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <f t="shared" ref="X5:X52" si="1">SUM(T5:W5)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>46.230000000000004</v>
       </c>
       <c r="Y5">
-        <f t="shared" ref="Y5:Y52" si="2">IF(ISERROR(X5*24/Q5),0,X5*24/Q5)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>46.23</v>
       </c>
       <c r="Z5">
-        <v>2143.33</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>2143.33</v>
+        <f t="shared" si="6"/>
+        <v>2052.3000000000002</v>
       </c>
       <c r="AB5">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1396,46 +1684,46 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <f t="shared" ref="AH5:AH52" si="3">SUM(AB5:AG5)</f>
-        <v>0.65</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" ref="AI5:AI52" si="4">IF(ISERROR(AH5*24/Q5),0,AH5*24/Q5)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f>331.95+AH5</f>
-        <v>332.59999999999997</v>
+        <v>0</v>
       </c>
       <c r="AK5">
+        <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL5" s="14">
-        <v>8</v>
-      </c>
-      <c r="AM5" s="14">
-        <v>20.7</v>
-      </c>
-      <c r="AN5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO5" s="14">
-        <v>79</v>
-      </c>
-      <c r="AP5" s="14">
-        <v>27.1</v>
-      </c>
-      <c r="AQ5" s="14" t="s">
-        <v>50</v>
+      <c r="AL5">
+        <v>10</v>
+      </c>
+      <c r="AM5">
+        <v>58.9</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO5">
+        <v>89</v>
+      </c>
+      <c r="AP5">
+        <v>24</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>45</v>
       </c>
       <c r="AR5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AS5">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D6">
         <v>2025</v>
       </c>
@@ -1446,51 +1734,51 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
         <v>89</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>1.3</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>2.2000000000000002</v>
+        <v>386</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q52" si="5">IFERROR((I6 - I5)*24,0)</f>
-        <v>1.3000000000465661</v>
+        <f t="shared" si="5"/>
+        <v>24</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>1.6923076922470739</v>
+        <v>16.083333333333332</v>
       </c>
       <c r="S6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>41.85</v>
       </c>
       <c r="U6">
-        <v>0.35</v>
+        <v>5.15</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1500,18 +1788,18 @@
       </c>
       <c r="X6">
         <f t="shared" si="1"/>
-        <v>2.1</v>
+        <v>47</v>
       </c>
       <c r="Y6">
         <f t="shared" si="2"/>
-        <v>38.769230767842053</v>
+        <v>47</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" ref="AA6:AA52" si="6">AA5-X6+Z6</f>
-        <v>2141.23</v>
+        <f t="shared" si="6"/>
+        <v>2005.3000000000002</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -1543,35 +1831,35 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" ref="AK6:AK52" si="7">AK5-AH6+AJ6</f>
+        <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL6" s="14">
-        <v>8</v>
-      </c>
-      <c r="AM6" s="14">
-        <v>20.7</v>
-      </c>
-      <c r="AN6" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO6" s="14">
-        <v>79</v>
-      </c>
-      <c r="AP6" s="14">
-        <v>27.1</v>
-      </c>
-      <c r="AQ6" s="14" t="s">
-        <v>50</v>
+      <c r="AL6">
+        <v>13</v>
+      </c>
+      <c r="AM6">
+        <v>39.1</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO6">
+        <v>95</v>
+      </c>
+      <c r="AP6">
+        <v>19.7</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>45</v>
       </c>
       <c r="AR6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS6">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D7">
         <v>2025</v>
       </c>
@@ -1582,34 +1870,34 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K7">
         <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P7">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="Q7">
         <f t="shared" si="5"/>
@@ -1617,16 +1905,16 @@
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>13.041666666666666</v>
+        <v>15.333333333333334</v>
       </c>
       <c r="S7" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="T7">
-        <v>35.5</v>
+        <v>42.75</v>
       </c>
       <c r="U7">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1636,18 +1924,18 @@
       </c>
       <c r="X7">
         <f t="shared" si="1"/>
-        <v>42.7</v>
+        <v>46.65</v>
       </c>
       <c r="Y7">
         <f t="shared" si="2"/>
-        <v>42.70000000000001</v>
+        <v>46.65</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7">
         <f t="shared" si="6"/>
-        <v>2098.5300000000002</v>
+        <v>1958.65</v>
       </c>
       <c r="AB7">
         <v>0</v>
@@ -1683,31 +1971,31 @@
         <v>331.95</v>
       </c>
       <c r="AL7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AM7">
-        <v>9.3000000000000007</v>
+        <v>11.9</v>
       </c>
       <c r="AN7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO7">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="AP7">
-        <v>11.4</v>
+        <v>3.4</v>
       </c>
       <c r="AQ7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS7">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D8">
         <v>2025</v>
       </c>
@@ -1718,34 +2006,34 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K8">
         <v>24</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P8">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="Q8">
         <f t="shared" si="5"/>
@@ -1753,16 +2041,16 @@
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>15.25</v>
+        <v>15.625</v>
       </c>
       <c r="S8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="T8">
-        <v>38.75</v>
+        <v>42.75</v>
       </c>
       <c r="U8">
-        <v>7.48</v>
+        <v>4</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -1772,18 +2060,18 @@
       </c>
       <c r="X8">
         <f t="shared" si="1"/>
-        <v>46.230000000000004</v>
+        <v>46.75</v>
       </c>
       <c r="Y8">
         <f t="shared" si="2"/>
-        <v>46.23</v>
+        <v>46.75</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AA8">
         <f t="shared" si="6"/>
-        <v>2052.3000000000002</v>
+        <v>1911.9</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -1819,31 +2107,31 @@
         <v>331.95</v>
       </c>
       <c r="AL8">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AM8">
-        <v>58.9</v>
+        <v>4.3</v>
       </c>
       <c r="AN8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="AP8">
-        <v>24</v>
+        <v>48.4</v>
       </c>
       <c r="AQ8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS8">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D9">
         <v>2025</v>
       </c>
@@ -1854,34 +2142,34 @@
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P9">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="Q9">
         <f t="shared" si="5"/>
@@ -1889,16 +2177,16 @@
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>16.083333333333332</v>
+        <v>15.375</v>
       </c>
       <c r="S9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="T9">
-        <v>41.85</v>
+        <v>43.35</v>
       </c>
       <c r="U9">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -1908,18 +2196,18 @@
       </c>
       <c r="X9">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>47.15</v>
       </c>
       <c r="Y9">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>47.15</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
       <c r="AA9">
         <f t="shared" si="6"/>
-        <v>2005.3000000000002</v>
+        <v>1864.75</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -1955,31 +2243,31 @@
         <v>331.95</v>
       </c>
       <c r="AL9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AM9">
-        <v>39.1</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO9">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="AP9">
-        <v>19.7</v>
+        <v>29.8</v>
       </c>
       <c r="AQ9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS9">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D10">
         <v>2025</v>
       </c>
@@ -1990,34 +2278,34 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="Q10">
         <f t="shared" si="5"/>
@@ -2025,13 +2313,13 @@
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
-        <v>15.333333333333334</v>
+        <v>14.875</v>
       </c>
       <c r="S10" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="T10">
-        <v>42.75</v>
+        <v>45.85</v>
       </c>
       <c r="U10">
         <v>3.9</v>
@@ -2044,18 +2332,18 @@
       </c>
       <c r="X10">
         <f t="shared" si="1"/>
-        <v>46.65</v>
+        <v>49.75</v>
       </c>
       <c r="Y10">
         <f t="shared" si="2"/>
-        <v>46.65</v>
+        <v>49.75</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
         <f t="shared" si="6"/>
-        <v>1958.65</v>
+        <v>1815</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -2091,31 +2379,31 @@
         <v>331.95</v>
       </c>
       <c r="AL10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AM10">
-        <v>11.9</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO10">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AP10">
-        <v>3.4</v>
+        <v>40</v>
       </c>
       <c r="AQ10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS10">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D11">
         <v>2025</v>
       </c>
@@ -2126,31 +2414,31 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K11">
         <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P11">
         <v>375</v>
@@ -2164,13 +2452,13 @@
         <v>15.625</v>
       </c>
       <c r="S11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="T11">
-        <v>42.75</v>
+        <v>43.25</v>
       </c>
       <c r="U11">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2180,18 +2468,18 @@
       </c>
       <c r="X11">
         <f t="shared" si="1"/>
-        <v>46.75</v>
+        <v>46.6</v>
       </c>
       <c r="Y11">
         <f t="shared" si="2"/>
-        <v>46.75</v>
+        <v>46.6</v>
       </c>
       <c r="Z11">
         <v>0</v>
       </c>
       <c r="AA11">
         <f t="shared" si="6"/>
-        <v>1911.9</v>
+        <v>1768.4</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -2227,31 +2515,31 @@
         <v>331.95</v>
       </c>
       <c r="AL11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AM11">
-        <v>4.3</v>
+        <v>36.4</v>
       </c>
       <c r="AN11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO11">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AP11">
-        <v>48.4</v>
+        <v>56.6</v>
       </c>
       <c r="AQ11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS11">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D12">
         <v>2025</v>
       </c>
@@ -2262,34 +2550,34 @@
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K12">
         <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P12">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q12">
         <f t="shared" si="5"/>
@@ -2297,16 +2585,16 @@
       </c>
       <c r="R12">
         <f t="shared" si="0"/>
-        <v>15.375</v>
+        <v>15.708333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="T12">
-        <v>43.35</v>
+        <v>45.4</v>
       </c>
       <c r="U12">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2316,18 +2604,18 @@
       </c>
       <c r="X12">
         <f t="shared" si="1"/>
-        <v>47.15</v>
+        <v>48.949999999999996</v>
       </c>
       <c r="Y12">
         <f t="shared" si="2"/>
-        <v>47.15</v>
+        <v>48.949999999999996</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
       <c r="AA12">
         <f t="shared" si="6"/>
-        <v>1864.75</v>
+        <v>1719.45</v>
       </c>
       <c r="AB12">
         <v>0</v>
@@ -2363,31 +2651,31 @@
         <v>331.95</v>
       </c>
       <c r="AL12">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AM12">
-        <v>5</v>
+        <v>56.4</v>
       </c>
       <c r="AN12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO12">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="AP12">
-        <v>29.8</v>
+        <v>38</v>
       </c>
       <c r="AQ12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS12">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D13">
         <v>2025</v>
       </c>
@@ -2398,34 +2686,34 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P13">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="Q13">
         <f t="shared" si="5"/>
@@ -2433,16 +2721,16 @@
       </c>
       <c r="R13">
         <f t="shared" si="0"/>
-        <v>14.875</v>
+        <v>15.125</v>
       </c>
       <c r="S13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T13">
-        <v>45.85</v>
+        <v>43.65</v>
       </c>
       <c r="U13">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -2452,18 +2740,18 @@
       </c>
       <c r="X13">
         <f t="shared" si="1"/>
-        <v>49.75</v>
+        <v>47.199999999999996</v>
       </c>
       <c r="Y13">
         <f t="shared" si="2"/>
-        <v>49.75</v>
+        <v>47.199999999999996</v>
       </c>
       <c r="Z13">
         <v>0</v>
       </c>
       <c r="AA13">
         <f t="shared" si="6"/>
-        <v>1815</v>
+        <v>1672.25</v>
       </c>
       <c r="AB13">
         <v>0</v>
@@ -2499,31 +2787,31 @@
         <v>331.95</v>
       </c>
       <c r="AL13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AM13">
-        <v>0.2</v>
+        <v>13</v>
       </c>
       <c r="AN13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO13">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="AP13">
-        <v>40</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="AQ13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS13">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D14">
         <v>2025</v>
       </c>
@@ -2534,34 +2822,34 @@
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O14" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P14">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="Q14">
         <f t="shared" si="5"/>
@@ -2569,16 +2857,16 @@
       </c>
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>15.625</v>
+        <v>16.208333333333332</v>
       </c>
       <c r="S14" t="s">
         <v>59</v>
       </c>
       <c r="T14">
-        <v>43.25</v>
+        <v>43.55</v>
       </c>
       <c r="U14">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2588,18 +2876,18 @@
       </c>
       <c r="X14">
         <f t="shared" si="1"/>
-        <v>46.6</v>
+        <v>47.25</v>
       </c>
       <c r="Y14">
         <f t="shared" si="2"/>
-        <v>46.6</v>
+        <v>47.25</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
       <c r="AA14">
         <f t="shared" si="6"/>
-        <v>1768.4</v>
+        <v>1625</v>
       </c>
       <c r="AB14">
         <v>0</v>
@@ -2635,31 +2923,31 @@
         <v>331.95</v>
       </c>
       <c r="AL14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM14">
-        <v>36.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AN14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO14">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="AP14">
-        <v>56.6</v>
+        <v>34.9</v>
       </c>
       <c r="AQ14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS14">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D15">
         <v>2025</v>
       </c>
@@ -2670,34 +2958,34 @@
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O15" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="P15">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="Q15">
         <f t="shared" si="5"/>
@@ -2705,16 +2993,16 @@
       </c>
       <c r="R15">
         <f t="shared" si="0"/>
-        <v>15.708333333333334</v>
+        <v>13.541666666666666</v>
       </c>
       <c r="S15" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="T15">
-        <v>45.4</v>
+        <v>42.3</v>
       </c>
       <c r="U15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2724,18 +3012,18 @@
       </c>
       <c r="X15">
         <f t="shared" si="1"/>
-        <v>48.949999999999996</v>
+        <v>45.9</v>
       </c>
       <c r="Y15">
         <f t="shared" si="2"/>
-        <v>48.949999999999996</v>
+        <v>45.9</v>
       </c>
       <c r="Z15">
         <v>0</v>
       </c>
       <c r="AA15">
         <f t="shared" si="6"/>
-        <v>1719.45</v>
+        <v>1579.1</v>
       </c>
       <c r="AB15">
         <v>0</v>
@@ -2771,31 +3059,31 @@
         <v>331.95</v>
       </c>
       <c r="AL15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM15">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="AN15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO15">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AP15">
-        <v>38</v>
+        <v>55.4</v>
       </c>
       <c r="AQ15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS15">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:91" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
       <c r="D16">
         <v>2025</v>
       </c>
@@ -2806,34 +3094,34 @@
         <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s">
         <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O16" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="P16">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="Q16">
         <f t="shared" si="5"/>
@@ -2841,16 +3129,16 @@
       </c>
       <c r="R16">
         <f t="shared" si="0"/>
-        <v>15.125</v>
+        <v>13.708333333333334</v>
       </c>
       <c r="S16" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T16">
-        <v>43.65</v>
+        <v>45.35</v>
       </c>
       <c r="U16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2860,18 +3148,18 @@
       </c>
       <c r="X16">
         <f t="shared" si="1"/>
-        <v>47.199999999999996</v>
+        <v>48.95</v>
       </c>
       <c r="Y16">
         <f t="shared" si="2"/>
-        <v>47.199999999999996</v>
+        <v>48.95000000000001</v>
       </c>
       <c r="Z16">
         <v>0</v>
       </c>
       <c r="AA16">
         <f t="shared" si="6"/>
-        <v>1672.25</v>
+        <v>1530.1499999999999</v>
       </c>
       <c r="AB16">
         <v>0</v>
@@ -2907,25 +3195,25 @@
         <v>331.95</v>
       </c>
       <c r="AL16">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AM16">
-        <v>13</v>
+        <v>59.7</v>
       </c>
       <c r="AN16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO16">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="AP16">
-        <v>18.399999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="AQ16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR16" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS16">
         <v>31</v>
@@ -2942,34 +3230,34 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P17">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="Q17">
         <f t="shared" si="5"/>
@@ -2977,16 +3265,16 @@
       </c>
       <c r="R17">
         <f t="shared" si="0"/>
-        <v>16.208333333333332</v>
+        <v>12.75</v>
       </c>
       <c r="S17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="T17">
-        <v>43.55</v>
+        <v>43.7</v>
       </c>
       <c r="U17">
-        <v>3.7</v>
+        <v>7.45</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -2996,18 +3284,18 @@
       </c>
       <c r="X17">
         <f t="shared" si="1"/>
-        <v>47.25</v>
+        <v>51.150000000000006</v>
       </c>
       <c r="Y17">
         <f t="shared" si="2"/>
-        <v>47.25</v>
+        <v>51.150000000000006</v>
       </c>
       <c r="Z17">
         <v>0</v>
       </c>
       <c r="AA17">
         <f t="shared" si="6"/>
-        <v>1625</v>
+        <v>1478.9999999999998</v>
       </c>
       <c r="AB17">
         <v>0</v>
@@ -3043,25 +3331,25 @@
         <v>331.95</v>
       </c>
       <c r="AL17">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="AM17">
-        <v>8.6999999999999993</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AN17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO17">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="AP17">
-        <v>34.9</v>
+        <v>8.5</v>
       </c>
       <c r="AQ17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS17">
         <v>31</v>
@@ -3078,34 +3366,34 @@
         <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K18">
         <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P18">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="Q18">
         <f t="shared" si="5"/>
@@ -3113,16 +3401,16 @@
       </c>
       <c r="R18">
         <f t="shared" si="0"/>
-        <v>13.541666666666666</v>
+        <v>12.958333333333334</v>
       </c>
       <c r="S18" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="T18">
-        <v>42.3</v>
+        <v>44.6</v>
       </c>
       <c r="U18">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -3132,18 +3420,18 @@
       </c>
       <c r="X18">
         <f t="shared" si="1"/>
-        <v>45.9</v>
+        <v>52.5</v>
       </c>
       <c r="Y18">
         <f t="shared" si="2"/>
-        <v>45.9</v>
+        <v>52.5</v>
       </c>
       <c r="Z18">
         <v>0</v>
       </c>
       <c r="AA18">
         <f t="shared" si="6"/>
-        <v>1579.1</v>
+        <v>1426.4999999999998</v>
       </c>
       <c r="AB18">
         <v>0</v>
@@ -3179,25 +3467,25 @@
         <v>331.95</v>
       </c>
       <c r="AL18">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM18">
-        <v>56.6</v>
+        <v>42.4</v>
       </c>
       <c r="AN18" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO18">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="AP18">
-        <v>55.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="AQ18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR18" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS18">
         <v>31</v>
@@ -3214,34 +3502,34 @@
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s">
         <v>106</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P19">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="Q19">
         <f t="shared" si="5"/>
@@ -3249,16 +3537,16 @@
       </c>
       <c r="R19">
         <f t="shared" si="0"/>
-        <v>13.708333333333334</v>
+        <v>11.791666666666666</v>
       </c>
       <c r="S19" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="T19">
-        <v>45.35</v>
+        <v>41.8</v>
       </c>
       <c r="U19">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -3268,18 +3556,18 @@
       </c>
       <c r="X19">
         <f t="shared" si="1"/>
-        <v>48.95</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="Y19">
         <f t="shared" si="2"/>
-        <v>48.95000000000001</v>
+        <v>49.599999999999994</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19">
         <f t="shared" si="6"/>
-        <v>1530.1499999999999</v>
+        <v>1376.8999999999999</v>
       </c>
       <c r="AB19">
         <v>0</v>
@@ -3315,25 +3603,25 @@
         <v>331.95</v>
       </c>
       <c r="AL19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AM19">
-        <v>59.7</v>
+        <v>31.8</v>
       </c>
       <c r="AN19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO19">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="AP19">
-        <v>23.6</v>
+        <v>10.4</v>
       </c>
       <c r="AQ19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS19">
         <v>31</v>
@@ -3350,34 +3638,34 @@
         <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K20">
         <v>24</v>
       </c>
       <c r="L20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N20" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O20" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="P20">
-        <v>306</v>
+        <v>354</v>
       </c>
       <c r="Q20">
         <f t="shared" si="5"/>
@@ -3385,16 +3673,16 @@
       </c>
       <c r="R20">
         <f t="shared" si="0"/>
-        <v>12.75</v>
+        <v>14.75</v>
       </c>
       <c r="S20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T20">
-        <v>43.7</v>
+        <v>42.4</v>
       </c>
       <c r="U20">
-        <v>7.45</v>
+        <v>4.75</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3404,18 +3692,18 @@
       </c>
       <c r="X20">
         <f t="shared" si="1"/>
-        <v>51.150000000000006</v>
+        <v>47.15</v>
       </c>
       <c r="Y20">
         <f t="shared" si="2"/>
-        <v>51.150000000000006</v>
+        <v>47.15</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
       <c r="AA20">
         <f t="shared" si="6"/>
-        <v>1478.9999999999998</v>
+        <v>1329.7499999999998</v>
       </c>
       <c r="AB20">
         <v>0</v>
@@ -3451,25 +3739,25 @@
         <v>331.95</v>
       </c>
       <c r="AL20">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AM20">
-        <v>36.799999999999997</v>
+        <v>11.2</v>
       </c>
       <c r="AN20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO20">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="AP20">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AR20" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS20">
         <v>31</v>
@@ -3486,34 +3774,34 @@
         <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K21">
         <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O21" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P21">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="Q21">
         <f t="shared" si="5"/>
@@ -3521,16 +3809,16 @@
       </c>
       <c r="R21">
         <f t="shared" si="0"/>
-        <v>12.958333333333334</v>
+        <v>15.333333333333334</v>
       </c>
       <c r="S21" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="T21">
         <v>44.6</v>
       </c>
       <c r="U21">
-        <v>7.9</v>
+        <v>3.45</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3540,18 +3828,18 @@
       </c>
       <c r="X21">
         <f t="shared" si="1"/>
-        <v>52.5</v>
+        <v>48.050000000000004</v>
       </c>
       <c r="Y21">
         <f t="shared" si="2"/>
-        <v>52.5</v>
+        <v>48.050000000000004</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
       <c r="AA21">
         <f t="shared" si="6"/>
-        <v>1426.4999999999998</v>
+        <v>1281.6999999999998</v>
       </c>
       <c r="AB21">
         <v>0</v>
@@ -3587,25 +3875,25 @@
         <v>331.95</v>
       </c>
       <c r="AL21">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AM21">
-        <v>42.4</v>
+        <v>16.5</v>
       </c>
       <c r="AN21" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO21">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AP21">
-        <v>17.399999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="AQ21" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AR21" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS21">
         <v>31</v>
@@ -3622,34 +3910,34 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K22">
         <v>24</v>
       </c>
       <c r="L22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N22" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O22" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P22">
-        <v>283</v>
+        <v>364</v>
       </c>
       <c r="Q22">
         <f t="shared" si="5"/>
@@ -3657,16 +3945,16 @@
       </c>
       <c r="R22">
         <f t="shared" si="0"/>
-        <v>11.791666666666666</v>
+        <v>15.166666666666666</v>
       </c>
       <c r="S22" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="T22">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="U22">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3676,18 +3964,18 @@
       </c>
       <c r="X22">
         <f t="shared" si="1"/>
-        <v>49.599999999999994</v>
+        <v>44.699999999999996</v>
       </c>
       <c r="Y22">
         <f t="shared" si="2"/>
-        <v>49.599999999999994</v>
+        <v>44.699999999999996</v>
       </c>
       <c r="Z22">
         <v>0</v>
       </c>
       <c r="AA22">
         <f t="shared" si="6"/>
-        <v>1376.8999999999999</v>
+        <v>1236.9999999999998</v>
       </c>
       <c r="AB22">
         <v>0</v>
@@ -3723,25 +4011,25 @@
         <v>331.95</v>
       </c>
       <c r="AL22">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AM22">
-        <v>31.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AN22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO22">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AP22">
-        <v>10.4</v>
+        <v>52.5</v>
       </c>
       <c r="AQ22" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AR22" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS22">
         <v>31</v>
@@ -3758,51 +4046,51 @@
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J23" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K23">
         <v>24</v>
       </c>
       <c r="L23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N23" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P23">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="Q23">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="R23">
         <f t="shared" si="0"/>
-        <v>14.75</v>
+        <v>8</v>
       </c>
       <c r="S23" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="T23">
-        <v>42.4</v>
+        <v>44.4</v>
       </c>
       <c r="U23">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3812,18 +4100,18 @@
       </c>
       <c r="X23">
         <f t="shared" si="1"/>
-        <v>47.15</v>
+        <v>47.6</v>
       </c>
       <c r="Y23">
         <f t="shared" si="2"/>
-        <v>47.15</v>
+        <v>23.8</v>
       </c>
       <c r="Z23">
         <v>0</v>
       </c>
       <c r="AA23">
         <f t="shared" si="6"/>
-        <v>1329.7499999999998</v>
+        <v>1189.3999999999999</v>
       </c>
       <c r="AB23">
         <v>0</v>
@@ -3859,25 +4147,25 @@
         <v>331.95</v>
       </c>
       <c r="AL23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM23">
-        <v>11.2</v>
+        <v>46.4</v>
       </c>
       <c r="AN23" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO23">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="AP23">
-        <v>13.5</v>
+        <v>50.9</v>
       </c>
       <c r="AQ23" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AR23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS23">
         <v>31</v>
@@ -3894,34 +4182,34 @@
         <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" t="s">
+        <v>48</v>
+      </c>
+      <c r="O24" t="s">
         <v>113</v>
       </c>
-      <c r="J24" t="s">
-        <v>45</v>
-      </c>
-      <c r="K24">
-        <v>25</v>
-      </c>
-      <c r="L24" t="s">
-        <v>60</v>
-      </c>
-      <c r="M24" t="s">
-        <v>60</v>
-      </c>
-      <c r="N24" t="s">
-        <v>53</v>
-      </c>
-      <c r="O24" t="s">
-        <v>110</v>
-      </c>
       <c r="P24">
-        <v>368</v>
+        <v>311</v>
       </c>
       <c r="Q24">
         <f t="shared" si="5"/>
@@ -3929,16 +4217,16 @@
       </c>
       <c r="R24">
         <f t="shared" si="0"/>
-        <v>15.333333333333334</v>
+        <v>12.958333333333334</v>
       </c>
       <c r="S24" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="T24">
-        <v>44.6</v>
+        <v>42.05</v>
       </c>
       <c r="U24">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -3948,18 +4236,18 @@
       </c>
       <c r="X24">
         <f t="shared" si="1"/>
-        <v>48.050000000000004</v>
+        <v>45.3</v>
       </c>
       <c r="Y24">
         <f t="shared" si="2"/>
-        <v>48.050000000000004</v>
+        <v>45.29999999999999</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AA24">
         <f t="shared" si="6"/>
-        <v>1281.6999999999998</v>
+        <v>1144.0999999999999</v>
       </c>
       <c r="AB24">
         <v>0</v>
@@ -3995,25 +4283,25 @@
         <v>331.95</v>
       </c>
       <c r="AL24">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM24">
-        <v>16.5</v>
+        <v>9.1</v>
       </c>
       <c r="AN24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO24">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="AP24">
-        <v>11.6</v>
+        <v>13.9</v>
       </c>
       <c r="AQ24" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR24" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS24">
         <v>31</v>
@@ -4030,34 +4318,34 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s">
         <v>114</v>
       </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O25" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P25">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="Q25">
         <f t="shared" si="5"/>
@@ -4065,16 +4353,16 @@
       </c>
       <c r="R25">
         <f t="shared" si="0"/>
-        <v>15.166666666666666</v>
+        <v>16.083333333333332</v>
       </c>
       <c r="S25" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="T25">
-        <v>41.4</v>
+        <v>45.35</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -4084,18 +4372,18 @@
       </c>
       <c r="X25">
         <f t="shared" si="1"/>
-        <v>44.699999999999996</v>
+        <v>48.85</v>
       </c>
       <c r="Y25">
         <f t="shared" si="2"/>
-        <v>44.699999999999996</v>
+        <v>48.85</v>
       </c>
       <c r="Z25">
         <v>0</v>
       </c>
       <c r="AA25">
         <f t="shared" si="6"/>
-        <v>1236.9999999999998</v>
+        <v>1095.25</v>
       </c>
       <c r="AB25">
         <v>0</v>
@@ -4131,25 +4419,25 @@
         <v>331.95</v>
       </c>
       <c r="AL25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM25">
-        <v>9.8000000000000007</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="AN25" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO25">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="AP25">
-        <v>52.5</v>
+        <v>17.3</v>
       </c>
       <c r="AQ25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR25" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS25">
         <v>31</v>
@@ -4166,51 +4454,51 @@
         <v>4</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s">
         <v>115</v>
       </c>
       <c r="J26" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M26" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O26" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="P26">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q26">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="R26">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>16.166666666666668</v>
       </c>
       <c r="S26" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T26">
-        <v>44.4</v>
+        <v>45.45</v>
       </c>
       <c r="U26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -4220,18 +4508,18 @@
       </c>
       <c r="X26">
         <f t="shared" si="1"/>
-        <v>47.6</v>
+        <v>48.7</v>
       </c>
       <c r="Y26">
         <f t="shared" si="2"/>
-        <v>23.8</v>
+        <v>48.70000000000001</v>
       </c>
       <c r="Z26">
         <v>0</v>
       </c>
       <c r="AA26">
         <f t="shared" si="6"/>
-        <v>1189.3999999999999</v>
+        <v>1046.55</v>
       </c>
       <c r="AB26">
         <v>0</v>
@@ -4267,25 +4555,25 @@
         <v>331.95</v>
       </c>
       <c r="AL26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AM26">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="AN26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO26">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="AP26">
-        <v>50.9</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AQ26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS26">
         <v>31</v>
@@ -4302,34 +4590,34 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J27" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K27">
         <v>24</v>
       </c>
       <c r="L27" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M27" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N27" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O27" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="P27">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="Q27">
         <f t="shared" si="5"/>
@@ -4337,16 +4625,16 @@
       </c>
       <c r="R27">
         <f t="shared" si="0"/>
-        <v>12.958333333333334</v>
+        <v>15.75</v>
       </c>
       <c r="S27" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="T27">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="U27">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -4356,18 +4644,18 @@
       </c>
       <c r="X27">
         <f t="shared" si="1"/>
-        <v>45.3</v>
+        <v>44.85</v>
       </c>
       <c r="Y27">
         <f t="shared" si="2"/>
-        <v>45.29999999999999</v>
+        <v>44.85</v>
       </c>
       <c r="Z27">
         <v>0</v>
       </c>
       <c r="AA27">
         <f t="shared" si="6"/>
-        <v>1144.0999999999999</v>
+        <v>1001.6999999999999</v>
       </c>
       <c r="AB27">
         <v>0</v>
@@ -4403,25 +4691,25 @@
         <v>331.95</v>
       </c>
       <c r="AL27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM27">
-        <v>9.1</v>
+        <v>3.6</v>
       </c>
       <c r="AN27" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO27">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="AP27">
-        <v>13.9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR27" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS27">
         <v>31</v>
@@ -4438,34 +4726,34 @@
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K28">
         <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M28" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N28" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P28">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q28">
         <f t="shared" si="5"/>
@@ -4473,16 +4761,16 @@
       </c>
       <c r="R28">
         <f t="shared" si="0"/>
-        <v>16.083333333333332</v>
+        <v>16</v>
       </c>
       <c r="S28" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="T28">
-        <v>45.35</v>
+        <v>43.15</v>
       </c>
       <c r="U28">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -4492,18 +4780,18 @@
       </c>
       <c r="X28">
         <f t="shared" si="1"/>
-        <v>48.85</v>
+        <v>46.449999999999996</v>
       </c>
       <c r="Y28">
         <f t="shared" si="2"/>
-        <v>48.85</v>
+        <v>46.449999999999996</v>
       </c>
       <c r="Z28">
         <v>0</v>
       </c>
       <c r="AA28">
         <f t="shared" si="6"/>
-        <v>1095.25</v>
+        <v>955.24999999999989</v>
       </c>
       <c r="AB28">
         <v>0</v>
@@ -4539,25 +4827,25 @@
         <v>331.95</v>
       </c>
       <c r="AL28">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AM28">
-        <v>39.299999999999997</v>
+        <v>14.3</v>
       </c>
       <c r="AN28" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO28">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="AP28">
-        <v>17.3</v>
+        <v>55.1</v>
       </c>
       <c r="AQ28" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR28" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS28">
         <v>31</v>
@@ -4574,34 +4862,34 @@
         <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J29" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L29" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M29" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N29" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O29" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="P29">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="Q29">
         <f t="shared" si="5"/>
@@ -4609,16 +4897,16 @@
       </c>
       <c r="R29">
         <f t="shared" si="0"/>
-        <v>16.166666666666668</v>
+        <v>15.791666666666666</v>
       </c>
       <c r="S29" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="T29">
-        <v>45.45</v>
+        <v>42.2</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>6.85</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -4628,18 +4916,18 @@
       </c>
       <c r="X29">
         <f t="shared" si="1"/>
-        <v>48.7</v>
+        <v>49.050000000000004</v>
       </c>
       <c r="Y29">
         <f t="shared" si="2"/>
-        <v>48.70000000000001</v>
+        <v>49.050000000000004</v>
       </c>
       <c r="Z29">
         <v>0</v>
       </c>
       <c r="AA29">
         <f t="shared" si="6"/>
-        <v>1046.55</v>
+        <v>906.19999999999993</v>
       </c>
       <c r="AB29">
         <v>0</v>
@@ -4674,26 +4962,26 @@
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL29">
-        <v>28</v>
-      </c>
-      <c r="AM29">
-        <v>53.7</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO29">
-        <v>143</v>
-      </c>
-      <c r="AP29">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AQ29" t="s">
-        <v>48</v>
+      <c r="AL29" s="9">
+        <v>35</v>
+      </c>
+      <c r="AM29" s="9">
+        <v>43.6</v>
+      </c>
+      <c r="AN29" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO29" s="9">
+        <v>124</v>
+      </c>
+      <c r="AP29" s="9">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AQ29" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="AR29" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS29">
         <v>31</v>
@@ -4710,51 +4998,51 @@
         <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="K30">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="L30" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M30" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O30" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="P30">
-        <v>378</v>
+        <v>113</v>
       </c>
       <c r="Q30">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>7.1999999998952262</v>
       </c>
       <c r="R30">
         <f t="shared" si="0"/>
-        <v>15.75</v>
+        <v>15.694444444672829</v>
       </c>
       <c r="S30" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T30">
-        <v>41.75</v>
+        <v>13.6</v>
       </c>
       <c r="U30">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4764,18 +5052,18 @@
       </c>
       <c r="X30">
         <f t="shared" si="1"/>
-        <v>44.85</v>
+        <v>15.25</v>
       </c>
       <c r="Y30">
         <f t="shared" si="2"/>
-        <v>44.85</v>
+        <v>50.833333334073053</v>
       </c>
       <c r="Z30">
         <v>0</v>
       </c>
       <c r="AA30">
         <f t="shared" si="6"/>
-        <v>1001.6999999999999</v>
+        <v>890.94999999999993</v>
       </c>
       <c r="AB30">
         <v>0</v>
@@ -4810,26 +5098,26 @@
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL30">
-        <v>30</v>
-      </c>
-      <c r="AM30">
-        <v>3.6</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO30">
-        <v>136</v>
-      </c>
-      <c r="AP30">
-        <v>7.6</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>48</v>
+      <c r="AL30" s="9">
+        <v>33</v>
+      </c>
+      <c r="AM30" s="9">
+        <v>43.3</v>
+      </c>
+      <c r="AN30" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO30" s="9">
+        <v>124</v>
+      </c>
+      <c r="AP30" s="9">
+        <v>10.9</v>
+      </c>
+      <c r="AQ30" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="AR30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AS30">
         <v>31</v>
@@ -4846,51 +5134,51 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H31" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J31" t="s">
         <v>122</v>
       </c>
-      <c r="J31" t="s">
-        <v>45</v>
-      </c>
       <c r="K31">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="L31" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M31" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="N31" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O31" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="P31">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="Q31">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>12.500000000058208</v>
       </c>
       <c r="R31">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19.999999999906869</v>
       </c>
       <c r="S31" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="T31">
-        <v>43.15</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -4900,24 +5188,24 @@
       </c>
       <c r="X31">
         <f t="shared" si="1"/>
-        <v>46.449999999999996</v>
+        <v>0</v>
       </c>
       <c r="Y31">
         <f t="shared" si="2"/>
-        <v>46.449999999999996</v>
+        <v>0</v>
       </c>
       <c r="Z31">
         <v>0</v>
       </c>
       <c r="AA31">
         <f t="shared" si="6"/>
-        <v>955.24999999999989</v>
+        <v>890.94999999999993</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -4933,39 +5221,39 @@
       </c>
       <c r="AH31">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="AI31">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41.8559999998051</v>
       </c>
       <c r="AJ31">
         <v>0</v>
       </c>
       <c r="AK31">
         <f t="shared" si="7"/>
-        <v>331.95</v>
-      </c>
-      <c r="AL31">
-        <v>31</v>
-      </c>
-      <c r="AM31">
-        <v>14.3</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO31">
-        <v>128</v>
-      </c>
-      <c r="AP31">
-        <v>55.1</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>48</v>
+        <v>310.14999999999998</v>
+      </c>
+      <c r="AL31" s="9">
+        <v>37</v>
+      </c>
+      <c r="AM31" s="9">
+        <v>43.1</v>
+      </c>
+      <c r="AN31" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO31" s="9">
+        <v>124</v>
+      </c>
+      <c r="AP31" s="9">
+        <v>8.4</v>
+      </c>
+      <c r="AQ31" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="AR31" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AS31">
         <v>31</v>
@@ -4982,51 +5270,51 @@
         <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J32" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K32">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M32" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N32" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O32" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="P32">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>4.3000000000465661</v>
       </c>
       <c r="R32">
         <f t="shared" si="0"/>
-        <v>15.791666666666666</v>
+        <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="T32">
-        <v>42.2</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -5036,27 +5324,27 @@
       </c>
       <c r="X32">
         <f t="shared" si="1"/>
-        <v>49.050000000000004</v>
+        <v>0</v>
       </c>
       <c r="Y32">
         <f t="shared" si="2"/>
-        <v>49.050000000000004</v>
+        <v>0</v>
       </c>
       <c r="Z32">
         <v>0</v>
       </c>
       <c r="AA32">
         <f t="shared" si="6"/>
-        <v>906.19999999999993</v>
+        <v>890.94999999999993</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -5069,39 +5357,39 @@
       </c>
       <c r="AH32">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.85000000000000009</v>
       </c>
       <c r="AI32">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.7441860464602517</v>
       </c>
       <c r="AJ32">
         <v>0</v>
       </c>
       <c r="AK32">
         <f t="shared" si="7"/>
-        <v>331.95</v>
-      </c>
-      <c r="AL32" s="11">
-        <v>35</v>
-      </c>
-      <c r="AM32" s="11">
-        <v>43.6</v>
-      </c>
-      <c r="AN32" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO32" s="11">
-        <v>124</v>
-      </c>
-      <c r="AP32" s="11">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="AQ32" s="11" t="s">
-        <v>48</v>
+        <v>309.29999999999995</v>
+      </c>
+      <c r="AL32" s="10">
+        <v>37</v>
+      </c>
+      <c r="AM32" s="10">
+        <v>43.1</v>
+      </c>
+      <c r="AN32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO32" s="10">
+        <v>120</v>
+      </c>
+      <c r="AP32" s="10">
+        <v>8.4</v>
+      </c>
+      <c r="AQ32" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="AR32" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS32">
         <v>31</v>
@@ -5118,51 +5406,51 @@
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H33" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K33">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M33" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N33" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O33" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="P33">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <f t="shared" si="5"/>
-        <v>7.1999999998952262</v>
+        <v>3</v>
       </c>
       <c r="R33">
         <f t="shared" si="0"/>
-        <v>15.694444444672829</v>
+        <v>2</v>
       </c>
       <c r="S33" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="T33">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -5172,11 +5460,11 @@
       </c>
       <c r="X33">
         <f t="shared" si="1"/>
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="Y33">
         <f t="shared" si="2"/>
-        <v>50.833333334073053</v>
+        <v>0</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5186,13 +5474,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -5205,39 +5493,39 @@
       </c>
       <c r="AH33">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="AI33">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="AJ33">
         <v>0</v>
       </c>
       <c r="AK33">
         <f t="shared" si="7"/>
-        <v>331.95</v>
-      </c>
-      <c r="AL33" s="11">
-        <v>33</v>
-      </c>
-      <c r="AM33" s="11">
-        <v>43.3</v>
-      </c>
-      <c r="AN33" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO33" s="11">
-        <v>124</v>
-      </c>
-      <c r="AP33" s="11">
-        <v>10.9</v>
-      </c>
-      <c r="AQ33" s="11" t="s">
-        <v>48</v>
+        <v>307.24999999999994</v>
+      </c>
+      <c r="AL33" s="10">
+        <v>37</v>
+      </c>
+      <c r="AM33" s="10">
+        <v>38.1</v>
+      </c>
+      <c r="AN33" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO33" s="10">
+        <v>120</v>
+      </c>
+      <c r="AP33" s="10">
+        <v>14.4</v>
+      </c>
+      <c r="AQ33" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="AR33" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AS33">
         <v>31</v>
@@ -5254,45 +5542,45 @@
         <v>4</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J34" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="K34">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M34" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N34" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="P34">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <f t="shared" si="5"/>
-        <v>12.500000000058208</v>
+        <v>21</v>
       </c>
       <c r="R34">
         <f t="shared" si="0"/>
-        <v>19.999999999906869</v>
+        <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -5322,13 +5610,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB34">
-        <v>20.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.45</v>
+        <v>3.9</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -5341,39 +5629,39 @@
       </c>
       <c r="AH34">
         <f t="shared" si="3"/>
-        <v>21.8</v>
+        <v>5</v>
       </c>
       <c r="AI34">
         <f t="shared" si="4"/>
-        <v>41.8559999998051</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="AJ34">
         <v>0</v>
       </c>
       <c r="AK34">
         <f t="shared" si="7"/>
-        <v>310.14999999999998</v>
+        <v>302.24999999999994</v>
       </c>
       <c r="AL34" s="11">
         <v>37</v>
       </c>
       <c r="AM34" s="11">
-        <v>43.1</v>
+        <v>39.4</v>
       </c>
       <c r="AN34" s="11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO34" s="11">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AP34" s="11">
-        <v>8.4</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="AQ34" s="11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR34" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AS34">
         <v>31</v>
@@ -5390,45 +5678,45 @@
         <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J35" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="K35">
-        <v>4.3</v>
+        <v>22</v>
       </c>
       <c r="L35" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" t="s">
+        <v>53</v>
+      </c>
+      <c r="N35" t="s">
+        <v>41</v>
+      </c>
+      <c r="O35" t="s">
         <v>57</v>
-      </c>
-      <c r="M35" t="s">
-        <v>58</v>
-      </c>
-      <c r="N35" t="s">
-        <v>46</v>
-      </c>
-      <c r="O35" t="s">
-        <v>130</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35">
         <f t="shared" si="5"/>
-        <v>4.3000000000465661</v>
+        <v>21.999999999941792</v>
       </c>
       <c r="R35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="T35">
         <v>0</v>
@@ -5458,13 +5746,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB35">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>0.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD35">
-        <v>0.3</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -5477,39 +5765,39 @@
       </c>
       <c r="AH35">
         <f t="shared" si="3"/>
-        <v>0.85000000000000009</v>
+        <v>5.6999999999999993</v>
       </c>
       <c r="AI35">
         <f t="shared" si="4"/>
-        <v>4.7441860464602517</v>
+        <v>6.2181818181982695</v>
       </c>
       <c r="AJ35">
         <v>0</v>
       </c>
       <c r="AK35">
         <f t="shared" si="7"/>
-        <v>309.29999999999995</v>
-      </c>
-      <c r="AL35" s="12">
+        <v>296.54999999999995</v>
+      </c>
+      <c r="AL35" s="11">
         <v>37</v>
       </c>
-      <c r="AM35" s="12">
-        <v>43.1</v>
-      </c>
-      <c r="AN35" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO35" s="12">
+      <c r="AM35" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="AN35" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO35" s="11">
         <v>120</v>
       </c>
-      <c r="AP35" s="12">
-        <v>8.4</v>
-      </c>
-      <c r="AQ35" s="12" t="s">
-        <v>48</v>
+      <c r="AP35" s="11">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AQ35" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="AR35" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AS35">
         <v>31</v>
@@ -5526,45 +5814,45 @@
         <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J36" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M36" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N36" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O36" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2.0000000000582077</v>
       </c>
       <c r="R36">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="T36">
         <v>0</v>
@@ -5594,13 +5882,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AD36">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -5613,39 +5901,39 @@
       </c>
       <c r="AH36">
         <f t="shared" si="3"/>
-        <v>2.0499999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="AI36">
         <f t="shared" si="4"/>
-        <v>16.399999999999999</v>
+        <v>3.5999999998952257</v>
       </c>
       <c r="AJ36">
         <v>0</v>
       </c>
       <c r="AK36">
         <f t="shared" si="7"/>
-        <v>307.24999999999994</v>
-      </c>
-      <c r="AL36" s="12">
+        <v>296.24999999999994</v>
+      </c>
+      <c r="AL36" s="13">
         <v>37</v>
       </c>
-      <c r="AM36" s="12">
-        <v>38.1</v>
-      </c>
-      <c r="AN36" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO36" s="12">
+      <c r="AM36" s="13">
+        <v>39.4</v>
+      </c>
+      <c r="AN36" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO36" s="13">
         <v>120</v>
       </c>
-      <c r="AP36" s="12">
-        <v>14.4</v>
-      </c>
-      <c r="AQ36" s="12" t="s">
-        <v>48</v>
+      <c r="AP36" s="13">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="AQ36" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="AR36" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AS36">
         <v>31</v>
@@ -5662,45 +5950,45 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s">
+        <v>133</v>
+      </c>
+      <c r="J37" t="s">
+        <v>80</v>
+      </c>
+      <c r="K37">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L37" t="s">
+        <v>53</v>
+      </c>
+      <c r="M37" t="s">
+        <v>47</v>
+      </c>
+      <c r="N37" t="s">
+        <v>41</v>
+      </c>
+      <c r="O37" t="s">
         <v>134</v>
       </c>
-      <c r="J37" t="s">
-        <v>45</v>
-      </c>
-      <c r="K37">
-        <v>21</v>
-      </c>
-      <c r="L37" t="s">
-        <v>68</v>
-      </c>
-      <c r="M37" t="s">
-        <v>68</v>
-      </c>
-      <c r="N37" t="s">
-        <v>46</v>
-      </c>
-      <c r="O37" t="s">
-        <v>135</v>
-      </c>
       <c r="P37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>1.0999999999185093</v>
       </c>
       <c r="R37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.2727272732660539</v>
       </c>
       <c r="S37" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="T37">
         <v>0</v>
@@ -5730,13 +6018,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AC37">
-        <v>3.9</v>
+        <v>0.25</v>
       </c>
       <c r="AD37">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -5749,18 +6037,18 @@
       </c>
       <c r="AH37">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>1.05</v>
       </c>
       <c r="AI37">
         <f t="shared" si="4"/>
-        <v>5.7142857142857144</v>
+        <v>22.909090910788073</v>
       </c>
       <c r="AJ37">
         <v>0</v>
       </c>
       <c r="AK37">
         <f t="shared" si="7"/>
-        <v>302.24999999999994</v>
+        <v>295.19999999999993</v>
       </c>
       <c r="AL37" s="13">
         <v>37</v>
@@ -5769,7 +6057,7 @@
         <v>39.4</v>
       </c>
       <c r="AN37" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO37" s="13">
         <v>120</v>
@@ -5778,10 +6066,10 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AQ37" s="13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR37" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AS37">
         <v>31</v>
@@ -5792,51 +6080,51 @@
         <v>2025</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="K38">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="L38" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="M38" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="N38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O38" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="Q38">
         <f t="shared" si="5"/>
-        <v>21.999999999941792</v>
+        <v>10.5</v>
       </c>
       <c r="R38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.523809523809524</v>
       </c>
       <c r="S38" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="T38">
         <v>0</v>
@@ -5866,13 +6154,13 @@
         <v>890.94999999999993</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="AC38">
-        <v>4.55</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AD38">
-        <v>1.1499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -5885,27 +6173,27 @@
       </c>
       <c r="AH38">
         <f t="shared" si="3"/>
-        <v>5.6999999999999993</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="AI38">
         <f t="shared" si="4"/>
-        <v>6.2181818181982695</v>
+        <v>37.48571428571428</v>
       </c>
       <c r="AJ38">
         <v>0</v>
       </c>
       <c r="AK38">
         <f t="shared" si="7"/>
-        <v>296.54999999999995</v>
+        <v>278.79999999999995</v>
       </c>
       <c r="AL38" s="13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AM38" s="13">
-        <v>39.4</v>
+        <v>41.4</v>
       </c>
       <c r="AN38" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO38" s="13">
         <v>120</v>
@@ -5914,10 +6202,10 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AQ38" s="13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR38" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="AS38">
         <v>31</v>
@@ -5928,57 +6216,57 @@
         <v>2025</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="H39" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="I39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>12.4</v>
       </c>
       <c r="L39" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M39" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="N39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O39" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="Q39">
         <f t="shared" si="5"/>
-        <v>2.0000000000582077</v>
+        <v>12.400000000081491</v>
       </c>
       <c r="R39">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.967741935378934</v>
       </c>
       <c r="S39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -5988,27 +6276,27 @@
       </c>
       <c r="X39">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>35.806451612667914</v>
       </c>
       <c r="Z39">
         <v>0</v>
       </c>
       <c r="AA39">
         <f t="shared" si="6"/>
-        <v>890.94999999999993</v>
+        <v>872.44999999999993</v>
       </c>
       <c r="AB39">
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6021,39 +6309,39 @@
       </c>
       <c r="AH39">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AI39">
         <f t="shared" si="4"/>
-        <v>3.5999999998952257</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
         <v>0</v>
       </c>
       <c r="AK39">
         <f t="shared" si="7"/>
-        <v>296.24999999999994</v>
-      </c>
-      <c r="AL39" s="15">
-        <v>37</v>
-      </c>
-      <c r="AM39" s="15">
-        <v>39.4</v>
-      </c>
-      <c r="AN39" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO39" s="15">
-        <v>120</v>
-      </c>
-      <c r="AP39" s="15">
+        <v>278.79999999999995</v>
+      </c>
+      <c r="AL39" s="12">
+        <v>35</v>
+      </c>
+      <c r="AM39" s="12">
+        <v>41.7</v>
+      </c>
+      <c r="AN39" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO39" s="12">
+        <v>125</v>
+      </c>
+      <c r="AP39" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ39" s="15" t="s">
-        <v>48</v>
+      <c r="AQ39" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="AR39" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS39">
         <v>31</v>
@@ -6064,57 +6352,57 @@
         <v>2025</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="I40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="K40">
-        <v>1.1000000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="L40" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M40" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O40" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="P40">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <f t="shared" si="5"/>
-        <v>1.0999999999185093</v>
+        <v>11.499999999941792</v>
       </c>
       <c r="R40">
         <f t="shared" si="0"/>
-        <v>7.2727272732660539</v>
+        <v>16.086956521820554</v>
       </c>
       <c r="S40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -6124,24 +6412,24 @@
       </c>
       <c r="X40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>43.826086956743566</v>
       </c>
       <c r="Z40">
         <v>0</v>
       </c>
       <c r="AA40">
         <f t="shared" si="6"/>
-        <v>890.94999999999993</v>
+        <v>851.44999999999993</v>
       </c>
       <c r="AB40">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -6157,39 +6445,39 @@
       </c>
       <c r="AH40">
         <f t="shared" si="3"/>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI40">
         <f t="shared" si="4"/>
-        <v>22.909090910788073</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
         <v>0</v>
       </c>
       <c r="AK40">
         <f t="shared" si="7"/>
-        <v>295.19999999999993</v>
-      </c>
-      <c r="AL40" s="15">
-        <v>37</v>
-      </c>
-      <c r="AM40" s="15">
-        <v>39.4</v>
-      </c>
-      <c r="AN40" s="15" t="s">
+        <v>278.79999999999995</v>
+      </c>
+      <c r="AL40" s="12">
+        <v>34</v>
+      </c>
+      <c r="AM40" s="12">
+        <v>41.7</v>
+      </c>
+      <c r="AN40" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO40" s="12">
+        <v>125</v>
+      </c>
+      <c r="AP40" s="12">
+        <v>34.1</v>
+      </c>
+      <c r="AQ40" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR40" t="s">
         <v>47</v>
-      </c>
-      <c r="AO40" s="15">
-        <v>120</v>
-      </c>
-      <c r="AP40" s="15">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="AQ40" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR40" t="s">
-        <v>58</v>
       </c>
       <c r="AS40">
         <v>31</v>
@@ -6206,45 +6494,45 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J41" t="s">
-        <v>143</v>
+        <v>56</v>
       </c>
       <c r="K41">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="L41" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M41" t="s">
         <v>52</v>
       </c>
       <c r="N41" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O41" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="P41">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="Q41">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="R41">
         <f t="shared" si="0"/>
-        <v>15.523809523809524</v>
+        <v>15.333333333333334</v>
       </c>
       <c r="S41" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="T41">
         <v>0</v>
@@ -6271,13 +6559,13 @@
       </c>
       <c r="AA41">
         <f t="shared" si="6"/>
-        <v>890.94999999999993</v>
+        <v>851.44999999999993</v>
       </c>
       <c r="AB41">
-        <v>15.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
-        <v>1.1499999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -6293,39 +6581,39 @@
       </c>
       <c r="AH41">
         <f t="shared" si="3"/>
-        <v>16.399999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="AI41">
         <f t="shared" si="4"/>
-        <v>37.48571428571428</v>
+        <v>31.2</v>
       </c>
       <c r="AJ41">
         <v>0</v>
       </c>
       <c r="AK41">
         <f t="shared" si="7"/>
-        <v>278.79999999999995</v>
-      </c>
-      <c r="AL41" s="15">
-        <v>36</v>
-      </c>
-      <c r="AM41" s="15">
-        <v>41.4</v>
-      </c>
-      <c r="AN41" s="15" t="s">
+        <v>276.84999999999997</v>
+      </c>
+      <c r="AL41" s="12">
+        <v>33</v>
+      </c>
+      <c r="AM41" s="12">
+        <v>42.7</v>
+      </c>
+      <c r="AN41" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO41" s="12">
+        <v>125</v>
+      </c>
+      <c r="AP41" s="12">
+        <v>40.1</v>
+      </c>
+      <c r="AQ41" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR41" t="s">
         <v>47</v>
-      </c>
-      <c r="AO41" s="15">
-        <v>120</v>
-      </c>
-      <c r="AP41" s="15">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="AQ41" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR41" t="s">
-        <v>52</v>
       </c>
       <c r="AS41">
         <v>31</v>
@@ -6342,51 +6630,51 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H42" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J42" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="K42">
-        <v>12.4</v>
+        <v>7.5</v>
       </c>
       <c r="L42" t="s">
         <v>52</v>
       </c>
       <c r="M42" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N42" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P42">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <f t="shared" si="5"/>
-        <v>12.400000000081491</v>
+        <v>7.5</v>
       </c>
       <c r="R42">
         <f t="shared" si="0"/>
-        <v>15.967741935378934</v>
+        <v>0</v>
       </c>
       <c r="S42" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="T42">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -6396,27 +6684,27 @@
       </c>
       <c r="X42">
         <f t="shared" si="1"/>
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y42">
         <f t="shared" si="2"/>
-        <v>35.806451612667914</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="AA42">
         <f t="shared" si="6"/>
-        <v>872.44999999999993</v>
+        <v>1601.4499999999998</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -6429,39 +6717,39 @@
       </c>
       <c r="AH42">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5499999999999998</v>
       </c>
       <c r="AI42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4.9599999999999991</v>
       </c>
       <c r="AJ42">
         <v>0</v>
       </c>
       <c r="AK42">
         <f t="shared" si="7"/>
-        <v>278.79999999999995</v>
-      </c>
-      <c r="AL42" s="14">
-        <v>35</v>
-      </c>
-      <c r="AM42" s="14">
-        <v>41.7</v>
-      </c>
-      <c r="AN42" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO42" s="14">
+        <v>275.29999999999995</v>
+      </c>
+      <c r="AL42" s="12">
+        <v>33</v>
+      </c>
+      <c r="AM42" s="12">
+        <v>42.7</v>
+      </c>
+      <c r="AN42" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO42" s="12">
         <v>125</v>
       </c>
-      <c r="AP42" s="14">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="AQ42" s="14" t="s">
-        <v>48</v>
+      <c r="AP42" s="12">
+        <v>40.1</v>
+      </c>
+      <c r="AQ42" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="AR42" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AS42">
         <v>31</v>
@@ -6475,54 +6763,54 @@
         <v>6</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H43" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K43">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="L43" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M43" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N43" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O43" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="P43">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <f t="shared" si="5"/>
-        <v>11.499999999941792</v>
+        <v>0.50000000005820766</v>
       </c>
       <c r="R43">
         <f t="shared" si="0"/>
-        <v>16.086956521820554</v>
+        <v>9.9999999988358468</v>
       </c>
       <c r="S43" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="T43">
-        <v>19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -6532,24 +6820,24 @@
       </c>
       <c r="X43">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y43">
         <f t="shared" si="2"/>
-        <v>43.826086956743566</v>
+        <v>0</v>
       </c>
       <c r="Z43">
         <v>0</v>
       </c>
       <c r="AA43">
         <f t="shared" si="6"/>
-        <v>851.44999999999993</v>
+        <v>1601.4499999999998</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6565,39 +6853,39 @@
       </c>
       <c r="AH43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="AI43">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21.599999997485426</v>
       </c>
       <c r="AJ43">
         <v>0</v>
       </c>
       <c r="AK43">
         <f t="shared" si="7"/>
-        <v>278.79999999999995</v>
-      </c>
-      <c r="AL43" s="14">
-        <v>34</v>
-      </c>
-      <c r="AM43" s="14">
-        <v>41.7</v>
-      </c>
-      <c r="AN43" s="14" t="s">
+        <v>274.84999999999997</v>
+      </c>
+      <c r="AL43" s="12">
+        <v>33</v>
+      </c>
+      <c r="AM43" s="12">
+        <v>42.7</v>
+      </c>
+      <c r="AN43" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO43" s="12">
+        <v>125</v>
+      </c>
+      <c r="AP43" s="12">
+        <v>42.1</v>
+      </c>
+      <c r="AQ43" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR43" t="s">
         <v>47</v>
-      </c>
-      <c r="AO43" s="14">
-        <v>125</v>
-      </c>
-      <c r="AP43" s="14">
-        <v>34.1</v>
-      </c>
-      <c r="AQ43" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR43" t="s">
-        <v>52</v>
       </c>
       <c r="AS43">
         <v>31</v>
@@ -6611,54 +6899,54 @@
         <v>6</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H44" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J44" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="K44">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L44" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M44" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N44" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O44" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="P44">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="Q44">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="R44">
         <f t="shared" si="0"/>
-        <v>15.333333333333334</v>
+        <v>22.333333333333332</v>
       </c>
       <c r="S44" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6668,24 +6956,24 @@
       </c>
       <c r="X44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="Y44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30.400000000000002</v>
       </c>
       <c r="Z44">
         <v>0</v>
       </c>
       <c r="AA44">
         <f t="shared" si="6"/>
-        <v>851.44999999999993</v>
+        <v>1597.6499999999999</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6701,39 +6989,39 @@
       </c>
       <c r="AH44">
         <f t="shared" si="3"/>
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI44">
         <f t="shared" si="4"/>
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
         <v>0</v>
       </c>
       <c r="AK44">
         <f t="shared" si="7"/>
-        <v>276.84999999999997</v>
-      </c>
-      <c r="AL44" s="14">
+        <v>274.84999999999997</v>
+      </c>
+      <c r="AL44">
         <v>33</v>
       </c>
-      <c r="AM44" s="14">
-        <v>42.7</v>
-      </c>
-      <c r="AN44" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO44" s="14">
-        <v>125</v>
-      </c>
-      <c r="AP44" s="14">
-        <v>40.1</v>
-      </c>
-      <c r="AQ44" s="14" t="s">
-        <v>48</v>
+      <c r="AM44">
+        <v>44.1</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO44">
+        <v>127</v>
+      </c>
+      <c r="AP44">
+        <v>53.3</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>43</v>
       </c>
       <c r="AR44" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AS44">
         <v>31</v>
@@ -6747,54 +7035,54 @@
         <v>6</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H45" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="I45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J45" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="K45">
-        <v>7.5</v>
+        <v>24</v>
       </c>
       <c r="L45" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="M45" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O45" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="Q45">
         <f t="shared" si="5"/>
-        <v>7.5</v>
+        <v>24</v>
       </c>
       <c r="R45">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.833333333333334</v>
       </c>
       <c r="S45" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6804,27 +7092,27 @@
       </c>
       <c r="X45">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40.050000000000004</v>
       </c>
       <c r="Y45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40.050000000000004</v>
       </c>
       <c r="Z45">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="AA45">
         <f t="shared" si="6"/>
-        <v>1601.4499999999998</v>
+        <v>1557.6</v>
       </c>
       <c r="AB45">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="AE45">
         <v>0</v>
@@ -6837,39 +7125,39 @@
       </c>
       <c r="AH45">
         <f t="shared" si="3"/>
-        <v>1.5499999999999998</v>
+        <v>0</v>
       </c>
       <c r="AI45">
         <f t="shared" si="4"/>
-        <v>4.9599999999999991</v>
+        <v>0</v>
       </c>
       <c r="AJ45">
         <v>0</v>
       </c>
       <c r="AK45">
         <f t="shared" si="7"/>
-        <v>275.29999999999995</v>
-      </c>
-      <c r="AL45" s="14">
-        <v>33</v>
-      </c>
-      <c r="AM45" s="14">
-        <v>42.7</v>
-      </c>
-      <c r="AN45" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO45" s="14">
-        <v>125</v>
-      </c>
-      <c r="AP45" s="14">
-        <v>40.1</v>
-      </c>
-      <c r="AQ45" s="14" t="s">
-        <v>48</v>
+        <v>274.84999999999997</v>
+      </c>
+      <c r="AL45">
+        <v>30</v>
+      </c>
+      <c r="AM45">
+        <v>53.1</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO45">
+        <v>132</v>
+      </c>
+      <c r="AP45">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AQ45" t="s">
+        <v>43</v>
       </c>
       <c r="AR45" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="AS45">
         <v>31</v>
@@ -6886,51 +7174,51 @@
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H46" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J46" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="K46">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N46" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O46" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="Q46">
         <f t="shared" si="5"/>
-        <v>0.50000000005820766</v>
+        <v>24</v>
       </c>
       <c r="R46">
         <f t="shared" si="0"/>
-        <v>9.9999999988358468</v>
+        <v>16.541666666666668</v>
       </c>
       <c r="S46" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6940,24 +7228,24 @@
       </c>
       <c r="X46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="Y46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="Z46">
         <v>0</v>
       </c>
       <c r="AA46">
         <f t="shared" si="6"/>
-        <v>1601.4499999999998</v>
+        <v>1513.35</v>
       </c>
       <c r="AB46">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6973,11 +7261,11 @@
       </c>
       <c r="AH46">
         <f t="shared" si="3"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AI46">
         <f t="shared" si="4"/>
-        <v>21.599999997485426</v>
+        <v>0</v>
       </c>
       <c r="AJ46">
         <v>0</v>
@@ -6986,26 +7274,26 @@
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL46" s="14">
-        <v>33</v>
-      </c>
-      <c r="AM46" s="14">
-        <v>42.7</v>
-      </c>
-      <c r="AN46" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO46" s="14">
-        <v>125</v>
-      </c>
-      <c r="AP46" s="14">
-        <v>42.1</v>
-      </c>
-      <c r="AQ46" s="14" t="s">
-        <v>48</v>
+      <c r="AL46">
+        <v>30</v>
+      </c>
+      <c r="AM46">
+        <v>42.5</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO46">
+        <v>140</v>
+      </c>
+      <c r="AP46">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AQ46" t="s">
+        <v>43</v>
       </c>
       <c r="AR46" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AS46">
         <v>31</v>
@@ -7022,51 +7310,51 @@
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H47" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J47" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L47" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M47" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N47" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P47">
-        <v>67</v>
+        <v>384</v>
       </c>
       <c r="Q47">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R47">
         <f t="shared" si="0"/>
-        <v>22.333333333333332</v>
+        <v>16</v>
       </c>
       <c r="S47" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="T47">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="U47">
         <v>3.45</v>
-      </c>
-      <c r="U47">
-        <v>0.35</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -7076,18 +7364,18 @@
       </c>
       <c r="X47">
         <f t="shared" si="1"/>
-        <v>3.8000000000000003</v>
+        <v>41.150000000000006</v>
       </c>
       <c r="Y47">
         <f t="shared" si="2"/>
-        <v>30.400000000000002</v>
+        <v>41.150000000000006</v>
       </c>
       <c r="Z47">
         <v>0</v>
       </c>
       <c r="AA47">
         <f t="shared" si="6"/>
-        <v>1597.6499999999999</v>
+        <v>1472.1999999999998</v>
       </c>
       <c r="AB47">
         <v>0</v>
@@ -7123,25 +7411,25 @@
         <v>274.84999999999997</v>
       </c>
       <c r="AL47">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AM47">
-        <v>44.1</v>
+        <v>14.4</v>
       </c>
       <c r="AN47" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO47">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="AP47">
-        <v>53.3</v>
+        <v>28.4</v>
       </c>
       <c r="AQ47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS47">
         <v>31</v>
@@ -7158,34 +7446,34 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H48" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J48" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K48">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L48" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M48" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N48" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O48" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P48">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="Q48">
         <f t="shared" si="5"/>
@@ -7193,16 +7481,16 @@
       </c>
       <c r="R48">
         <f t="shared" si="0"/>
-        <v>15.833333333333334</v>
+        <v>15.375</v>
       </c>
       <c r="S48" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="T48">
-        <v>36.700000000000003</v>
+        <v>37.75</v>
       </c>
       <c r="U48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -7212,18 +7500,18 @@
       </c>
       <c r="X48">
         <f t="shared" si="1"/>
-        <v>40.050000000000004</v>
+        <v>41.15</v>
       </c>
       <c r="Y48">
         <f t="shared" si="2"/>
-        <v>40.050000000000004</v>
+        <v>41.15</v>
       </c>
       <c r="Z48">
         <v>0</v>
       </c>
       <c r="AA48">
         <f t="shared" si="6"/>
-        <v>1557.6</v>
+        <v>1431.0499999999997</v>
       </c>
       <c r="AB48">
         <v>0</v>
@@ -7259,25 +7547,25 @@
         <v>274.84999999999997</v>
       </c>
       <c r="AL48">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM48">
-        <v>53.1</v>
+        <v>22.1</v>
       </c>
       <c r="AN48" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO48">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="AP48">
-        <v>37.700000000000003</v>
+        <v>26.8</v>
       </c>
       <c r="AQ48" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR48" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS48">
         <v>31</v>
@@ -7294,34 +7582,34 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H49" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J49" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K49">
         <v>24</v>
       </c>
       <c r="L49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N49" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O49" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P49">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="Q49">
         <f t="shared" si="5"/>
@@ -7329,16 +7617,16 @@
       </c>
       <c r="R49">
         <f t="shared" si="0"/>
-        <v>16.541666666666668</v>
+        <v>15.916666666666666</v>
       </c>
       <c r="S49" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="T49">
-        <v>38.450000000000003</v>
+        <v>38.1</v>
       </c>
       <c r="U49">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -7348,18 +7636,18 @@
       </c>
       <c r="X49">
         <f t="shared" si="1"/>
-        <v>44.25</v>
+        <v>44.35</v>
       </c>
       <c r="Y49">
         <f t="shared" si="2"/>
-        <v>44.25</v>
+        <v>44.35</v>
       </c>
       <c r="Z49">
         <v>0</v>
       </c>
       <c r="AA49">
         <f t="shared" si="6"/>
-        <v>1513.35</v>
+        <v>1386.6999999999998</v>
       </c>
       <c r="AB49">
         <v>0</v>
@@ -7395,454 +7683,31 @@
         <v>274.84999999999997</v>
       </c>
       <c r="AL49">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM49">
-        <v>42.5</v>
+        <v>7.4</v>
       </c>
       <c r="AN49" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AO49">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="AP49">
-        <v>9.6999999999999993</v>
+        <v>31.2</v>
       </c>
       <c r="AQ49" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AR49" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AS49">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="4:45" x14ac:dyDescent="0.3">
-      <c r="D50">
-        <v>2025</v>
-      </c>
-      <c r="E50">
-        <v>6</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="G50" t="s">
-        <v>141</v>
-      </c>
-      <c r="H50" t="s">
-        <v>83</v>
-      </c>
-      <c r="I50" t="s">
-        <v>159</v>
-      </c>
-      <c r="J50" t="s">
-        <v>45</v>
-      </c>
-      <c r="K50">
-        <v>24</v>
-      </c>
-      <c r="L50" t="s">
-        <v>52</v>
-      </c>
-      <c r="M50" t="s">
-        <v>52</v>
-      </c>
-      <c r="N50" t="s">
-        <v>53</v>
-      </c>
-      <c r="O50" t="s">
-        <v>79</v>
-      </c>
-      <c r="P50">
-        <v>384</v>
-      </c>
-      <c r="Q50">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="R50">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="S50" t="s">
-        <v>160</v>
-      </c>
-      <c r="T50">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="U50">
-        <v>3.45</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <f t="shared" si="1"/>
-        <v>41.150000000000006</v>
-      </c>
-      <c r="Y50">
-        <f t="shared" si="2"/>
-        <v>41.150000000000006</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <f t="shared" si="6"/>
-        <v>1472.1999999999998</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI50">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <f t="shared" si="7"/>
-        <v>274.84999999999997</v>
-      </c>
-      <c r="AL50">
-        <v>30</v>
-      </c>
-      <c r="AM50">
-        <v>14.4</v>
-      </c>
-      <c r="AN50" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO50">
-        <v>147</v>
-      </c>
-      <c r="AP50">
-        <v>28.4</v>
-      </c>
-      <c r="AQ50" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR50" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS50">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="4:45" x14ac:dyDescent="0.3">
-      <c r="D51">
-        <v>2025</v>
-      </c>
-      <c r="E51">
-        <v>6</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51" t="s">
-        <v>141</v>
-      </c>
-      <c r="H51" t="s">
-        <v>83</v>
-      </c>
-      <c r="I51" t="s">
-        <v>161</v>
-      </c>
-      <c r="J51" t="s">
-        <v>45</v>
-      </c>
-      <c r="K51">
-        <v>23</v>
-      </c>
-      <c r="L51" t="s">
-        <v>52</v>
-      </c>
-      <c r="M51" t="s">
-        <v>52</v>
-      </c>
-      <c r="N51" t="s">
-        <v>53</v>
-      </c>
-      <c r="O51" t="s">
-        <v>79</v>
-      </c>
-      <c r="P51">
-        <v>369</v>
-      </c>
-      <c r="Q51">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="R51">
-        <f t="shared" si="0"/>
-        <v>15.375</v>
-      </c>
-      <c r="S51" t="s">
-        <v>160</v>
-      </c>
-      <c r="T51">
-        <v>37.75</v>
-      </c>
-      <c r="U51">
-        <v>3.4</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <f t="shared" si="1"/>
-        <v>41.15</v>
-      </c>
-      <c r="Y51">
-        <f t="shared" si="2"/>
-        <v>41.15</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <f t="shared" si="6"/>
-        <v>1431.0499999999997</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
-      <c r="AH51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI51">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AJ51">
-        <v>0</v>
-      </c>
-      <c r="AK51">
-        <f t="shared" si="7"/>
-        <v>274.84999999999997</v>
-      </c>
-      <c r="AL51">
-        <v>29</v>
-      </c>
-      <c r="AM51">
-        <v>22.1</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO51">
-        <v>154</v>
-      </c>
-      <c r="AP51">
-        <v>26.8</v>
-      </c>
-      <c r="AQ51" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR51" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS51">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="4:45" x14ac:dyDescent="0.3">
-      <c r="D52">
-        <v>2025</v>
-      </c>
-      <c r="E52">
-        <v>6</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="G52" t="s">
-        <v>141</v>
-      </c>
-      <c r="H52" t="s">
-        <v>83</v>
-      </c>
-      <c r="I52" t="s">
-        <v>162</v>
-      </c>
-      <c r="J52" t="s">
-        <v>45</v>
-      </c>
-      <c r="K52">
-        <v>24</v>
-      </c>
-      <c r="L52" t="s">
-        <v>52</v>
-      </c>
-      <c r="M52" t="s">
-        <v>52</v>
-      </c>
-      <c r="N52" t="s">
-        <v>53</v>
-      </c>
-      <c r="O52" t="s">
-        <v>79</v>
-      </c>
-      <c r="P52">
-        <v>382</v>
-      </c>
-      <c r="Q52">
-        <f t="shared" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="R52">
-        <f t="shared" si="0"/>
-        <v>15.916666666666666</v>
-      </c>
-      <c r="S52" t="s">
-        <v>65</v>
-      </c>
-      <c r="T52">
-        <v>38.1</v>
-      </c>
-      <c r="U52">
-        <v>6.25</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
-      </c>
-      <c r="W52">
-        <v>0</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="1"/>
-        <v>44.35</v>
-      </c>
-      <c r="Y52">
-        <f t="shared" si="2"/>
-        <v>44.35</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
-      </c>
-      <c r="AA52">
-        <f t="shared" si="6"/>
-        <v>1386.6999999999998</v>
-      </c>
-      <c r="AB52">
-        <v>0</v>
-      </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>0</v>
-      </c>
-      <c r="AG52">
-        <v>0</v>
-      </c>
-      <c r="AH52">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI52">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AJ52">
-        <v>0</v>
-      </c>
-      <c r="AK52">
-        <f t="shared" si="7"/>
-        <v>274.84999999999997</v>
-      </c>
-      <c r="AL52">
-        <v>28</v>
-      </c>
-      <c r="AM52">
-        <v>7.4</v>
-      </c>
-      <c r="AN52" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO52">
-        <v>161</v>
-      </c>
-      <c r="AP52">
-        <v>31.2</v>
-      </c>
-      <c r="AQ52" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR52" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS52">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="4:45" x14ac:dyDescent="0.3">
-      <c r="AK53" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="4:45" x14ac:dyDescent="0.3">
-      <c r="AA56">
-        <f>1386.7 +755.63</f>
-        <v>2142.33</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="T3:AA3"/>
-    <mergeCell ref="AB3:AK3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
+++ b/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1950E20-AFC9-41B5-AC47-392C4C797030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56F4A80-958D-4207-8F60-189ADC3ED5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="166">
   <si>
     <t>voyageId</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>ROB_MGO</t>
+  </si>
+  <si>
+    <t>date_ETA</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AV49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="4" customWidth="1"/>
@@ -1024,20 +1027,20 @@
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="24.77734375" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
-    <col min="13" max="13" width="22.109375" customWidth="1"/>
-    <col min="14" max="14" width="24.21875" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="34" width="13.21875" customWidth="1"/>
-    <col min="35" max="35" width="25.109375" customWidth="1"/>
-    <col min="36" max="38" width="13.21875" customWidth="1"/>
-    <col min="39" max="47" width="8" customWidth="1"/>
+    <col min="9" max="10" width="24.77734375" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" customWidth="1"/>
+    <col min="15" max="15" width="24.21875" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="35" width="13.21875" customWidth="1"/>
+    <col min="36" max="36" width="25.109375" customWidth="1"/>
+    <col min="37" max="39" width="13.21875" customWidth="1"/>
+    <col min="40" max="48" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,121 +1069,124 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AN1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AU1" s="8" t="s">
+      <c r="AV1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D2">
         <v>2025</v>
       </c>
@@ -1200,40 +1206,40 @@
         <v>82</v>
       </c>
       <c r="J2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" t="s">
         <v>70</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
       </c>
       <c r="M2" t="s">
         <v>55</v>
       </c>
       <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
         <v>48</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>83</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>6</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <f>IFERROR((I2 -#REF!)*24,0)</f>
         <v>0</v>
       </c>
-      <c r="R2">
-        <f t="shared" ref="R2:R49" si="0">IF(ISERROR(P2/Q2),0,P2/Q2)</f>
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="S2">
+        <f t="shared" ref="S2:S49" si="0">IF(ISERROR(Q2/R2),0,Q2/R2)</f>
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
         <v>51</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -1244,28 +1250,28 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X49" si="1">SUM(T2:W2)</f>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" ref="Y2:Y49" si="2">IF(ISERROR(X2*24/Q2),0,X2*24/Q2)</f>
+        <f t="shared" ref="Y2:Y49" si="1">SUM(U2:X2)</f>
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>2143.33</v>
+        <f t="shared" ref="Z2:Z49" si="2">IF(ISERROR(Y2*24/R2),0,Y2*24/R2)</f>
+        <v>0</v>
       </c>
       <c r="AA2">
         <v>2143.33</v>
       </c>
       <c r="AB2">
+        <v>2143.33</v>
+      </c>
+      <c r="AC2">
         <v>0.45</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
       <c r="AE2">
         <v>0</v>
       </c>
@@ -1276,46 +1282,49 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <f t="shared" ref="AH2:AH49" si="3">SUM(AB2:AG2)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:AI49" si="3">SUM(AC2:AH2)</f>
         <v>0.65</v>
       </c>
-      <c r="AI2">
-        <f t="shared" ref="AI2:AI49" si="4">IF(ISERROR(AH2*24/Q2),0,AH2*24/Q2)</f>
-        <v>0</v>
-      </c>
       <c r="AJ2">
-        <f>331.95+AH2</f>
+        <f t="shared" ref="AJ2:AJ49" si="4">IF(ISERROR(AI2*24/R2),0,AI2*24/R2)</f>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f>331.95+AI2</f>
         <v>332.59999999999997</v>
       </c>
-      <c r="AK2">
+      <c r="AL2">
         <v>331.95</v>
       </c>
-      <c r="AL2" s="12">
+      <c r="AM2" s="12">
         <v>8</v>
       </c>
-      <c r="AM2" s="12">
+      <c r="AN2" s="12">
         <v>20.7</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AO2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO2" s="12">
+      <c r="AP2" s="12">
         <v>79</v>
       </c>
-      <c r="AP2" s="12">
+      <c r="AQ2" s="12">
         <v>27.1</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>55</v>
       </c>
-      <c r="AS2">
+      <c r="AT2">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D3">
         <v>2025</v>
       </c>
@@ -1335,67 +1344,67 @@
         <v>84</v>
       </c>
       <c r="J3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" t="s">
         <v>40</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1.3</v>
-      </c>
-      <c r="L3" t="s">
-        <v>55</v>
       </c>
       <c r="M3" t="s">
         <v>55</v>
       </c>
       <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
         <v>48</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>85</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q49" si="5">IFERROR((I3 - I2)*24,0)</f>
+      <c r="R3">
+        <f t="shared" ref="R3:R49" si="5">IFERROR((I3 - I2)*24,0)</f>
         <v>1.3000000000465661</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <f t="shared" si="0"/>
         <v>1.6923076922470739</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>51</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>1.75</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>0.35</v>
       </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
       <c r="W3">
         <v>0</v>
       </c>
       <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
         <f t="shared" si="1"/>
         <v>2.1</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <f t="shared" si="2"/>
         <v>38.769230767842053</v>
       </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
       <c r="AA3">
-        <f t="shared" ref="AA3:AA49" si="6">AA2-X3+Z3</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" ref="AB3:AB49" si="6">AB2-Y3+AA3</f>
         <v>2141.23</v>
       </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
       <c r="AC3">
         <v>0</v>
       </c>
@@ -1412,46 +1421,49 @@
         <v>0</v>
       </c>
       <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI3">
+      <c r="AJ3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
       <c r="AK3">
-        <f t="shared" ref="AK3:AK49" si="7">AK2-AH3+AJ3</f>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" ref="AL3:AL49" si="7">AL2-AI3+AK3</f>
         <v>331.95</v>
       </c>
-      <c r="AL3" s="12">
+      <c r="AM3" s="12">
         <v>8</v>
       </c>
-      <c r="AM3" s="12">
+      <c r="AN3" s="12">
         <v>20.7</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AO3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO3" s="12">
+      <c r="AP3" s="12">
         <v>79</v>
       </c>
-      <c r="AP3" s="12">
+      <c r="AQ3" s="12">
         <v>27.1</v>
       </c>
-      <c r="AQ3" s="12" t="s">
+      <c r="AR3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>44</v>
       </c>
-      <c r="AS3">
+      <c r="AT3">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D4">
         <v>2025</v>
       </c>
@@ -1471,67 +1483,67 @@
         <v>86</v>
       </c>
       <c r="J4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
       </c>
       <c r="M4" t="s">
         <v>55</v>
       </c>
       <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
         <v>48</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>85</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>313</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <f t="shared" si="0"/>
         <v>13.041666666666666</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>87</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>35.5</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>7.2</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
       <c r="W4">
         <v>0</v>
       </c>
       <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
         <f t="shared" si="1"/>
         <v>42.7</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <f t="shared" si="2"/>
         <v>42.70000000000001</v>
       </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
       <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
         <f t="shared" si="6"/>
         <v>2098.5300000000002</v>
       </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
       <c r="AC4">
         <v>0</v>
       </c>
@@ -1548,46 +1560,49 @@
         <v>0</v>
       </c>
       <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI4">
+      <c r="AJ4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
       <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL4">
+      <c r="AM4">
         <v>8</v>
       </c>
-      <c r="AM4">
+      <c r="AN4">
         <v>9.3000000000000007</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>42</v>
       </c>
-      <c r="AO4">
+      <c r="AP4">
         <v>84</v>
       </c>
-      <c r="AP4">
+      <c r="AQ4">
         <v>11.4</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>45</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>44</v>
       </c>
-      <c r="AS4">
+      <c r="AT4">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D5">
         <v>2025</v>
       </c>
@@ -1607,67 +1622,67 @@
         <v>88</v>
       </c>
       <c r="J5" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" t="s">
         <v>40</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>55</v>
       </c>
       <c r="M5" t="s">
         <v>55</v>
       </c>
       <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
         <v>48</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>85</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>366</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <f t="shared" si="0"/>
         <v>15.25</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>62</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>38.75</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>7.48</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
         <v>0</v>
       </c>
       <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <f t="shared" si="1"/>
         <v>46.230000000000004</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <f t="shared" si="2"/>
         <v>46.23</v>
       </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
       <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
         <f t="shared" si="6"/>
         <v>2052.3000000000002</v>
       </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
       <c r="AC5">
         <v>0</v>
       </c>
@@ -1684,46 +1699,49 @@
         <v>0</v>
       </c>
       <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI5">
+      <c r="AJ5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
       <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL5">
+      <c r="AM5">
         <v>10</v>
       </c>
-      <c r="AM5">
+      <c r="AN5">
         <v>58.9</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>42</v>
       </c>
-      <c r="AO5">
+      <c r="AP5">
         <v>89</v>
       </c>
-      <c r="AP5">
+      <c r="AQ5">
         <v>24</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AR5" t="s">
         <v>45</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>44</v>
       </c>
-      <c r="AS5">
+      <c r="AT5">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D6">
         <v>2025</v>
       </c>
@@ -1743,67 +1761,67 @@
         <v>89</v>
       </c>
       <c r="J6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K6" t="s">
         <v>40</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
       </c>
       <c r="M6" t="s">
         <v>55</v>
       </c>
       <c r="N6" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" t="s">
         <v>48</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>85</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>386</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <f t="shared" si="0"/>
         <v>16.083333333333332</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>50</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>41.85</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>5.15</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
       <c r="W6">
         <v>0</v>
       </c>
       <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
       <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
         <f t="shared" si="6"/>
         <v>2005.3000000000002</v>
       </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
       <c r="AC6">
         <v>0</v>
       </c>
@@ -1820,46 +1838,49 @@
         <v>0</v>
       </c>
       <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI6">
+      <c r="AJ6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
       <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL6">
+      <c r="AM6">
         <v>13</v>
       </c>
-      <c r="AM6">
+      <c r="AN6">
         <v>39.1</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>42</v>
       </c>
-      <c r="AO6">
+      <c r="AP6">
         <v>95</v>
       </c>
-      <c r="AP6">
+      <c r="AQ6">
         <v>19.7</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>45</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>44</v>
       </c>
-      <c r="AS6">
+      <c r="AT6">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D7">
         <v>2025</v>
       </c>
@@ -1879,67 +1900,67 @@
         <v>90</v>
       </c>
       <c r="J7" t="s">
+        <v>121</v>
+      </c>
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>24</v>
-      </c>
-      <c r="L7" t="s">
-        <v>55</v>
       </c>
       <c r="M7" t="s">
         <v>55</v>
       </c>
       <c r="N7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" t="s">
         <v>48</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>85</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>368</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>66</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>42.75</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>3.9</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
       <c r="W7">
         <v>0</v>
       </c>
       <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
         <f t="shared" si="1"/>
         <v>46.65</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <f t="shared" si="2"/>
         <v>46.65</v>
       </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
       <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
         <f t="shared" si="6"/>
         <v>1958.65</v>
       </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
       <c r="AC7">
         <v>0</v>
       </c>
@@ -1956,46 +1977,49 @@
         <v>0</v>
       </c>
       <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI7">
+      <c r="AJ7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
       <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL7">
+      <c r="AM7">
         <v>16</v>
       </c>
-      <c r="AM7">
+      <c r="AN7">
         <v>11.9</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>42</v>
       </c>
-      <c r="AO7">
+      <c r="AP7">
         <v>101</v>
       </c>
-      <c r="AP7">
+      <c r="AQ7">
         <v>3.4</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AR7" t="s">
         <v>45</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>44</v>
       </c>
-      <c r="AS7">
+      <c r="AT7">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D8">
         <v>2025</v>
       </c>
@@ -2015,67 +2039,67 @@
         <v>91</v>
       </c>
       <c r="J8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" t="s">
         <v>40</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>24</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
       </c>
       <c r="M8" t="s">
         <v>55</v>
       </c>
       <c r="N8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" t="s">
         <v>48</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>85</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>375</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <f t="shared" si="0"/>
         <v>15.625</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>58</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>42.75</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>4</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
       <c r="W8">
         <v>0</v>
       </c>
       <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
         <f t="shared" si="1"/>
         <v>46.75</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <f t="shared" si="2"/>
         <v>46.75</v>
       </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
       <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
         <f t="shared" si="6"/>
         <v>1911.9</v>
       </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
       <c r="AC8">
         <v>0</v>
       </c>
@@ -2092,46 +2116,49 @@
         <v>0</v>
       </c>
       <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI8">
+      <c r="AJ8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
       <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL8">
+      <c r="AM8">
         <v>19</v>
       </c>
-      <c r="AM8">
+      <c r="AN8">
         <v>4.3</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>42</v>
       </c>
-      <c r="AO8">
+      <c r="AP8">
         <v>106</v>
       </c>
-      <c r="AP8">
+      <c r="AQ8">
         <v>48.4</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AR8" t="s">
         <v>45</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AS8" t="s">
         <v>44</v>
       </c>
-      <c r="AS8">
+      <c r="AT8">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D9">
         <v>2025</v>
       </c>
@@ -2151,67 +2178,67 @@
         <v>92</v>
       </c>
       <c r="J9" t="s">
+        <v>121</v>
+      </c>
+      <c r="K9" t="s">
         <v>40</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
       </c>
       <c r="M9" t="s">
         <v>55</v>
       </c>
       <c r="N9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" t="s">
         <v>48</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>85</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>369</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <f t="shared" si="0"/>
         <v>15.375</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>51</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>43.35</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>3.8</v>
       </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
       <c r="W9">
         <v>0</v>
       </c>
       <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
         <f t="shared" si="1"/>
         <v>47.15</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <f t="shared" si="2"/>
         <v>47.15</v>
       </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
       <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
         <f t="shared" si="6"/>
         <v>1864.75</v>
       </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
       <c r="AC9">
         <v>0</v>
       </c>
@@ -2228,46 +2255,49 @@
         <v>0</v>
       </c>
       <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
       <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL9">
+      <c r="AM9">
         <v>22</v>
       </c>
-      <c r="AM9">
+      <c r="AN9">
         <v>5</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AO9" t="s">
         <v>42</v>
       </c>
-      <c r="AO9">
+      <c r="AP9">
         <v>112</v>
       </c>
-      <c r="AP9">
+      <c r="AQ9">
         <v>29.8</v>
       </c>
-      <c r="AQ9" t="s">
+      <c r="AR9" t="s">
         <v>45</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AS9" t="s">
         <v>44</v>
       </c>
-      <c r="AS9">
+      <c r="AT9">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D10">
         <v>2025</v>
       </c>
@@ -2287,67 +2317,67 @@
         <v>93</v>
       </c>
       <c r="J10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K10" t="s">
         <v>40</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>25</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
       </c>
       <c r="M10" t="s">
         <v>55</v>
       </c>
       <c r="N10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" t="s">
         <v>48</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>85</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>357</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <f t="shared" si="0"/>
         <v>14.875</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>54</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>45.85</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>3.9</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
       <c r="W10">
         <v>0</v>
       </c>
       <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
         <f t="shared" si="1"/>
         <v>49.75</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <f t="shared" si="2"/>
         <v>49.75</v>
       </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
       <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
         <f t="shared" si="6"/>
         <v>1815</v>
       </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
       <c r="AC10">
         <v>0</v>
       </c>
@@ -2364,46 +2394,49 @@
         <v>0</v>
       </c>
       <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI10">
+      <c r="AJ10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
       <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL10">
+      <c r="AM10">
         <v>25</v>
       </c>
-      <c r="AM10">
+      <c r="AN10">
         <v>0.2</v>
       </c>
-      <c r="AN10" t="s">
+      <c r="AO10" t="s">
         <v>42</v>
       </c>
-      <c r="AO10">
+      <c r="AP10">
         <v>118</v>
       </c>
-      <c r="AP10">
+      <c r="AQ10">
         <v>40</v>
       </c>
-      <c r="AQ10" t="s">
+      <c r="AR10" t="s">
         <v>45</v>
       </c>
-      <c r="AR10" t="s">
+      <c r="AS10" t="s">
         <v>44</v>
       </c>
-      <c r="AS10">
+      <c r="AT10">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D11">
         <v>2025</v>
       </c>
@@ -2423,67 +2456,67 @@
         <v>94</v>
       </c>
       <c r="J11" t="s">
+        <v>121</v>
+      </c>
+      <c r="K11" t="s">
         <v>40</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>55</v>
       </c>
       <c r="M11" t="s">
         <v>55</v>
       </c>
       <c r="N11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" t="s">
         <v>48</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>85</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>375</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <f t="shared" si="0"/>
         <v>15.625</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>54</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>43.25</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>3.35</v>
       </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
       <c r="W11">
         <v>0</v>
       </c>
       <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
         <f t="shared" si="1"/>
         <v>46.6</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <f t="shared" si="2"/>
         <v>46.6</v>
       </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
       <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
         <f t="shared" si="6"/>
         <v>1768.4</v>
       </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
       <c r="AC11">
         <v>0</v>
       </c>
@@ -2500,46 +2533,49 @@
         <v>0</v>
       </c>
       <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
       <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL11">
+      <c r="AM11">
         <v>27</v>
       </c>
-      <c r="AM11">
+      <c r="AN11">
         <v>36.4</v>
       </c>
-      <c r="AN11" t="s">
+      <c r="AO11" t="s">
         <v>42</v>
       </c>
-      <c r="AO11">
+      <c r="AP11">
         <v>124</v>
       </c>
-      <c r="AP11">
+      <c r="AQ11">
         <v>56.6</v>
       </c>
-      <c r="AQ11" t="s">
+      <c r="AR11" t="s">
         <v>45</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AS11" t="s">
         <v>44</v>
       </c>
-      <c r="AS11">
+      <c r="AT11">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D12">
         <v>2025</v>
       </c>
@@ -2559,67 +2595,67 @@
         <v>95</v>
       </c>
       <c r="J12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" t="s">
         <v>40</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>55</v>
       </c>
       <c r="M12" t="s">
         <v>55</v>
       </c>
       <c r="N12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" t="s">
         <v>48</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>85</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>377</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <f t="shared" si="0"/>
         <v>15.708333333333334</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>66</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>45.4</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>3.55</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
       <c r="W12">
         <v>0</v>
       </c>
       <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
         <f t="shared" si="1"/>
         <v>48.949999999999996</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <f t="shared" si="2"/>
         <v>48.949999999999996</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
       <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
         <f t="shared" si="6"/>
         <v>1719.45</v>
       </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
       <c r="AC12">
         <v>0</v>
       </c>
@@ -2636,46 +2672,49 @@
         <v>0</v>
       </c>
       <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
       <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL12">
+      <c r="AM12">
         <v>29</v>
       </c>
-      <c r="AM12">
+      <c r="AN12">
         <v>56.4</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AO12" t="s">
         <v>42</v>
       </c>
-      <c r="AO12">
+      <c r="AP12">
         <v>131</v>
       </c>
-      <c r="AP12">
+      <c r="AQ12">
         <v>38</v>
       </c>
-      <c r="AQ12" t="s">
+      <c r="AR12" t="s">
         <v>45</v>
       </c>
-      <c r="AR12" t="s">
+      <c r="AS12" t="s">
         <v>44</v>
       </c>
-      <c r="AS12">
+      <c r="AT12">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D13">
         <v>2025</v>
       </c>
@@ -2695,67 +2734,67 @@
         <v>96</v>
       </c>
       <c r="J13" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" t="s">
         <v>40</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>55</v>
       </c>
       <c r="M13" t="s">
         <v>55</v>
       </c>
       <c r="N13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" t="s">
         <v>48</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>85</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>363</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <f t="shared" si="0"/>
         <v>15.125</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>54</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>43.65</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>3.55</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
       <c r="W13">
         <v>0</v>
       </c>
       <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
         <f t="shared" si="1"/>
         <v>47.199999999999996</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <f t="shared" si="2"/>
         <v>47.199999999999996</v>
       </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
       <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
         <f t="shared" si="6"/>
         <v>1672.25</v>
       </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
       <c r="AC13">
         <v>0</v>
       </c>
@@ -2772,46 +2811,49 @@
         <v>0</v>
       </c>
       <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
       <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL13">
+      <c r="AM13">
         <v>29</v>
       </c>
-      <c r="AM13">
+      <c r="AN13">
         <v>13</v>
       </c>
-      <c r="AN13" t="s">
+      <c r="AO13" t="s">
         <v>42</v>
       </c>
-      <c r="AO13">
+      <c r="AP13">
         <v>138</v>
       </c>
-      <c r="AP13">
+      <c r="AQ13">
         <v>18.399999999999999</v>
       </c>
-      <c r="AQ13" t="s">
+      <c r="AR13" t="s">
         <v>45</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AS13" t="s">
         <v>44</v>
       </c>
-      <c r="AS13">
+      <c r="AT13">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D14">
         <v>2025</v>
       </c>
@@ -2831,67 +2873,67 @@
         <v>97</v>
       </c>
       <c r="J14" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" t="s">
         <v>40</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>25</v>
-      </c>
-      <c r="L14" t="s">
-        <v>55</v>
       </c>
       <c r="M14" t="s">
         <v>55</v>
       </c>
       <c r="N14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" t="s">
         <v>48</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>85</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>389</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <f t="shared" si="0"/>
         <v>16.208333333333332</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>59</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>43.55</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>3.7</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
         <f t="shared" si="1"/>
         <v>47.25</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <f t="shared" si="2"/>
         <v>47.25</v>
       </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
       <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
         <f t="shared" si="6"/>
         <v>1625</v>
       </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
       <c r="AC14">
         <v>0</v>
       </c>
@@ -2908,46 +2950,49 @@
         <v>0</v>
       </c>
       <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
       <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL14">
+      <c r="AM14">
         <v>30</v>
       </c>
-      <c r="AM14">
+      <c r="AN14">
         <v>8.6999999999999993</v>
       </c>
-      <c r="AN14" t="s">
+      <c r="AO14" t="s">
         <v>42</v>
       </c>
-      <c r="AO14">
+      <c r="AP14">
         <v>145</v>
       </c>
-      <c r="AP14">
+      <c r="AQ14">
         <v>34.9</v>
       </c>
-      <c r="AQ14" t="s">
+      <c r="AR14" t="s">
         <v>45</v>
       </c>
-      <c r="AR14" t="s">
+      <c r="AS14" t="s">
         <v>44</v>
       </c>
-      <c r="AS14">
+      <c r="AT14">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D15">
         <v>2025</v>
       </c>
@@ -2967,67 +3012,67 @@
         <v>98</v>
       </c>
       <c r="J15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K15" t="s">
         <v>40</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>25</v>
-      </c>
-      <c r="L15" t="s">
-        <v>55</v>
       </c>
       <c r="M15" t="s">
         <v>55</v>
       </c>
       <c r="N15" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" t="s">
         <v>48</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>99</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>325</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <f t="shared" si="0"/>
         <v>13.541666666666666</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>100</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>42.3</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>3.6</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
         <f t="shared" si="1"/>
         <v>45.9</v>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <f t="shared" si="2"/>
         <v>45.9</v>
       </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
       <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
         <f t="shared" si="6"/>
         <v>1579.1</v>
       </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
       <c r="AC15">
         <v>0</v>
       </c>
@@ -3044,46 +3089,49 @@
         <v>0</v>
       </c>
       <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
       <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL15">
+      <c r="AM15">
         <v>32</v>
       </c>
-      <c r="AM15">
+      <c r="AN15">
         <v>56.6</v>
       </c>
-      <c r="AN15" t="s">
+      <c r="AO15" t="s">
         <v>42</v>
       </c>
-      <c r="AO15">
+      <c r="AP15">
         <v>150</v>
       </c>
-      <c r="AP15">
+      <c r="AQ15">
         <v>55.4</v>
       </c>
-      <c r="AQ15" t="s">
+      <c r="AR15" t="s">
         <v>45</v>
       </c>
-      <c r="AR15" t="s">
+      <c r="AS15" t="s">
         <v>44</v>
       </c>
-      <c r="AS15">
+      <c r="AT15">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
       <c r="D16">
         <v>2025</v>
       </c>
@@ -3103,67 +3151,67 @@
         <v>101</v>
       </c>
       <c r="J16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" t="s">
         <v>40</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>25</v>
-      </c>
-      <c r="L16" t="s">
-        <v>55</v>
       </c>
       <c r="M16" t="s">
         <v>55</v>
       </c>
       <c r="N16" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" t="s">
         <v>48</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>102</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>329</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <f t="shared" si="0"/>
         <v>13.708333333333334</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>72</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>45.35</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>3.6</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
       <c r="W16">
         <v>0</v>
       </c>
       <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <f t="shared" si="1"/>
         <v>48.95</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <f t="shared" si="2"/>
         <v>48.95000000000001</v>
       </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
       <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
         <f t="shared" si="6"/>
         <v>1530.1499999999999</v>
       </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
       <c r="AC16">
         <v>0</v>
       </c>
@@ -3180,46 +3228,49 @@
         <v>0</v>
       </c>
       <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI16">
+      <c r="AJ16">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
       <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL16">
+      <c r="AM16">
         <v>35</v>
       </c>
-      <c r="AM16">
+      <c r="AN16">
         <v>59.7</v>
       </c>
-      <c r="AN16" t="s">
+      <c r="AO16" t="s">
         <v>42</v>
       </c>
-      <c r="AO16">
+      <c r="AP16">
         <v>156</v>
       </c>
-      <c r="AP16">
+      <c r="AQ16">
         <v>23.6</v>
       </c>
-      <c r="AQ16" t="s">
+      <c r="AR16" t="s">
         <v>45</v>
       </c>
-      <c r="AR16" t="s">
+      <c r="AS16" t="s">
         <v>44</v>
       </c>
-      <c r="AS16">
+      <c r="AT16">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D17">
         <v>2025</v>
       </c>
@@ -3239,67 +3290,67 @@
         <v>103</v>
       </c>
       <c r="J17" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" t="s">
         <v>40</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>24</v>
-      </c>
-      <c r="L17" t="s">
-        <v>55</v>
       </c>
       <c r="M17" t="s">
         <v>55</v>
       </c>
       <c r="N17" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" t="s">
         <v>48</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>85</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>306</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <f t="shared" si="0"/>
         <v>12.75</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>61</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>43.7</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>7.45</v>
       </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
         <f t="shared" si="1"/>
         <v>51.150000000000006</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <f t="shared" si="2"/>
         <v>51.150000000000006</v>
       </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
       <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
         <f t="shared" si="6"/>
         <v>1478.9999999999998</v>
       </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -3316,46 +3367,49 @@
         <v>0</v>
       </c>
       <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
       <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL17">
+      <c r="AM17">
         <v>37</v>
       </c>
-      <c r="AM17">
+      <c r="AN17">
         <v>36.799999999999997</v>
       </c>
-      <c r="AN17" t="s">
+      <c r="AO17" t="s">
         <v>42</v>
       </c>
-      <c r="AO17">
+      <c r="AP17">
         <v>162</v>
       </c>
-      <c r="AP17">
+      <c r="AQ17">
         <v>8.5</v>
       </c>
-      <c r="AQ17" t="s">
+      <c r="AR17" t="s">
         <v>45</v>
       </c>
-      <c r="AR17" t="s">
+      <c r="AS17" t="s">
         <v>44</v>
       </c>
-      <c r="AS17">
+      <c r="AT17">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D18">
         <v>2025</v>
       </c>
@@ -3375,67 +3429,67 @@
         <v>104</v>
       </c>
       <c r="J18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" t="s">
         <v>40</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>25</v>
-      </c>
-      <c r="L18" t="s">
-        <v>55</v>
       </c>
       <c r="M18" t="s">
         <v>55</v>
       </c>
       <c r="N18" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" t="s">
         <v>48</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>105</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>311</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f t="shared" si="0"/>
         <v>12.958333333333334</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>67</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>44.6</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>7.9</v>
       </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
       <c r="W18">
         <v>0</v>
       </c>
       <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <f t="shared" si="2"/>
         <v>52.5</v>
       </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
       <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
         <f t="shared" si="6"/>
         <v>1426.4999999999998</v>
       </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
       <c r="AC18">
         <v>0</v>
       </c>
@@ -3452,46 +3506,49 @@
         <v>0</v>
       </c>
       <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
       <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL18">
+      <c r="AM18">
         <v>36</v>
       </c>
-      <c r="AM18">
+      <c r="AN18">
         <v>42.4</v>
       </c>
-      <c r="AN18" t="s">
+      <c r="AO18" t="s">
         <v>42</v>
       </c>
-      <c r="AO18">
+      <c r="AP18">
         <v>168</v>
       </c>
-      <c r="AP18">
+      <c r="AQ18">
         <v>17.399999999999999</v>
       </c>
-      <c r="AQ18" t="s">
+      <c r="AR18" t="s">
         <v>45</v>
       </c>
-      <c r="AR18" t="s">
+      <c r="AS18" t="s">
         <v>44</v>
       </c>
-      <c r="AS18">
+      <c r="AT18">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D19">
         <v>2025</v>
       </c>
@@ -3511,67 +3568,67 @@
         <v>106</v>
       </c>
       <c r="J19" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" t="s">
         <v>40</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>24</v>
-      </c>
-      <c r="L19" t="s">
-        <v>55</v>
       </c>
       <c r="M19" t="s">
         <v>55</v>
       </c>
       <c r="N19" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" t="s">
         <v>48</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>105</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>283</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f t="shared" si="0"/>
         <v>11.791666666666666</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>69</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>41.8</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>7.8</v>
       </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
       <c r="W19">
         <v>0</v>
       </c>
       <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
         <f t="shared" si="1"/>
         <v>49.599999999999994</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <f t="shared" si="2"/>
         <v>49.599999999999994</v>
       </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
       <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
         <f t="shared" si="6"/>
         <v>1376.8999999999999</v>
       </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
       <c r="AC19">
         <v>0</v>
       </c>
@@ -3588,46 +3645,49 @@
         <v>0</v>
       </c>
       <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
       <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL19">
+      <c r="AM19">
         <v>34</v>
       </c>
-      <c r="AM19">
+      <c r="AN19">
         <v>31.8</v>
       </c>
-      <c r="AN19" t="s">
+      <c r="AO19" t="s">
         <v>42</v>
       </c>
-      <c r="AO19">
+      <c r="AP19">
         <v>173</v>
       </c>
-      <c r="AP19">
+      <c r="AQ19">
         <v>10.4</v>
       </c>
-      <c r="AQ19" t="s">
+      <c r="AR19" t="s">
         <v>45</v>
       </c>
-      <c r="AR19" t="s">
+      <c r="AS19" t="s">
         <v>44</v>
       </c>
-      <c r="AS19">
+      <c r="AT19">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D20">
         <v>2025</v>
       </c>
@@ -3647,67 +3707,67 @@
         <v>107</v>
       </c>
       <c r="J20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K20" t="s">
         <v>40</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>24</v>
-      </c>
-      <c r="L20" t="s">
-        <v>55</v>
       </c>
       <c r="M20" t="s">
         <v>55</v>
       </c>
       <c r="N20" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" t="s">
         <v>48</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>105</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>354</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f t="shared" si="0"/>
         <v>14.75</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>64</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>42.4</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>4.75</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
       <c r="W20">
         <v>0</v>
       </c>
       <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
         <f t="shared" si="1"/>
         <v>47.15</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <f t="shared" si="2"/>
         <v>47.15</v>
       </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
       <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
         <f t="shared" si="6"/>
         <v>1329.7499999999998</v>
       </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
       <c r="AC20">
         <v>0</v>
       </c>
@@ -3724,46 +3784,49 @@
         <v>0</v>
       </c>
       <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
       <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL20">
+      <c r="AM20">
         <v>30</v>
       </c>
-      <c r="AM20">
+      <c r="AN20">
         <v>11.2</v>
       </c>
-      <c r="AN20" t="s">
+      <c r="AO20" t="s">
         <v>42</v>
       </c>
-      <c r="AO20">
+      <c r="AP20">
         <v>177</v>
       </c>
-      <c r="AP20">
+      <c r="AQ20">
         <v>13.5</v>
       </c>
-      <c r="AQ20" t="s">
+      <c r="AR20" t="s">
         <v>45</v>
       </c>
-      <c r="AR20" t="s">
+      <c r="AS20" t="s">
         <v>44</v>
       </c>
-      <c r="AS20">
+      <c r="AT20">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D21">
         <v>2025</v>
       </c>
@@ -3783,67 +3846,67 @@
         <v>108</v>
       </c>
       <c r="J21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" t="s">
         <v>40</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>25</v>
-      </c>
-      <c r="L21" t="s">
-        <v>55</v>
       </c>
       <c r="M21" t="s">
         <v>55</v>
       </c>
       <c r="N21" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" t="s">
         <v>48</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>105</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>368</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>65</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>44.6</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>3.45</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
       <c r="W21">
         <v>0</v>
       </c>
       <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
         <f t="shared" si="1"/>
         <v>48.050000000000004</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <f t="shared" si="2"/>
         <v>48.050000000000004</v>
       </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
       <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
         <f t="shared" si="6"/>
         <v>1281.6999999999998</v>
       </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
       <c r="AC21">
         <v>0</v>
       </c>
@@ -3860,46 +3923,49 @@
         <v>0</v>
       </c>
       <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
       <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL21">
+      <c r="AM21">
         <v>28</v>
       </c>
-      <c r="AM21">
+      <c r="AN21">
         <v>16.5</v>
       </c>
-      <c r="AN21" t="s">
+      <c r="AO21" t="s">
         <v>42</v>
       </c>
-      <c r="AO21">
+      <c r="AP21">
         <v>176</v>
       </c>
-      <c r="AP21">
+      <c r="AQ21">
         <v>11.6</v>
       </c>
-      <c r="AQ21" t="s">
+      <c r="AR21" t="s">
         <v>43</v>
       </c>
-      <c r="AR21" t="s">
+      <c r="AS21" t="s">
         <v>44</v>
       </c>
-      <c r="AS21">
+      <c r="AT21">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D22">
         <v>2025</v>
       </c>
@@ -3919,67 +3985,67 @@
         <v>109</v>
       </c>
       <c r="J22" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" t="s">
         <v>40</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>24</v>
-      </c>
-      <c r="L22" t="s">
-        <v>55</v>
       </c>
       <c r="M22" t="s">
         <v>55</v>
       </c>
       <c r="N22" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" t="s">
         <v>48</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>105</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>364</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f t="shared" si="0"/>
         <v>15.166666666666666</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>49</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>41.4</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>3.3</v>
       </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
       <c r="W22">
         <v>0</v>
       </c>
       <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
         <f t="shared" si="1"/>
         <v>44.699999999999996</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
         <f t="shared" si="2"/>
         <v>44.699999999999996</v>
       </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
       <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
         <f t="shared" si="6"/>
         <v>1236.9999999999998</v>
       </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
       <c r="AC22">
         <v>0</v>
       </c>
@@ -3996,46 +4062,49 @@
         <v>0</v>
       </c>
       <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
       <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL22">
+      <c r="AM22">
         <v>26</v>
       </c>
-      <c r="AM22">
+      <c r="AN22">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AN22" t="s">
+      <c r="AO22" t="s">
         <v>42</v>
       </c>
-      <c r="AO22">
+      <c r="AP22">
         <v>169</v>
       </c>
-      <c r="AP22">
+      <c r="AQ22">
         <v>52.5</v>
       </c>
-      <c r="AQ22" t="s">
+      <c r="AR22" t="s">
         <v>43</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AS22" t="s">
         <v>44</v>
       </c>
-      <c r="AS22">
+      <c r="AT22">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D23">
         <v>2025</v>
       </c>
@@ -4055,67 +4124,67 @@
         <v>110</v>
       </c>
       <c r="J23" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" t="s">
         <v>40</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>24</v>
-      </c>
-      <c r="L23" t="s">
-        <v>55</v>
       </c>
       <c r="M23" t="s">
         <v>55</v>
       </c>
       <c r="N23" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" t="s">
         <v>48</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>111</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>384</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>65</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>44.4</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>3.2</v>
       </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
       <c r="W23">
         <v>0</v>
       </c>
       <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
         <f t="shared" si="1"/>
         <v>47.6</v>
       </c>
-      <c r="Y23">
+      <c r="Z23">
         <f t="shared" si="2"/>
         <v>23.8</v>
       </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
       <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
         <f t="shared" si="6"/>
         <v>1189.3999999999999</v>
       </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
       <c r="AC23">
         <v>0</v>
       </c>
@@ -4132,46 +4201,49 @@
         <v>0</v>
       </c>
       <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
       <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL23">
+      <c r="AM23">
         <v>25</v>
       </c>
-      <c r="AM23">
+      <c r="AN23">
         <v>46.4</v>
       </c>
-      <c r="AN23" t="s">
+      <c r="AO23" t="s">
         <v>42</v>
       </c>
-      <c r="AO23">
+      <c r="AP23">
         <v>162</v>
       </c>
-      <c r="AP23">
+      <c r="AQ23">
         <v>50.9</v>
       </c>
-      <c r="AQ23" t="s">
+      <c r="AR23" t="s">
         <v>43</v>
       </c>
-      <c r="AR23" t="s">
+      <c r="AS23" t="s">
         <v>44</v>
       </c>
-      <c r="AS23">
+      <c r="AT23">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D24">
         <v>2025</v>
       </c>
@@ -4191,67 +4263,67 @@
         <v>112</v>
       </c>
       <c r="J24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24" t="s">
         <v>40</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>24</v>
-      </c>
-      <c r="L24" t="s">
-        <v>55</v>
       </c>
       <c r="M24" t="s">
         <v>55</v>
       </c>
       <c r="N24" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" t="s">
         <v>48</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>113</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>311</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <f t="shared" si="0"/>
         <v>12.958333333333334</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>59</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>42.05</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>3.25</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
       <c r="W24">
         <v>0</v>
       </c>
       <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
         <f t="shared" si="1"/>
         <v>45.3</v>
       </c>
-      <c r="Y24">
+      <c r="Z24">
         <f t="shared" si="2"/>
         <v>45.29999999999999</v>
       </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
       <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
         <f t="shared" si="6"/>
         <v>1144.0999999999999</v>
       </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
       <c r="AC24">
         <v>0</v>
       </c>
@@ -4268,46 +4340,49 @@
         <v>0</v>
       </c>
       <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
       <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL24">
+      <c r="AM24">
         <v>26</v>
       </c>
-      <c r="AM24">
+      <c r="AN24">
         <v>9.1</v>
       </c>
-      <c r="AN24" t="s">
+      <c r="AO24" t="s">
         <v>42</v>
       </c>
-      <c r="AO24">
+      <c r="AP24">
         <v>157</v>
       </c>
-      <c r="AP24">
+      <c r="AQ24">
         <v>13.9</v>
       </c>
-      <c r="AQ24" t="s">
+      <c r="AR24" t="s">
         <v>43</v>
       </c>
-      <c r="AR24" t="s">
+      <c r="AS24" t="s">
         <v>44</v>
       </c>
-      <c r="AS24">
+      <c r="AT24">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D25">
         <v>2025</v>
       </c>
@@ -4327,67 +4402,67 @@
         <v>114</v>
       </c>
       <c r="J25" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" t="s">
         <v>40</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>25</v>
-      </c>
-      <c r="L25" t="s">
-        <v>55</v>
       </c>
       <c r="M25" t="s">
         <v>55</v>
       </c>
       <c r="N25" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" t="s">
         <v>48</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>105</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>386</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <f t="shared" si="0"/>
         <v>16.083333333333332</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>73</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>45.35</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>3.5</v>
       </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
       <c r="W25">
         <v>0</v>
       </c>
       <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
         <f t="shared" si="1"/>
         <v>48.85</v>
       </c>
-      <c r="Y25">
+      <c r="Z25">
         <f t="shared" si="2"/>
         <v>48.85</v>
       </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
       <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
         <f t="shared" si="6"/>
         <v>1095.25</v>
       </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
       <c r="AC25">
         <v>0</v>
       </c>
@@ -4404,46 +4479,49 @@
         <v>0</v>
       </c>
       <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
       <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL25">
+      <c r="AM25">
         <v>27</v>
       </c>
-      <c r="AM25">
+      <c r="AN25">
         <v>39.299999999999997</v>
       </c>
-      <c r="AN25" t="s">
+      <c r="AO25" t="s">
         <v>42</v>
       </c>
-      <c r="AO25">
+      <c r="AP25">
         <v>150</v>
       </c>
-      <c r="AP25">
+      <c r="AQ25">
         <v>17.3</v>
       </c>
-      <c r="AQ25" t="s">
+      <c r="AR25" t="s">
         <v>43</v>
       </c>
-      <c r="AR25" t="s">
+      <c r="AS25" t="s">
         <v>44</v>
       </c>
-      <c r="AS25">
+      <c r="AT25">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D26">
         <v>2025</v>
       </c>
@@ -4463,67 +4541,67 @@
         <v>115</v>
       </c>
       <c r="J26" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" t="s">
         <v>40</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>25</v>
-      </c>
-      <c r="L26" t="s">
-        <v>55</v>
       </c>
       <c r="M26" t="s">
         <v>55</v>
       </c>
       <c r="N26" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" t="s">
         <v>48</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>105</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>388</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <f t="shared" si="0"/>
         <v>16.166666666666668</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>65</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>45.45</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>3.25</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
       <c r="W26">
         <v>0</v>
       </c>
       <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
         <f t="shared" si="1"/>
         <v>48.7</v>
       </c>
-      <c r="Y26">
+      <c r="Z26">
         <f t="shared" si="2"/>
         <v>48.70000000000001</v>
       </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
       <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
         <f t="shared" si="6"/>
         <v>1046.55</v>
       </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
       <c r="AC26">
         <v>0</v>
       </c>
@@ -4540,46 +4618,49 @@
         <v>0</v>
       </c>
       <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
       <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL26">
+      <c r="AM26">
         <v>28</v>
       </c>
-      <c r="AM26">
+      <c r="AN26">
         <v>53.7</v>
       </c>
-      <c r="AN26" t="s">
+      <c r="AO26" t="s">
         <v>42</v>
       </c>
-      <c r="AO26">
+      <c r="AP26">
         <v>143</v>
       </c>
-      <c r="AP26">
+      <c r="AQ26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AQ26" t="s">
+      <c r="AR26" t="s">
         <v>43</v>
       </c>
-      <c r="AR26" t="s">
+      <c r="AS26" t="s">
         <v>44</v>
       </c>
-      <c r="AS26">
+      <c r="AT26">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D27">
         <v>2025</v>
       </c>
@@ -4599,67 +4680,67 @@
         <v>116</v>
       </c>
       <c r="J27" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
         <v>40</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>55</v>
       </c>
       <c r="M27" t="s">
         <v>55</v>
       </c>
       <c r="N27" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" t="s">
         <v>48</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>105</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>378</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <f t="shared" si="0"/>
         <v>15.75</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>49</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>41.75</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>3.1</v>
       </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
       <c r="W27">
         <v>0</v>
       </c>
       <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
         <f t="shared" si="1"/>
         <v>44.85</v>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <f t="shared" si="2"/>
         <v>44.85</v>
       </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
       <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
         <f t="shared" si="6"/>
         <v>1001.6999999999999</v>
       </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
       <c r="AC27">
         <v>0</v>
       </c>
@@ -4676,46 +4757,49 @@
         <v>0</v>
       </c>
       <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
       <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL27">
+      <c r="AM27">
         <v>30</v>
       </c>
-      <c r="AM27">
+      <c r="AN27">
         <v>3.6</v>
       </c>
-      <c r="AN27" t="s">
+      <c r="AO27" t="s">
         <v>42</v>
       </c>
-      <c r="AO27">
+      <c r="AP27">
         <v>136</v>
       </c>
-      <c r="AP27">
+      <c r="AQ27">
         <v>7.6</v>
       </c>
-      <c r="AQ27" t="s">
+      <c r="AR27" t="s">
         <v>43</v>
       </c>
-      <c r="AR27" t="s">
+      <c r="AS27" t="s">
         <v>44</v>
       </c>
-      <c r="AS27">
+      <c r="AT27">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D28">
         <v>2025</v>
       </c>
@@ -4735,67 +4819,67 @@
         <v>117</v>
       </c>
       <c r="J28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28" t="s">
         <v>40</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>25</v>
-      </c>
-      <c r="L28" t="s">
-        <v>55</v>
       </c>
       <c r="M28" t="s">
         <v>55</v>
       </c>
       <c r="N28" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" t="s">
         <v>48</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>105</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>384</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>65</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>43.15</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>3.3</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
       <c r="W28">
         <v>0</v>
       </c>
       <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
         <f t="shared" si="1"/>
         <v>46.449999999999996</v>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <f t="shared" si="2"/>
         <v>46.449999999999996</v>
       </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
       <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
         <f t="shared" si="6"/>
         <v>955.24999999999989</v>
       </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
       <c r="AC28">
         <v>0</v>
       </c>
@@ -4812,46 +4896,49 @@
         <v>0</v>
       </c>
       <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
       <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL28">
+      <c r="AM28">
         <v>31</v>
       </c>
-      <c r="AM28">
+      <c r="AN28">
         <v>14.3</v>
       </c>
-      <c r="AN28" t="s">
+      <c r="AO28" t="s">
         <v>42</v>
       </c>
-      <c r="AO28">
+      <c r="AP28">
         <v>128</v>
       </c>
-      <c r="AP28">
+      <c r="AQ28">
         <v>55.1</v>
       </c>
-      <c r="AQ28" t="s">
+      <c r="AR28" t="s">
         <v>43</v>
       </c>
-      <c r="AR28" t="s">
+      <c r="AS28" t="s">
         <v>44</v>
       </c>
-      <c r="AS28">
+      <c r="AT28">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D29">
         <v>2025</v>
       </c>
@@ -4871,67 +4958,67 @@
         <v>118</v>
       </c>
       <c r="J29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" t="s">
         <v>40</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>24</v>
-      </c>
-      <c r="L29" t="s">
-        <v>55</v>
       </c>
       <c r="M29" t="s">
         <v>55</v>
       </c>
       <c r="N29" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" t="s">
         <v>48</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>105</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>379</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <f t="shared" si="0"/>
         <v>15.791666666666666</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>49</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>42.2</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>6.85</v>
       </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
       <c r="W29">
         <v>0</v>
       </c>
       <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
         <f t="shared" si="1"/>
         <v>49.050000000000004</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <f t="shared" si="2"/>
         <v>49.050000000000004</v>
       </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
       <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
         <f t="shared" si="6"/>
         <v>906.19999999999993</v>
       </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
       <c r="AC29">
         <v>0</v>
       </c>
@@ -4948,46 +5035,49 @@
         <v>0</v>
       </c>
       <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
       <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL29" s="9">
+      <c r="AM29" s="9">
         <v>35</v>
       </c>
-      <c r="AM29" s="9">
+      <c r="AN29" s="9">
         <v>43.6</v>
       </c>
-      <c r="AN29" s="9" t="s">
+      <c r="AO29" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AO29" s="9">
+      <c r="AP29" s="9">
         <v>124</v>
       </c>
-      <c r="AP29" s="9">
+      <c r="AQ29" s="9">
         <v>16.899999999999999</v>
       </c>
-      <c r="AQ29" s="9" t="s">
+      <c r="AR29" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AR29" t="s">
+      <c r="AS29" t="s">
         <v>44</v>
       </c>
-      <c r="AS29">
+      <c r="AT29">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D30">
         <v>2025</v>
       </c>
@@ -5007,67 +5097,67 @@
         <v>119</v>
       </c>
       <c r="J30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K30" t="s">
         <v>120</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>7.2</v>
-      </c>
-      <c r="L30" t="s">
-        <v>55</v>
       </c>
       <c r="M30" t="s">
         <v>55</v>
       </c>
       <c r="N30" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" t="s">
         <v>48</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>77</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>113</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <f t="shared" si="5"/>
         <v>7.1999999998952262</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <f t="shared" si="0"/>
         <v>15.694444444672829</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>50</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>13.6</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>1.65</v>
       </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
       <c r="W30">
         <v>0</v>
       </c>
       <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
         <f t="shared" si="1"/>
         <v>15.25</v>
       </c>
-      <c r="Y30">
+      <c r="Z30">
         <f t="shared" si="2"/>
         <v>50.833333334073053</v>
       </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
       <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
       <c r="AC30">
         <v>0</v>
       </c>
@@ -5084,46 +5174,49 @@
         <v>0</v>
       </c>
       <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30">
+      <c r="AJ30">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
       <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
         <f t="shared" si="7"/>
         <v>331.95</v>
       </c>
-      <c r="AL30" s="9">
+      <c r="AM30" s="9">
         <v>33</v>
       </c>
-      <c r="AM30" s="9">
+      <c r="AN30" s="9">
         <v>43.3</v>
       </c>
-      <c r="AN30" s="9" t="s">
+      <c r="AO30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AO30" s="9">
+      <c r="AP30" s="9">
         <v>124</v>
       </c>
-      <c r="AP30" s="9">
+      <c r="AQ30" s="9">
         <v>10.9</v>
       </c>
-      <c r="AQ30" s="9" t="s">
+      <c r="AR30" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AR30" t="s">
+      <c r="AS30" t="s">
         <v>52</v>
       </c>
-      <c r="AS30">
+      <c r="AT30">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D31">
         <v>2025</v>
       </c>
@@ -5143,40 +5236,40 @@
         <v>121</v>
       </c>
       <c r="J31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" t="s">
         <v>122</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>12.5</v>
       </c>
-      <c r="L31" t="s">
+      <c r="M31" t="s">
         <v>55</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>52</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>48</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>123</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>250</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <f t="shared" si="5"/>
         <v>12.500000000058208</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <f t="shared" si="0"/>
         <v>19.999999999906869</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
         <v>49</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
         <v>0</v>
       </c>
@@ -5187,29 +5280,29 @@
         <v>0</v>
       </c>
       <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y31">
+      <c r="Z31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
       <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <v>20.350000000000001</v>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <v>1.45</v>
       </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
       <c r="AE31">
         <v>0</v>
       </c>
@@ -5220,46 +5313,49 @@
         <v>0</v>
       </c>
       <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
         <f t="shared" si="3"/>
         <v>21.8</v>
       </c>
-      <c r="AI31">
+      <c r="AJ31">
         <f t="shared" si="4"/>
         <v>41.8559999998051</v>
       </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
       <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
         <f t="shared" si="7"/>
         <v>310.14999999999998</v>
       </c>
-      <c r="AL31" s="9">
+      <c r="AM31" s="9">
         <v>37</v>
       </c>
-      <c r="AM31" s="9">
+      <c r="AN31" s="9">
         <v>43.1</v>
       </c>
-      <c r="AN31" s="9" t="s">
+      <c r="AO31" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AO31" s="9">
+      <c r="AP31" s="9">
         <v>124</v>
       </c>
-      <c r="AP31" s="9">
+      <c r="AQ31" s="9">
         <v>8.4</v>
       </c>
-      <c r="AQ31" s="9" t="s">
+      <c r="AR31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AR31" t="s">
+      <c r="AS31" t="s">
         <v>55</v>
       </c>
-      <c r="AS31">
+      <c r="AT31">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D32">
         <v>2025</v>
       </c>
@@ -5279,40 +5375,40 @@
         <v>124</v>
       </c>
       <c r="J32" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" t="s">
         <v>40</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>4.3</v>
       </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
         <v>52</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>53</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>41</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>125</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
       <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
         <f t="shared" si="5"/>
         <v>4.3000000000465661</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S32" t="s">
+      <c r="T32" t="s">
         <v>41</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
         <v>0</v>
       </c>
@@ -5323,32 +5419,32 @@
         <v>0</v>
       </c>
       <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y32">
+      <c r="Z32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
       <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <v>0.05</v>
       </c>
-      <c r="AC32">
+      <c r="AD32">
         <v>0.5</v>
       </c>
-      <c r="AD32">
+      <c r="AE32">
         <v>0.3</v>
       </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
       <c r="AF32">
         <v>0</v>
       </c>
@@ -5356,46 +5452,49 @@
         <v>0</v>
       </c>
       <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
         <f t="shared" si="3"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="AI32">
+      <c r="AJ32">
         <f t="shared" si="4"/>
         <v>4.7441860464602517</v>
       </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
       <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
         <f t="shared" si="7"/>
         <v>309.29999999999995</v>
       </c>
-      <c r="AL32" s="10">
+      <c r="AM32" s="10">
         <v>37</v>
       </c>
-      <c r="AM32" s="10">
+      <c r="AN32" s="10">
         <v>43.1</v>
       </c>
-      <c r="AN32" s="10" t="s">
+      <c r="AO32" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AO32" s="10">
+      <c r="AP32" s="10">
         <v>120</v>
       </c>
-      <c r="AP32" s="10">
+      <c r="AQ32" s="10">
         <v>8.4</v>
       </c>
-      <c r="AQ32" s="10" t="s">
+      <c r="AR32" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AR32" t="s">
+      <c r="AS32" t="s">
         <v>44</v>
       </c>
-      <c r="AS32">
+      <c r="AT32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D33">
         <v>2025</v>
       </c>
@@ -5415,40 +5514,40 @@
         <v>126</v>
       </c>
       <c r="J33" t="s">
+        <v>121</v>
+      </c>
+      <c r="K33" t="s">
         <v>127</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>3</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>53</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>63</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>41</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>128</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>6</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
         <v>49</v>
       </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
       <c r="U33">
         <v>0</v>
       </c>
@@ -5459,32 +5558,32 @@
         <v>0</v>
       </c>
       <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y33">
+      <c r="Z33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
       <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>1.2</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>0.75</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>0.1</v>
       </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
       <c r="AF33">
         <v>0</v>
       </c>
@@ -5492,46 +5591,49 @@
         <v>0</v>
       </c>
       <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
         <f t="shared" si="3"/>
         <v>2.0499999999999998</v>
       </c>
-      <c r="AI33">
+      <c r="AJ33">
         <f t="shared" si="4"/>
         <v>16.399999999999999</v>
       </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
       <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
         <f t="shared" si="7"/>
         <v>307.24999999999994</v>
       </c>
-      <c r="AL33" s="10">
+      <c r="AM33" s="10">
         <v>37</v>
       </c>
-      <c r="AM33" s="10">
+      <c r="AN33" s="10">
         <v>38.1</v>
       </c>
-      <c r="AN33" s="10" t="s">
+      <c r="AO33" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AO33" s="10">
+      <c r="AP33" s="10">
         <v>120</v>
       </c>
-      <c r="AP33" s="10">
+      <c r="AQ33" s="10">
         <v>14.4</v>
       </c>
-      <c r="AQ33" s="10" t="s">
+      <c r="AR33" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AR33" t="s">
+      <c r="AS33" t="s">
         <v>53</v>
       </c>
-      <c r="AS33">
+      <c r="AT33">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D34">
         <v>2025</v>
       </c>
@@ -5551,40 +5653,40 @@
         <v>129</v>
       </c>
       <c r="J34" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" t="s">
         <v>40</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>21</v>
-      </c>
-      <c r="L34" t="s">
-        <v>63</v>
       </c>
       <c r="M34" t="s">
         <v>63</v>
       </c>
       <c r="N34" t="s">
+        <v>63</v>
+      </c>
+      <c r="O34" t="s">
         <v>41</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>130</v>
       </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
       <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>41</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
       <c r="U34">
         <v>0</v>
       </c>
@@ -5595,32 +5697,32 @@
         <v>0</v>
       </c>
       <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y34">
+      <c r="Z34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
       <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
       <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
         <v>3.9</v>
       </c>
-      <c r="AD34">
+      <c r="AE34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
       <c r="AF34">
         <v>0</v>
       </c>
@@ -5628,46 +5730,49 @@
         <v>0</v>
       </c>
       <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="AI34">
+      <c r="AJ34">
         <f t="shared" si="4"/>
         <v>5.7142857142857144</v>
       </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
       <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
         <f t="shared" si="7"/>
         <v>302.24999999999994</v>
       </c>
-      <c r="AL34" s="11">
+      <c r="AM34" s="11">
         <v>37</v>
       </c>
-      <c r="AM34" s="11">
+      <c r="AN34" s="11">
         <v>39.4</v>
       </c>
-      <c r="AN34" s="11" t="s">
+      <c r="AO34" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AO34" s="11">
+      <c r="AP34" s="11">
         <v>120</v>
       </c>
-      <c r="AP34" s="11">
+      <c r="AQ34" s="11">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ34" s="11" t="s">
+      <c r="AR34" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AR34" t="s">
+      <c r="AS34" t="s">
         <v>44</v>
       </c>
-      <c r="AS34">
+      <c r="AT34">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D35">
         <v>2025</v>
       </c>
@@ -5687,40 +5792,40 @@
         <v>131</v>
       </c>
       <c r="J35" t="s">
+        <v>121</v>
+      </c>
+      <c r="K35" t="s">
         <v>79</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>22</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>63</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>53</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>41</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>57</v>
       </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
       <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
         <f t="shared" si="5"/>
         <v>21.999999999941792</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S35" t="s">
+      <c r="T35" t="s">
         <v>41</v>
       </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
       <c r="U35">
         <v>0</v>
       </c>
@@ -5731,32 +5836,32 @@
         <v>0</v>
       </c>
       <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y35">
+      <c r="Z35">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
       <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
       <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
         <v>4.55</v>
       </c>
-      <c r="AD35">
+      <c r="AE35">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
       <c r="AF35">
         <v>0</v>
       </c>
@@ -5764,46 +5869,49 @@
         <v>0</v>
       </c>
       <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
         <f t="shared" si="3"/>
         <v>5.6999999999999993</v>
       </c>
-      <c r="AI35">
+      <c r="AJ35">
         <f t="shared" si="4"/>
         <v>6.2181818181982695</v>
       </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
       <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
         <f t="shared" si="7"/>
         <v>296.54999999999995</v>
       </c>
-      <c r="AL35" s="11">
+      <c r="AM35" s="11">
         <v>37</v>
       </c>
-      <c r="AM35" s="11">
+      <c r="AN35" s="11">
         <v>39.4</v>
       </c>
-      <c r="AN35" s="11" t="s">
+      <c r="AO35" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AO35" s="11">
+      <c r="AP35" s="11">
         <v>120</v>
       </c>
-      <c r="AP35" s="11">
+      <c r="AQ35" s="11">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ35" s="11" t="s">
+      <c r="AR35" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AR35" t="s">
+      <c r="AS35" t="s">
         <v>63</v>
       </c>
-      <c r="AS35">
+      <c r="AT35">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D36">
         <v>2025</v>
       </c>
@@ -5823,40 +5931,40 @@
         <v>132</v>
       </c>
       <c r="J36" t="s">
+        <v>121</v>
+      </c>
+      <c r="K36" t="s">
         <v>40</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>2</v>
-      </c>
-      <c r="L36" t="s">
-        <v>53</v>
       </c>
       <c r="M36" t="s">
         <v>53</v>
       </c>
       <c r="N36" t="s">
+        <v>53</v>
+      </c>
+      <c r="O36" t="s">
         <v>41</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>71</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
       <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
         <f t="shared" si="5"/>
         <v>2.0000000000582077</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S36" t="s">
+      <c r="T36" t="s">
         <v>68</v>
       </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
       <c r="U36">
         <v>0</v>
       </c>
@@ -5867,32 +5975,32 @@
         <v>0</v>
       </c>
       <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y36">
+      <c r="Z36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
       <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
       <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
         <v>0.25</v>
       </c>
-      <c r="AD36">
+      <c r="AE36">
         <v>0.05</v>
       </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
       <c r="AF36">
         <v>0</v>
       </c>
@@ -5900,46 +6008,49 @@
         <v>0</v>
       </c>
       <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
-      <c r="AI36">
+      <c r="AJ36">
         <f t="shared" si="4"/>
         <v>3.5999999998952257</v>
       </c>
-      <c r="AJ36">
-        <v>0</v>
-      </c>
       <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
         <f t="shared" si="7"/>
         <v>296.24999999999994</v>
       </c>
-      <c r="AL36" s="13">
+      <c r="AM36" s="13">
         <v>37</v>
       </c>
-      <c r="AM36" s="13">
+      <c r="AN36" s="13">
         <v>39.4</v>
       </c>
-      <c r="AN36" s="13" t="s">
+      <c r="AO36" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AO36" s="13">
+      <c r="AP36" s="13">
         <v>120</v>
       </c>
-      <c r="AP36" s="13">
+      <c r="AQ36" s="13">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ36" s="13" t="s">
+      <c r="AR36" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AR36" t="s">
+      <c r="AS36" t="s">
         <v>44</v>
       </c>
-      <c r="AS36">
+      <c r="AT36">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D37">
         <v>2025</v>
       </c>
@@ -5959,40 +6070,40 @@
         <v>133</v>
       </c>
       <c r="J37" t="s">
+        <v>121</v>
+      </c>
+      <c r="K37" t="s">
         <v>80</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>1.1000000000000001</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>53</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>47</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>41</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>134</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>8</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <f t="shared" si="5"/>
         <v>1.0999999999185093</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <f t="shared" si="0"/>
         <v>7.2727272732660539</v>
       </c>
-      <c r="S37" t="s">
+      <c r="T37" t="s">
         <v>68</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
       <c r="U37">
         <v>0</v>
       </c>
@@ -6003,29 +6114,29 @@
         <v>0</v>
       </c>
       <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y37">
+      <c r="Z37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
       <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <v>0.8</v>
       </c>
-      <c r="AC37">
+      <c r="AD37">
         <v>0.25</v>
       </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
       <c r="AE37">
         <v>0</v>
       </c>
@@ -6036,46 +6147,49 @@
         <v>0</v>
       </c>
       <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
         <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
-      <c r="AI37">
+      <c r="AJ37">
         <f t="shared" si="4"/>
         <v>22.909090910788073</v>
       </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
       <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
         <f t="shared" si="7"/>
         <v>295.19999999999993</v>
       </c>
-      <c r="AL37" s="13">
+      <c r="AM37" s="13">
         <v>37</v>
       </c>
-      <c r="AM37" s="13">
+      <c r="AN37" s="13">
         <v>39.4</v>
       </c>
-      <c r="AN37" s="13" t="s">
+      <c r="AO37" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AO37" s="13">
+      <c r="AP37" s="13">
         <v>120</v>
       </c>
-      <c r="AP37" s="13">
+      <c r="AQ37" s="13">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ37" s="13" t="s">
+      <c r="AR37" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AR37" t="s">
+      <c r="AS37" t="s">
         <v>53</v>
       </c>
-      <c r="AS37">
+      <c r="AT37">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D38">
         <v>2025</v>
       </c>
@@ -6095,40 +6209,40 @@
         <v>137</v>
       </c>
       <c r="J38" t="s">
+        <v>144</v>
+      </c>
+      <c r="K38" t="s">
         <v>138</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>10.5</v>
-      </c>
-      <c r="L38" t="s">
-        <v>47</v>
       </c>
       <c r="M38" t="s">
         <v>47</v>
       </c>
       <c r="N38" t="s">
+        <v>47</v>
+      </c>
+      <c r="O38" t="s">
         <v>48</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>76</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>163</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <f t="shared" si="0"/>
         <v>15.523809523809524</v>
       </c>
-      <c r="S38" t="s">
+      <c r="T38" t="s">
         <v>68</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
       <c r="U38">
         <v>0</v>
       </c>
@@ -6139,29 +6253,29 @@
         <v>0</v>
       </c>
       <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y38">
+      <c r="Z38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
       <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
         <f t="shared" si="6"/>
         <v>890.94999999999993</v>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <v>15.25</v>
       </c>
-      <c r="AC38">
+      <c r="AD38">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AD38">
-        <v>0</v>
-      </c>
       <c r="AE38">
         <v>0</v>
       </c>
@@ -6172,46 +6286,49 @@
         <v>0</v>
       </c>
       <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
         <f t="shared" si="3"/>
         <v>16.399999999999999</v>
       </c>
-      <c r="AI38">
+      <c r="AJ38">
         <f t="shared" si="4"/>
         <v>37.48571428571428</v>
       </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
       <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
         <f t="shared" si="7"/>
         <v>278.79999999999995</v>
       </c>
-      <c r="AL38" s="13">
+      <c r="AM38" s="13">
         <v>36</v>
       </c>
-      <c r="AM38" s="13">
+      <c r="AN38" s="13">
         <v>41.4</v>
       </c>
-      <c r="AN38" s="13" t="s">
+      <c r="AO38" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AO38" s="13">
+      <c r="AP38" s="13">
         <v>120</v>
       </c>
-      <c r="AP38" s="13">
+      <c r="AQ38" s="13">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ38" s="13" t="s">
+      <c r="AR38" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AR38" t="s">
+      <c r="AS38" t="s">
         <v>47</v>
       </c>
-      <c r="AS38">
+      <c r="AT38">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D39">
         <v>2025</v>
       </c>
@@ -6231,67 +6348,67 @@
         <v>139</v>
       </c>
       <c r="J39" t="s">
+        <v>144</v>
+      </c>
+      <c r="K39" t="s">
         <v>40</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>12.4</v>
-      </c>
-      <c r="L39" t="s">
-        <v>47</v>
       </c>
       <c r="M39" t="s">
         <v>47</v>
       </c>
       <c r="N39" t="s">
+        <v>47</v>
+      </c>
+      <c r="O39" t="s">
         <v>48</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>140</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>198</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <f t="shared" si="5"/>
         <v>12.400000000081491</v>
       </c>
-      <c r="R39">
+      <c r="S39">
         <f t="shared" si="0"/>
         <v>15.967741935378934</v>
       </c>
-      <c r="S39" t="s">
+      <c r="T39" t="s">
         <v>75</v>
       </c>
-      <c r="T39">
+      <c r="U39">
         <v>17</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>1.5</v>
       </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
       <c r="W39">
         <v>0</v>
       </c>
       <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
         <f t="shared" si="1"/>
         <v>18.5</v>
       </c>
-      <c r="Y39">
+      <c r="Z39">
         <f t="shared" si="2"/>
         <v>35.806451612667914</v>
       </c>
-      <c r="Z39">
-        <v>0</v>
-      </c>
       <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
         <f t="shared" si="6"/>
         <v>872.44999999999993</v>
       </c>
-      <c r="AB39">
-        <v>0</v>
-      </c>
       <c r="AC39">
         <v>0</v>
       </c>
@@ -6308,46 +6425,49 @@
         <v>0</v>
       </c>
       <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI39">
+      <c r="AJ39">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ39">
-        <v>0</v>
-      </c>
       <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
         <f t="shared" si="7"/>
         <v>278.79999999999995</v>
       </c>
-      <c r="AL39" s="12">
+      <c r="AM39" s="12">
         <v>35</v>
       </c>
-      <c r="AM39" s="12">
+      <c r="AN39" s="12">
         <v>41.7</v>
       </c>
-      <c r="AN39" s="12" t="s">
+      <c r="AO39" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO39" s="12">
+      <c r="AP39" s="12">
         <v>125</v>
       </c>
-      <c r="AP39" s="12">
+      <c r="AQ39" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="AQ39" s="12" t="s">
+      <c r="AR39" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AR39" t="s">
+      <c r="AS39" t="s">
         <v>44</v>
       </c>
-      <c r="AS39">
+      <c r="AT39">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D40">
         <v>2025</v>
       </c>
@@ -6367,67 +6487,67 @@
         <v>141</v>
       </c>
       <c r="J40" t="s">
+        <v>144</v>
+      </c>
+      <c r="K40" t="s">
         <v>142</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>11.5</v>
-      </c>
-      <c r="L40" t="s">
-        <v>47</v>
       </c>
       <c r="M40" t="s">
         <v>47</v>
       </c>
       <c r="N40" t="s">
+        <v>47</v>
+      </c>
+      <c r="O40" t="s">
         <v>48</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>143</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>185</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <f t="shared" si="5"/>
         <v>11.499999999941792</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <f t="shared" si="0"/>
         <v>16.086956521820554</v>
       </c>
-      <c r="S40" t="s">
+      <c r="T40" t="s">
         <v>75</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>19.350000000000001</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>1.65</v>
       </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
       <c r="W40">
         <v>0</v>
       </c>
       <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="Y40">
+      <c r="Z40">
         <f t="shared" si="2"/>
         <v>43.826086956743566</v>
       </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
       <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
         <f t="shared" si="6"/>
         <v>851.44999999999993</v>
       </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
       <c r="AC40">
         <v>0</v>
       </c>
@@ -6444,46 +6564,49 @@
         <v>0</v>
       </c>
       <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI40">
+      <c r="AJ40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
       <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
         <f t="shared" si="7"/>
         <v>278.79999999999995</v>
       </c>
-      <c r="AL40" s="12">
+      <c r="AM40" s="12">
         <v>34</v>
       </c>
-      <c r="AM40" s="12">
+      <c r="AN40" s="12">
         <v>41.7</v>
       </c>
-      <c r="AN40" s="12" t="s">
+      <c r="AO40" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO40" s="12">
+      <c r="AP40" s="12">
         <v>125</v>
       </c>
-      <c r="AP40" s="12">
+      <c r="AQ40" s="12">
         <v>34.1</v>
       </c>
-      <c r="AQ40" s="12" t="s">
+      <c r="AR40" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AR40" t="s">
+      <c r="AS40" t="s">
         <v>47</v>
       </c>
-      <c r="AS40">
+      <c r="AT40">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="41" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D41">
         <v>2025</v>
       </c>
@@ -6503,40 +6626,40 @@
         <v>144</v>
       </c>
       <c r="J41" t="s">
+        <v>144</v>
+      </c>
+      <c r="K41" t="s">
         <v>56</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>1.5</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>47</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>52</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>48</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>145</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>23</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
-      <c r="S41" t="s">
+      <c r="T41" t="s">
         <v>75</v>
       </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
       <c r="U41">
         <v>0</v>
       </c>
@@ -6547,29 +6670,29 @@
         <v>0</v>
       </c>
       <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y41">
+      <c r="Z41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
       <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
         <f t="shared" si="6"/>
         <v>851.44999999999993</v>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <v>1.75</v>
       </c>
-      <c r="AC41">
+      <c r="AD41">
         <v>0.2</v>
       </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
       <c r="AE41">
         <v>0</v>
       </c>
@@ -6580,46 +6703,49 @@
         <v>0</v>
       </c>
       <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
         <f t="shared" si="3"/>
         <v>1.95</v>
       </c>
-      <c r="AI41">
+      <c r="AJ41">
         <f t="shared" si="4"/>
         <v>31.2</v>
       </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
       <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
         <f t="shared" si="7"/>
         <v>276.84999999999997</v>
       </c>
-      <c r="AL41" s="12">
+      <c r="AM41" s="12">
         <v>33</v>
       </c>
-      <c r="AM41" s="12">
+      <c r="AN41" s="12">
         <v>42.7</v>
       </c>
-      <c r="AN41" s="12" t="s">
+      <c r="AO41" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO41" s="12">
+      <c r="AP41" s="12">
         <v>125</v>
       </c>
-      <c r="AP41" s="12">
+      <c r="AQ41" s="12">
         <v>40.1</v>
       </c>
-      <c r="AQ41" s="12" t="s">
+      <c r="AR41" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AR41" t="s">
+      <c r="AS41" t="s">
         <v>47</v>
       </c>
-      <c r="AS41">
+      <c r="AT41">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D42">
         <v>2025</v>
       </c>
@@ -6639,40 +6765,40 @@
         <v>146</v>
       </c>
       <c r="J42" t="s">
+        <v>144</v>
+      </c>
+      <c r="K42" t="s">
         <v>147</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>7.5</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>52</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>47</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>41</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>148</v>
       </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
       <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
         <f t="shared" si="5"/>
         <v>7.5</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S42" t="s">
+      <c r="T42" t="s">
         <v>41</v>
       </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
       <c r="U42">
         <v>0</v>
       </c>
@@ -6683,32 +6809,32 @@
         <v>0</v>
       </c>
       <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y42">
+      <c r="Z42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>750</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <f t="shared" si="6"/>
         <v>1601.4499999999998</v>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AC42">
+      <c r="AD42">
         <v>0.85</v>
       </c>
-      <c r="AD42">
+      <c r="AE42">
         <v>0.42</v>
       </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
       <c r="AF42">
         <v>0</v>
       </c>
@@ -6716,46 +6842,49 @@
         <v>0</v>
       </c>
       <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
         <f t="shared" si="3"/>
         <v>1.5499999999999998</v>
       </c>
-      <c r="AI42">
+      <c r="AJ42">
         <f t="shared" si="4"/>
         <v>4.9599999999999991</v>
       </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
       <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
         <f t="shared" si="7"/>
         <v>275.29999999999995</v>
       </c>
-      <c r="AL42" s="12">
+      <c r="AM42" s="12">
         <v>33</v>
       </c>
-      <c r="AM42" s="12">
+      <c r="AN42" s="12">
         <v>42.7</v>
       </c>
-      <c r="AN42" s="12" t="s">
+      <c r="AO42" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO42" s="12">
+      <c r="AP42" s="12">
         <v>125</v>
       </c>
-      <c r="AP42" s="12">
+      <c r="AQ42" s="12">
         <v>40.1</v>
       </c>
-      <c r="AQ42" s="12" t="s">
+      <c r="AR42" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AR42" t="s">
+      <c r="AS42" t="s">
         <v>52</v>
       </c>
-      <c r="AS42">
+      <c r="AT42">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="43" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D43">
         <v>2025</v>
       </c>
@@ -6775,40 +6904,40 @@
         <v>149</v>
       </c>
       <c r="J43" t="s">
+        <v>157</v>
+      </c>
+      <c r="K43" t="s">
         <v>150</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.5</v>
-      </c>
-      <c r="L43" t="s">
-        <v>47</v>
       </c>
       <c r="M43" t="s">
         <v>47</v>
       </c>
       <c r="N43" t="s">
+        <v>47</v>
+      </c>
+      <c r="O43" t="s">
         <v>48</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>76</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>5</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <f t="shared" si="5"/>
         <v>0.50000000005820766</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <f t="shared" si="0"/>
         <v>9.9999999988358468</v>
       </c>
-      <c r="S43" t="s">
+      <c r="T43" t="s">
         <v>49</v>
       </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
       <c r="U43">
         <v>0</v>
       </c>
@@ -6819,29 +6948,29 @@
         <v>0</v>
       </c>
       <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
       <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
         <f t="shared" si="6"/>
         <v>1601.4499999999998</v>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <v>0.35</v>
       </c>
-      <c r="AC43">
+      <c r="AD43">
         <v>0.1</v>
       </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
       <c r="AE43">
         <v>0</v>
       </c>
@@ -6852,46 +6981,49 @@
         <v>0</v>
       </c>
       <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
         <f t="shared" si="3"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="AI43">
+      <c r="AJ43">
         <f t="shared" si="4"/>
         <v>21.599999997485426</v>
       </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
       <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL43" s="12">
+      <c r="AM43" s="12">
         <v>33</v>
       </c>
-      <c r="AM43" s="12">
+      <c r="AN43" s="12">
         <v>42.7</v>
       </c>
-      <c r="AN43" s="12" t="s">
+      <c r="AO43" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="AO43" s="12">
+      <c r="AP43" s="12">
         <v>125</v>
       </c>
-      <c r="AP43" s="12">
+      <c r="AQ43" s="12">
         <v>42.1</v>
       </c>
-      <c r="AQ43" s="12" t="s">
+      <c r="AR43" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AR43" t="s">
+      <c r="AS43" t="s">
         <v>47</v>
       </c>
-      <c r="AS43">
+      <c r="AT43">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="44" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D44">
         <v>2025</v>
       </c>
@@ -6911,67 +7043,67 @@
         <v>151</v>
       </c>
       <c r="J44" t="s">
+        <v>157</v>
+      </c>
+      <c r="K44" t="s">
         <v>40</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>3</v>
-      </c>
-      <c r="L44" t="s">
-        <v>47</v>
       </c>
       <c r="M44" t="s">
         <v>47</v>
       </c>
       <c r="N44" t="s">
+        <v>47</v>
+      </c>
+      <c r="O44" t="s">
         <v>48</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>74</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>67</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="R44">
+      <c r="S44">
         <f t="shared" si="0"/>
         <v>22.333333333333332</v>
       </c>
-      <c r="S44" t="s">
+      <c r="T44" t="s">
         <v>49</v>
       </c>
-      <c r="T44">
+      <c r="U44">
         <v>3.45</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <v>0.35</v>
       </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
       <c r="W44">
         <v>0</v>
       </c>
       <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
         <f t="shared" si="1"/>
         <v>3.8000000000000003</v>
       </c>
-      <c r="Y44">
+      <c r="Z44">
         <f t="shared" si="2"/>
         <v>30.400000000000002</v>
       </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
       <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
         <f t="shared" si="6"/>
         <v>1597.6499999999999</v>
       </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
       <c r="AC44">
         <v>0</v>
       </c>
@@ -6988,46 +7120,49 @@
         <v>0</v>
       </c>
       <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI44">
+      <c r="AJ44">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ44">
-        <v>0</v>
-      </c>
       <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL44">
+      <c r="AM44">
         <v>33</v>
       </c>
-      <c r="AM44">
+      <c r="AN44">
         <v>44.1</v>
       </c>
-      <c r="AN44" t="s">
+      <c r="AO44" t="s">
         <v>42</v>
       </c>
-      <c r="AO44">
+      <c r="AP44">
         <v>127</v>
       </c>
-      <c r="AP44">
+      <c r="AQ44">
         <v>53.3</v>
       </c>
-      <c r="AQ44" t="s">
+      <c r="AR44" t="s">
         <v>43</v>
       </c>
-      <c r="AR44" t="s">
+      <c r="AS44" t="s">
         <v>44</v>
       </c>
-      <c r="AS44">
+      <c r="AT44">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="45" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D45">
         <v>2025</v>
       </c>
@@ -7047,67 +7182,67 @@
         <v>152</v>
       </c>
       <c r="J45" t="s">
+        <v>157</v>
+      </c>
+      <c r="K45" t="s">
         <v>40</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>24</v>
-      </c>
-      <c r="L45" t="s">
-        <v>47</v>
       </c>
       <c r="M45" t="s">
         <v>47</v>
       </c>
       <c r="N45" t="s">
+        <v>47</v>
+      </c>
+      <c r="O45" t="s">
         <v>48</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>74</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>380</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <f t="shared" si="0"/>
         <v>15.833333333333334</v>
       </c>
-      <c r="S45" t="s">
+      <c r="T45" t="s">
         <v>68</v>
       </c>
-      <c r="T45">
+      <c r="U45">
         <v>36.700000000000003</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <v>3.35</v>
       </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
       <c r="W45">
         <v>0</v>
       </c>
       <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
         <f t="shared" si="1"/>
         <v>40.050000000000004</v>
       </c>
-      <c r="Y45">
+      <c r="Z45">
         <f t="shared" si="2"/>
         <v>40.050000000000004</v>
       </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
       <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
         <f t="shared" si="6"/>
         <v>1557.6</v>
       </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
       <c r="AC45">
         <v>0</v>
       </c>
@@ -7124,46 +7259,49 @@
         <v>0</v>
       </c>
       <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI45">
+      <c r="AJ45">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ45">
-        <v>0</v>
-      </c>
       <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL45">
+      <c r="AM45">
         <v>30</v>
       </c>
-      <c r="AM45">
+      <c r="AN45">
         <v>53.1</v>
       </c>
-      <c r="AN45" t="s">
+      <c r="AO45" t="s">
         <v>42</v>
       </c>
-      <c r="AO45">
+      <c r="AP45">
         <v>132</v>
       </c>
-      <c r="AP45">
+      <c r="AQ45">
         <v>37.700000000000003</v>
       </c>
-      <c r="AQ45" t="s">
+      <c r="AR45" t="s">
         <v>43</v>
       </c>
-      <c r="AR45" t="s">
+      <c r="AS45" t="s">
         <v>44</v>
       </c>
-      <c r="AS45">
+      <c r="AT45">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D46">
         <v>2025</v>
       </c>
@@ -7183,67 +7321,67 @@
         <v>153</v>
       </c>
       <c r="J46" t="s">
+        <v>157</v>
+      </c>
+      <c r="K46" t="s">
         <v>40</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>24</v>
-      </c>
-      <c r="L46" t="s">
-        <v>47</v>
       </c>
       <c r="M46" t="s">
         <v>47</v>
       </c>
       <c r="N46" t="s">
+        <v>47</v>
+      </c>
+      <c r="O46" t="s">
         <v>48</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>74</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>397</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <f t="shared" si="0"/>
         <v>16.541666666666668</v>
       </c>
-      <c r="S46" t="s">
+      <c r="T46" t="s">
         <v>100</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <v>38.450000000000003</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>5.8</v>
       </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
       <c r="W46">
         <v>0</v>
       </c>
       <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
         <f t="shared" si="1"/>
         <v>44.25</v>
       </c>
-      <c r="Y46">
+      <c r="Z46">
         <f t="shared" si="2"/>
         <v>44.25</v>
       </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
       <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
         <f t="shared" si="6"/>
         <v>1513.35</v>
       </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
       <c r="AC46">
         <v>0</v>
       </c>
@@ -7260,46 +7398,49 @@
         <v>0</v>
       </c>
       <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI46">
+      <c r="AJ46">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ46">
-        <v>0</v>
-      </c>
       <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL46">
+      <c r="AM46">
         <v>30</v>
       </c>
-      <c r="AM46">
+      <c r="AN46">
         <v>42.5</v>
       </c>
-      <c r="AN46" t="s">
+      <c r="AO46" t="s">
         <v>42</v>
       </c>
-      <c r="AO46">
+      <c r="AP46">
         <v>140</v>
       </c>
-      <c r="AP46">
+      <c r="AQ46">
         <v>9.6999999999999993</v>
       </c>
-      <c r="AQ46" t="s">
+      <c r="AR46" t="s">
         <v>43</v>
       </c>
-      <c r="AR46" t="s">
+      <c r="AS46" t="s">
         <v>44</v>
       </c>
-      <c r="AS46">
+      <c r="AT46">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="47" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D47">
         <v>2025</v>
       </c>
@@ -7319,67 +7460,67 @@
         <v>154</v>
       </c>
       <c r="J47" t="s">
+        <v>157</v>
+      </c>
+      <c r="K47" t="s">
         <v>40</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>24</v>
-      </c>
-      <c r="L47" t="s">
-        <v>47</v>
       </c>
       <c r="M47" t="s">
         <v>47</v>
       </c>
       <c r="N47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O47" t="s">
         <v>48</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>74</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>384</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="S47" t="s">
+      <c r="T47" t="s">
         <v>155</v>
       </c>
-      <c r="T47">
+      <c r="U47">
         <v>37.700000000000003</v>
       </c>
-      <c r="U47">
+      <c r="V47">
         <v>3.45</v>
       </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
       <c r="W47">
         <v>0</v>
       </c>
       <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
         <f t="shared" si="1"/>
         <v>41.150000000000006</v>
       </c>
-      <c r="Y47">
+      <c r="Z47">
         <f t="shared" si="2"/>
         <v>41.150000000000006</v>
       </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
       <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
         <f t="shared" si="6"/>
         <v>1472.1999999999998</v>
       </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
       <c r="AC47">
         <v>0</v>
       </c>
@@ -7396,46 +7537,49 @@
         <v>0</v>
       </c>
       <c r="AH47">
+        <v>0</v>
+      </c>
+      <c r="AI47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI47">
+      <c r="AJ47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ47">
-        <v>0</v>
-      </c>
       <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL47">
+      <c r="AM47">
         <v>30</v>
       </c>
-      <c r="AM47">
+      <c r="AN47">
         <v>14.4</v>
       </c>
-      <c r="AN47" t="s">
+      <c r="AO47" t="s">
         <v>42</v>
       </c>
-      <c r="AO47">
+      <c r="AP47">
         <v>147</v>
       </c>
-      <c r="AP47">
+      <c r="AQ47">
         <v>28.4</v>
       </c>
-      <c r="AQ47" t="s">
+      <c r="AR47" t="s">
         <v>43</v>
       </c>
-      <c r="AR47" t="s">
+      <c r="AS47" t="s">
         <v>44</v>
       </c>
-      <c r="AS47">
+      <c r="AT47">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D48">
         <v>2025</v>
       </c>
@@ -7455,67 +7599,67 @@
         <v>156</v>
       </c>
       <c r="J48" t="s">
+        <v>157</v>
+      </c>
+      <c r="K48" t="s">
         <v>40</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>23</v>
-      </c>
-      <c r="L48" t="s">
-        <v>47</v>
       </c>
       <c r="M48" t="s">
         <v>47</v>
       </c>
       <c r="N48" t="s">
+        <v>47</v>
+      </c>
+      <c r="O48" t="s">
         <v>48</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>74</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>369</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <f t="shared" si="0"/>
         <v>15.375</v>
       </c>
-      <c r="S48" t="s">
+      <c r="T48" t="s">
         <v>155</v>
       </c>
-      <c r="T48">
+      <c r="U48">
         <v>37.75</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <v>3.4</v>
       </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
       <c r="W48">
         <v>0</v>
       </c>
       <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
         <f t="shared" si="1"/>
         <v>41.15</v>
       </c>
-      <c r="Y48">
+      <c r="Z48">
         <f t="shared" si="2"/>
         <v>41.15</v>
       </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
       <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
         <f t="shared" si="6"/>
         <v>1431.0499999999997</v>
       </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
       <c r="AC48">
         <v>0</v>
       </c>
@@ -7532,46 +7676,49 @@
         <v>0</v>
       </c>
       <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI48">
+      <c r="AJ48">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
       <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL48">
+      <c r="AM48">
         <v>29</v>
       </c>
-      <c r="AM48">
+      <c r="AN48">
         <v>22.1</v>
       </c>
-      <c r="AN48" t="s">
+      <c r="AO48" t="s">
         <v>42</v>
       </c>
-      <c r="AO48">
+      <c r="AP48">
         <v>154</v>
       </c>
-      <c r="AP48">
+      <c r="AQ48">
         <v>26.8</v>
       </c>
-      <c r="AQ48" t="s">
+      <c r="AR48" t="s">
         <v>43</v>
       </c>
-      <c r="AR48" t="s">
+      <c r="AS48" t="s">
         <v>44</v>
       </c>
-      <c r="AS48">
+      <c r="AT48">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="4:45" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:46" x14ac:dyDescent="0.3">
       <c r="D49">
         <v>2025</v>
       </c>
@@ -7591,67 +7738,67 @@
         <v>157</v>
       </c>
       <c r="J49" t="s">
+        <v>157</v>
+      </c>
+      <c r="K49" t="s">
         <v>40</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>24</v>
-      </c>
-      <c r="L49" t="s">
-        <v>47</v>
       </c>
       <c r="M49" t="s">
         <v>47</v>
       </c>
       <c r="N49" t="s">
+        <v>47</v>
+      </c>
+      <c r="O49" t="s">
         <v>48</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>74</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>382</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <f t="shared" si="0"/>
         <v>15.916666666666666</v>
       </c>
-      <c r="S49" t="s">
+      <c r="T49" t="s">
         <v>60</v>
       </c>
-      <c r="T49">
+      <c r="U49">
         <v>38.1</v>
       </c>
-      <c r="U49">
+      <c r="V49">
         <v>6.25</v>
       </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
       <c r="W49">
         <v>0</v>
       </c>
       <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
         <f t="shared" si="1"/>
         <v>44.35</v>
       </c>
-      <c r="Y49">
+      <c r="Z49">
         <f t="shared" si="2"/>
         <v>44.35</v>
       </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
       <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
         <f t="shared" si="6"/>
         <v>1386.6999999999998</v>
       </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
       <c r="AC49">
         <v>0</v>
       </c>
@@ -7668,42 +7815,45 @@
         <v>0</v>
       </c>
       <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI49">
+      <c r="AJ49">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
       <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
         <f t="shared" si="7"/>
         <v>274.84999999999997</v>
       </c>
-      <c r="AL49">
+      <c r="AM49">
         <v>28</v>
       </c>
-      <c r="AM49">
+      <c r="AN49">
         <v>7.4</v>
       </c>
-      <c r="AN49" t="s">
+      <c r="AO49" t="s">
         <v>42</v>
       </c>
-      <c r="AO49">
+      <c r="AP49">
         <v>161</v>
       </c>
-      <c r="AP49">
+      <c r="AQ49">
         <v>31.2</v>
       </c>
-      <c r="AQ49" t="s">
+      <c r="AR49" t="s">
         <v>43</v>
       </c>
-      <c r="AR49" t="s">
+      <c r="AS49" t="s">
         <v>44</v>
       </c>
-      <c r="AS49">
+      <c r="AT49">
         <v>31</v>
       </c>
     </row>

--- a/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
+++ b/DATA REGISTER ATLATICVICTORY - CARGA DE DATA 2025.xlsx
@@ -1,16 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56F4A80-958D-4207-8F60-189ADC3ED5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E288E17-BB78-4351-8985-B7F8AE0DDB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report register" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -65,9 +76,6 @@
     <t>steamingTime2</t>
   </si>
   <si>
-    <t>SPEED22</t>
-  </si>
-  <si>
     <t>beaufour</t>
   </si>
   <si>
@@ -499,22 +507,25 @@
     <t>TOTAL_IFO</t>
   </si>
   <si>
-    <t>DAILY_COSUMTION_IFO</t>
-  </si>
-  <si>
     <t>ROB_IFO</t>
   </si>
   <si>
     <t>TOTAL_MGO</t>
   </si>
   <si>
-    <t>DAILY_COSUMTION_MGO</t>
-  </si>
-  <si>
     <t>ROB_MGO</t>
   </si>
   <si>
     <t>date_ETA</t>
+  </si>
+  <si>
+    <t>SPEED</t>
+  </si>
+  <si>
+    <t>DAILY_CONSUMPTION_IFO</t>
+  </si>
+  <si>
+    <t>DAILY_CONSUMPTION_MGO</t>
   </si>
 </sst>
 </file>
@@ -1020,12 +1031,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AV49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="4" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
     <col min="7" max="8" width="16" customWidth="1"/>
     <col min="9" max="10" width="24.77734375" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
@@ -1037,7 +1050,9 @@
     <col min="17" max="35" width="13.21875" customWidth="1"/>
     <col min="36" max="36" width="25.109375" customWidth="1"/>
     <col min="37" max="39" width="13.21875" customWidth="1"/>
-    <col min="40" max="48" width="8" customWidth="1"/>
+    <col min="40" max="44" width="8" customWidth="1"/>
+    <col min="45" max="45" width="20.109375" customWidth="1"/>
+    <col min="46" max="48" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1069,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>9</v>
@@ -1081,7 +1096,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>12</v>
@@ -1096,97 +1111,106 @@
         <v>15</v>
       </c>
       <c r="S1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AC1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI1" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL1" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AC1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AI1" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ1" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AL1" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AO1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="AV1" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="D2">
         <v>2025</v>
       </c>
@@ -1197,34 +1221,34 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" t="s">
         <v>81</v>
       </c>
-      <c r="I2" t="s">
-        <v>82</v>
-      </c>
       <c r="J2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2">
         <v>0.9</v>
       </c>
       <c r="M2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1238,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1306,7 +1330,7 @@
         <v>20.7</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP2" s="12">
         <v>79</v>
@@ -1315,16 +1339,31 @@
         <v>27.1</v>
       </c>
       <c r="AR2" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AT2">
         <v>31</v>
       </c>
+      <c r="AU2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3">
         <v>2025</v>
       </c>
@@ -1335,34 +1374,34 @@
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L3">
         <v>1.3</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q3">
         <v>2.2000000000000002</v>
@@ -1376,7 +1415,7 @@
         <v>1.6923076922470739</v>
       </c>
       <c r="T3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U3">
         <v>1.75</v>
@@ -1445,7 +1484,7 @@
         <v>20.7</v>
       </c>
       <c r="AO3" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP3" s="12">
         <v>79</v>
@@ -1454,16 +1493,31 @@
         <v>27.1</v>
       </c>
       <c r="AR3" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT3">
         <v>31</v>
       </c>
+      <c r="AU3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
         <v>2025</v>
       </c>
@@ -1474,37 +1528,37 @@
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L4">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q4">
-        <v>313</v>
+        <v>573</v>
       </c>
       <c r="R4">
         <f t="shared" si="5"/>
@@ -1512,10 +1566,10 @@
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>13.041666666666666</v>
+        <v>23.875</v>
       </c>
       <c r="T4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U4">
         <v>35.5</v>
@@ -1584,7 +1638,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="AO4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP4">
         <v>84</v>
@@ -1593,16 +1647,31 @@
         <v>11.4</v>
       </c>
       <c r="AR4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT4">
         <v>31</v>
       </c>
+      <c r="AU4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5">
         <v>2025</v>
       </c>
@@ -1613,37 +1682,37 @@
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L5">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q5">
-        <v>366</v>
+        <v>574</v>
       </c>
       <c r="R5">
         <f t="shared" si="5"/>
@@ -1651,10 +1720,10 @@
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>15.25</v>
+        <v>23.916666666666668</v>
       </c>
       <c r="T5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U5">
         <v>38.75</v>
@@ -1717,13 +1786,13 @@
         <v>331.95</v>
       </c>
       <c r="AM5">
-        <v>10</v>
+        <v>2333</v>
       </c>
       <c r="AN5">
         <v>58.9</v>
       </c>
       <c r="AO5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP5">
         <v>89</v>
@@ -1732,16 +1801,31 @@
         <v>24</v>
       </c>
       <c r="AR5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT5">
         <v>31</v>
       </c>
+      <c r="AU5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="D6">
         <v>2025</v>
       </c>
@@ -1752,34 +1836,34 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L6">
         <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q6">
         <v>386</v>
@@ -1793,7 +1877,7 @@
         <v>16.083333333333332</v>
       </c>
       <c r="T6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U6">
         <v>41.85</v>
@@ -1862,7 +1946,7 @@
         <v>39.1</v>
       </c>
       <c r="AO6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP6">
         <v>95</v>
@@ -1871,16 +1955,31 @@
         <v>19.7</v>
       </c>
       <c r="AR6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT6">
         <v>31</v>
       </c>
+      <c r="AU6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
       <c r="D7">
         <v>2025</v>
       </c>
@@ -1891,34 +1990,34 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>24</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q7">
         <v>368</v>
@@ -1932,7 +2031,7 @@
         <v>15.333333333333334</v>
       </c>
       <c r="T7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U7">
         <v>42.75</v>
@@ -2001,7 +2100,7 @@
         <v>11.9</v>
       </c>
       <c r="AO7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP7">
         <v>101</v>
@@ -2010,16 +2109,31 @@
         <v>3.4</v>
       </c>
       <c r="AR7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT7">
         <v>31</v>
       </c>
+      <c r="AU7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
       <c r="D8">
         <v>2025</v>
       </c>
@@ -2030,34 +2144,34 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L8">
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q8">
         <v>375</v>
@@ -2071,7 +2185,7 @@
         <v>15.625</v>
       </c>
       <c r="T8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U8">
         <v>42.75</v>
@@ -2140,7 +2254,7 @@
         <v>4.3</v>
       </c>
       <c r="AO8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP8">
         <v>106</v>
@@ -2149,16 +2263,31 @@
         <v>48.4</v>
       </c>
       <c r="AR8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT8">
         <v>31</v>
       </c>
+      <c r="AU8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
       <c r="D9">
         <v>2025</v>
       </c>
@@ -2169,34 +2298,34 @@
         <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L9">
         <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q9">
         <v>369</v>
@@ -2210,7 +2339,7 @@
         <v>15.375</v>
       </c>
       <c r="T9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U9">
         <v>43.35</v>
@@ -2279,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="AO9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP9">
         <v>112</v>
@@ -2288,16 +2417,31 @@
         <v>29.8</v>
       </c>
       <c r="AR9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT9">
         <v>31</v>
       </c>
+      <c r="AU9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
       <c r="D10">
         <v>2025</v>
       </c>
@@ -2308,37 +2452,37 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L10">
         <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q10">
-        <v>357</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <f t="shared" si="5"/>
@@ -2346,10 +2490,10 @@
       </c>
       <c r="S10">
         <f t="shared" si="0"/>
-        <v>14.875</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="T10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U10">
         <v>45.85</v>
@@ -2418,7 +2562,7 @@
         <v>0.2</v>
       </c>
       <c r="AO10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP10">
         <v>118</v>
@@ -2427,16 +2571,31 @@
         <v>40</v>
       </c>
       <c r="AR10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT10">
         <v>31</v>
       </c>
+      <c r="AU10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
       <c r="D11">
         <v>2025</v>
       </c>
@@ -2447,34 +2606,34 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L11">
         <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q11">
         <v>375</v>
@@ -2488,7 +2647,7 @@
         <v>15.625</v>
       </c>
       <c r="T11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U11">
         <v>43.25</v>
@@ -2557,7 +2716,7 @@
         <v>36.4</v>
       </c>
       <c r="AO11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP11">
         <v>124</v>
@@ -2566,16 +2725,31 @@
         <v>56.6</v>
       </c>
       <c r="AR11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT11">
         <v>31</v>
       </c>
+      <c r="AU11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
       <c r="D12">
         <v>2025</v>
       </c>
@@ -2586,34 +2760,34 @@
         <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L12">
         <v>24</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q12">
         <v>377</v>
@@ -2627,7 +2801,7 @@
         <v>15.708333333333334</v>
       </c>
       <c r="T12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U12">
         <v>45.4</v>
@@ -2696,7 +2870,7 @@
         <v>56.4</v>
       </c>
       <c r="AO12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP12">
         <v>131</v>
@@ -2705,16 +2879,31 @@
         <v>38</v>
       </c>
       <c r="AR12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT12">
         <v>31</v>
       </c>
+      <c r="AU12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
       <c r="D13">
         <v>2025</v>
       </c>
@@ -2725,34 +2914,34 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L13">
         <v>24</v>
       </c>
       <c r="M13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q13">
         <v>363</v>
@@ -2766,7 +2955,7 @@
         <v>15.125</v>
       </c>
       <c r="T13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U13">
         <v>43.65</v>
@@ -2835,7 +3024,7 @@
         <v>13</v>
       </c>
       <c r="AO13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP13">
         <v>138</v>
@@ -2844,16 +3033,31 @@
         <v>18.399999999999999</v>
       </c>
       <c r="AR13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT13">
         <v>31</v>
       </c>
+      <c r="AU13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="D14">
         <v>2025</v>
       </c>
@@ -2864,34 +3068,34 @@
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L14">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q14">
         <v>389</v>
@@ -2905,7 +3109,7 @@
         <v>16.208333333333332</v>
       </c>
       <c r="T14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U14">
         <v>43.55</v>
@@ -2974,7 +3178,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="AO14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP14">
         <v>145</v>
@@ -2983,16 +3187,31 @@
         <v>34.9</v>
       </c>
       <c r="AR14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT14">
         <v>31</v>
       </c>
+      <c r="AU14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="D15">
         <v>2025</v>
       </c>
@@ -3003,34 +3222,34 @@
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L15">
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q15">
         <v>325</v>
@@ -3044,7 +3263,7 @@
         <v>13.541666666666666</v>
       </c>
       <c r="T15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U15">
         <v>42.3</v>
@@ -3113,7 +3332,7 @@
         <v>56.6</v>
       </c>
       <c r="AO15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP15">
         <v>150</v>
@@ -3122,16 +3341,31 @@
         <v>55.4</v>
       </c>
       <c r="AR15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT15">
         <v>31</v>
       </c>
+      <c r="AU15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="D16">
         <v>2025</v>
       </c>
@@ -3142,34 +3376,34 @@
         <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L16">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q16">
         <v>329</v>
@@ -3183,7 +3417,7 @@
         <v>13.708333333333334</v>
       </c>
       <c r="T16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U16">
         <v>45.35</v>
@@ -3252,7 +3486,7 @@
         <v>59.7</v>
       </c>
       <c r="AO16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP16">
         <v>156</v>
@@ -3261,16 +3495,31 @@
         <v>23.6</v>
       </c>
       <c r="AR16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT16">
         <v>31</v>
       </c>
+      <c r="AU16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
       <c r="D17">
         <v>2025</v>
       </c>
@@ -3281,34 +3530,34 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L17">
         <v>24</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q17">
         <v>306</v>
@@ -3322,7 +3571,7 @@
         <v>12.75</v>
       </c>
       <c r="T17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U17">
         <v>43.7</v>
@@ -3391,7 +3640,7 @@
         <v>36.799999999999997</v>
       </c>
       <c r="AO17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP17">
         <v>162</v>
@@ -3400,16 +3649,31 @@
         <v>8.5</v>
       </c>
       <c r="AR17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT17">
         <v>31</v>
       </c>
+      <c r="AU17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
       <c r="D18">
         <v>2025</v>
       </c>
@@ -3420,34 +3684,34 @@
         <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L18">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q18">
         <v>311</v>
@@ -3461,7 +3725,7 @@
         <v>12.958333333333334</v>
       </c>
       <c r="T18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U18">
         <v>44.6</v>
@@ -3530,7 +3794,7 @@
         <v>42.4</v>
       </c>
       <c r="AO18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP18">
         <v>168</v>
@@ -3539,16 +3803,31 @@
         <v>17.399999999999999</v>
       </c>
       <c r="AR18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT18">
         <v>31</v>
       </c>
+      <c r="AU18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
       <c r="D19">
         <v>2025</v>
       </c>
@@ -3559,34 +3838,34 @@
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L19">
         <v>24</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q19">
         <v>283</v>
@@ -3600,7 +3879,7 @@
         <v>11.791666666666666</v>
       </c>
       <c r="T19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U19">
         <v>41.8</v>
@@ -3663,13 +3942,13 @@
         <v>331.95</v>
       </c>
       <c r="AM19">
-        <v>34</v>
+        <v>2332</v>
       </c>
       <c r="AN19">
         <v>31.8</v>
       </c>
       <c r="AO19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP19">
         <v>173</v>
@@ -3678,16 +3957,31 @@
         <v>10.4</v>
       </c>
       <c r="AR19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT19">
         <v>31</v>
       </c>
+      <c r="AU19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:48" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
       <c r="D20">
         <v>2025</v>
       </c>
@@ -3698,37 +3992,37 @@
         <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L20">
         <v>24</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q20">
-        <v>354</v>
+        <v>2</v>
       </c>
       <c r="R20">
         <f t="shared" si="5"/>
@@ -3736,10 +4030,10 @@
       </c>
       <c r="S20">
         <f t="shared" si="0"/>
-        <v>14.75</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="T20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U20">
         <v>42.4</v>
@@ -3808,7 +4102,7 @@
         <v>11.2</v>
       </c>
       <c r="AO20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP20">
         <v>177</v>
@@ -3817,16 +4111,31 @@
         <v>13.5</v>
       </c>
       <c r="AR20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AS20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AT20">
         <v>31</v>
       </c>
+      <c r="AU20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
       <c r="D21">
         <v>2025</v>
       </c>
@@ -3837,34 +4146,34 @@
         <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L21">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q21">
         <v>368</v>
@@ -3878,7 +4187,7 @@
         <v>15.333333333333334</v>
       </c>
       <c r="T21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U21">
         <v>44.6</v>
@@ -3947,7 +4256,7 @@
         <v>16.5</v>
       </c>
       <c r="AO21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP21">
         <v>176</v>
@@ -3956,16 +4265,31 @@
         <v>11.6</v>
       </c>
       <c r="AR21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS21" t="s">
         <v>43</v>
-      </c>
-      <c r="AS21" t="s">
-        <v>44</v>
       </c>
       <c r="AT21">
         <v>31</v>
       </c>
+      <c r="AU21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="D22">
         <v>2025</v>
       </c>
@@ -3976,34 +4300,34 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L22">
         <v>24</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q22">
         <v>364</v>
@@ -4017,7 +4341,7 @@
         <v>15.166666666666666</v>
       </c>
       <c r="T22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U22">
         <v>41.4</v>
@@ -4086,7 +4410,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="AO22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP22">
         <v>169</v>
@@ -4095,16 +4419,31 @@
         <v>52.5</v>
       </c>
       <c r="AR22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS22" t="s">
         <v>43</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>44</v>
       </c>
       <c r="AT22">
         <v>31</v>
       </c>
+      <c r="AU22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
       <c r="D23">
         <v>2025</v>
       </c>
@@ -4115,34 +4454,34 @@
         <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L23">
         <v>24</v>
       </c>
       <c r="M23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q23">
         <v>384</v>
@@ -4156,7 +4495,7 @@
         <v>8</v>
       </c>
       <c r="T23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U23">
         <v>44.4</v>
@@ -4225,7 +4564,7 @@
         <v>46.4</v>
       </c>
       <c r="AO23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP23">
         <v>162</v>
@@ -4234,16 +4573,31 @@
         <v>50.9</v>
       </c>
       <c r="AR23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS23" t="s">
         <v>43</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>44</v>
       </c>
       <c r="AT23">
         <v>31</v>
       </c>
+      <c r="AU23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
       <c r="D24">
         <v>2025</v>
       </c>
@@ -4254,34 +4608,34 @@
         <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L24">
         <v>24</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q24">
         <v>311</v>
@@ -4295,7 +4649,7 @@
         <v>12.958333333333334</v>
       </c>
       <c r="T24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U24">
         <v>42.05</v>
@@ -4364,7 +4718,7 @@
         <v>9.1</v>
       </c>
       <c r="AO24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP24">
         <v>157</v>
@@ -4373,16 +4727,31 @@
         <v>13.9</v>
       </c>
       <c r="AR24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS24" t="s">
         <v>43</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>44</v>
       </c>
       <c r="AT24">
         <v>31</v>
       </c>
+      <c r="AU24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="D25">
         <v>2025</v>
       </c>
@@ -4393,34 +4762,34 @@
         <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L25">
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q25">
         <v>386</v>
@@ -4434,7 +4803,7 @@
         <v>16.083333333333332</v>
       </c>
       <c r="T25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U25">
         <v>45.35</v>
@@ -4503,7 +4872,7 @@
         <v>39.299999999999997</v>
       </c>
       <c r="AO25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP25">
         <v>150</v>
@@ -4512,16 +4881,31 @@
         <v>17.3</v>
       </c>
       <c r="AR25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS25" t="s">
         <v>43</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>44</v>
       </c>
       <c r="AT25">
         <v>31</v>
       </c>
+      <c r="AU25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
       <c r="D26">
         <v>2025</v>
       </c>
@@ -4532,37 +4916,37 @@
         <v>4</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L26">
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q26">
-        <v>388</v>
+        <v>3</v>
       </c>
       <c r="R26">
         <f t="shared" si="5"/>
@@ -4570,10 +4954,10 @@
       </c>
       <c r="S26">
         <f t="shared" si="0"/>
-        <v>16.166666666666668</v>
+        <v>0.125</v>
       </c>
       <c r="T26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U26">
         <v>45.45</v>
@@ -4642,7 +5026,7 @@
         <v>53.7</v>
       </c>
       <c r="AO26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP26">
         <v>143</v>
@@ -4651,16 +5035,31 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="AR26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS26" t="s">
         <v>43</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>44</v>
       </c>
       <c r="AT26">
         <v>31</v>
       </c>
+      <c r="AU26" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV26" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
       <c r="D27">
         <v>2025</v>
       </c>
@@ -4671,34 +5070,34 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L27">
         <v>24</v>
       </c>
       <c r="M27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q27">
         <v>378</v>
@@ -4712,7 +5111,7 @@
         <v>15.75</v>
       </c>
       <c r="T27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U27">
         <v>41.75</v>
@@ -4781,7 +5180,7 @@
         <v>3.6</v>
       </c>
       <c r="AO27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP27">
         <v>136</v>
@@ -4790,16 +5189,31 @@
         <v>7.6</v>
       </c>
       <c r="AR27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS27" t="s">
         <v>43</v>
-      </c>
-      <c r="AS27" t="s">
-        <v>44</v>
       </c>
       <c r="AT27">
         <v>31</v>
       </c>
+      <c r="AU27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
       <c r="D28">
         <v>2025</v>
       </c>
@@ -4810,34 +5224,34 @@
         <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L28">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q28">
         <v>384</v>
@@ -4851,7 +5265,7 @@
         <v>16</v>
       </c>
       <c r="T28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U28">
         <v>43.15</v>
@@ -4920,7 +5334,7 @@
         <v>14.3</v>
       </c>
       <c r="AO28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP28">
         <v>128</v>
@@ -4929,16 +5343,31 @@
         <v>55.1</v>
       </c>
       <c r="AR28" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS28" t="s">
         <v>43</v>
-      </c>
-      <c r="AS28" t="s">
-        <v>44</v>
       </c>
       <c r="AT28">
         <v>31</v>
       </c>
+      <c r="AU28" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
       <c r="D29">
         <v>2025</v>
       </c>
@@ -4949,34 +5378,34 @@
         <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L29">
         <v>24</v>
       </c>
       <c r="M29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q29">
         <v>379</v>
@@ -4990,7 +5419,7 @@
         <v>15.791666666666666</v>
       </c>
       <c r="T29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U29">
         <v>42.2</v>
@@ -5059,7 +5488,7 @@
         <v>43.6</v>
       </c>
       <c r="AO29" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP29" s="9">
         <v>124</v>
@@ -5068,16 +5497,31 @@
         <v>16.899999999999999</v>
       </c>
       <c r="AR29" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS29" t="s">
         <v>43</v>
-      </c>
-      <c r="AS29" t="s">
-        <v>44</v>
       </c>
       <c r="AT29">
         <v>31</v>
       </c>
+      <c r="AU29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
       <c r="D30">
         <v>2025</v>
       </c>
@@ -5088,34 +5532,34 @@
         <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" t="s">
+        <v>120</v>
+      </c>
+      <c r="K30" t="s">
         <v>119</v>
-      </c>
-      <c r="J30" t="s">
-        <v>121</v>
-      </c>
-      <c r="K30" t="s">
-        <v>120</v>
       </c>
       <c r="L30">
         <v>7.2</v>
       </c>
       <c r="M30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q30">
         <v>113</v>
@@ -5129,7 +5573,7 @@
         <v>15.694444444672829</v>
       </c>
       <c r="T30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U30">
         <v>13.6</v>
@@ -5198,7 +5642,7 @@
         <v>43.3</v>
       </c>
       <c r="AO30" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP30" s="9">
         <v>124</v>
@@ -5207,16 +5651,31 @@
         <v>10.9</v>
       </c>
       <c r="AR30" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AT30">
         <v>31</v>
       </c>
+      <c r="AU30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV30" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="D31">
         <v>2025</v>
       </c>
@@ -5227,34 +5686,34 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
+        <v>120</v>
+      </c>
+      <c r="J31" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" t="s">
         <v>121</v>
-      </c>
-      <c r="J31" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" t="s">
-        <v>122</v>
       </c>
       <c r="L31">
         <v>12.5</v>
       </c>
       <c r="M31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31">
         <v>250</v>
@@ -5268,7 +5727,7 @@
         <v>19.999999999906869</v>
       </c>
       <c r="T31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -5337,7 +5796,7 @@
         <v>43.1</v>
       </c>
       <c r="AO31" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP31" s="9">
         <v>124</v>
@@ -5346,16 +5805,31 @@
         <v>8.4</v>
       </c>
       <c r="AR31" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AT31">
         <v>31</v>
       </c>
+      <c r="AU31" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV31" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
       <c r="D32">
         <v>2025</v>
       </c>
@@ -5366,34 +5840,34 @@
         <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L32">
         <v>4.3</v>
       </c>
       <c r="M32" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" t="s">
         <v>52</v>
       </c>
-      <c r="N32" t="s">
-        <v>53</v>
-      </c>
       <c r="O32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5407,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U32">
         <v>0</v>
@@ -5476,7 +5950,7 @@
         <v>43.1</v>
       </c>
       <c r="AO32" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP32" s="10">
         <v>120</v>
@@ -5485,16 +5959,31 @@
         <v>8.4</v>
       </c>
       <c r="AR32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS32" t="s">
         <v>43</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>44</v>
       </c>
       <c r="AT32">
         <v>31</v>
       </c>
+      <c r="AU32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="D33">
         <v>2025</v>
       </c>
@@ -5505,34 +5994,34 @@
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s">
+        <v>125</v>
+      </c>
+      <c r="J33" t="s">
+        <v>120</v>
+      </c>
+      <c r="K33" t="s">
         <v>126</v>
-      </c>
-      <c r="J33" t="s">
-        <v>121</v>
-      </c>
-      <c r="K33" t="s">
-        <v>127</v>
       </c>
       <c r="L33">
         <v>3</v>
       </c>
       <c r="M33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33">
         <v>6</v>
@@ -5546,7 +6035,7 @@
         <v>2</v>
       </c>
       <c r="T33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -5615,7 +6104,7 @@
         <v>38.1</v>
       </c>
       <c r="AO33" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP33" s="10">
         <v>120</v>
@@ -5624,16 +6113,31 @@
         <v>14.4</v>
       </c>
       <c r="AR33" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AT33">
         <v>31</v>
       </c>
+      <c r="AU33" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV33" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
       <c r="D34">
         <v>2025</v>
       </c>
@@ -5644,34 +6148,34 @@
         <v>4</v>
       </c>
       <c r="G34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L34">
         <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5685,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U34">
         <v>0</v>
@@ -5754,7 +6258,7 @@
         <v>39.4</v>
       </c>
       <c r="AO34" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP34" s="11">
         <v>120</v>
@@ -5763,16 +6267,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR34" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS34" t="s">
         <v>43</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>44</v>
       </c>
       <c r="AT34">
         <v>31</v>
       </c>
+      <c r="AU34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
       <c r="D35">
         <v>2025</v>
       </c>
@@ -5783,34 +6302,34 @@
         <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L35">
         <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -5824,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -5893,7 +6412,7 @@
         <v>39.4</v>
       </c>
       <c r="AO35" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP35" s="11">
         <v>120</v>
@@ -5902,16 +6421,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR35" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT35">
         <v>31</v>
       </c>
+      <c r="AU35" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV35" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
       <c r="D36">
         <v>2025</v>
       </c>
@@ -5922,34 +6456,34 @@
         <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L36">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -5963,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -6032,7 +6566,7 @@
         <v>39.4</v>
       </c>
       <c r="AO36" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP36" s="13">
         <v>120</v>
@@ -6041,16 +6575,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR36" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS36" t="s">
         <v>43</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>44</v>
       </c>
       <c r="AT36">
         <v>31</v>
       </c>
+      <c r="AU36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV36" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
       <c r="D37">
         <v>2025</v>
       </c>
@@ -6061,34 +6610,34 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L37">
         <v>1.1000000000000001</v>
       </c>
       <c r="M37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -6102,7 +6651,7 @@
         <v>7.2727272732660539</v>
       </c>
       <c r="T37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -6171,7 +6720,7 @@
         <v>39.4</v>
       </c>
       <c r="AO37" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP37" s="13">
         <v>120</v>
@@ -6180,16 +6729,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR37" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AT37">
         <v>31</v>
       </c>
+      <c r="AU37" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV37" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38">
         <v>2025</v>
       </c>
@@ -6200,34 +6764,34 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" t="s">
         <v>135</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>136</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
+        <v>143</v>
+      </c>
+      <c r="K38" t="s">
         <v>137</v>
-      </c>
-      <c r="J38" t="s">
-        <v>144</v>
-      </c>
-      <c r="K38" t="s">
-        <v>138</v>
       </c>
       <c r="L38">
         <v>10.5</v>
       </c>
       <c r="M38" t="s">
+        <v>46</v>
+      </c>
+      <c r="N38" t="s">
+        <v>46</v>
+      </c>
+      <c r="O38" t="s">
         <v>47</v>
       </c>
-      <c r="N38" t="s">
-        <v>47</v>
-      </c>
-      <c r="O38" t="s">
-        <v>48</v>
-      </c>
       <c r="P38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q38">
         <v>163</v>
@@ -6241,7 +6805,7 @@
         <v>15.523809523809524</v>
       </c>
       <c r="T38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U38">
         <v>0</v>
@@ -6310,7 +6874,7 @@
         <v>41.4</v>
       </c>
       <c r="AO38" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP38" s="13">
         <v>120</v>
@@ -6319,16 +6883,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR38" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AT38">
         <v>31</v>
       </c>
+      <c r="AU38" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV38" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
       <c r="D39">
         <v>2025</v>
       </c>
@@ -6339,34 +6918,34 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H39" t="s">
         <v>135</v>
       </c>
-      <c r="H39" t="s">
-        <v>136</v>
-      </c>
       <c r="I39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L39">
         <v>12.4</v>
       </c>
       <c r="M39" t="s">
+        <v>46</v>
+      </c>
+      <c r="N39" t="s">
+        <v>46</v>
+      </c>
+      <c r="O39" t="s">
         <v>47</v>
       </c>
-      <c r="N39" t="s">
-        <v>47</v>
-      </c>
-      <c r="O39" t="s">
-        <v>48</v>
-      </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q39">
         <v>198</v>
@@ -6380,7 +6959,7 @@
         <v>15.967741935378934</v>
       </c>
       <c r="T39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U39">
         <v>17</v>
@@ -6449,7 +7028,7 @@
         <v>41.7</v>
       </c>
       <c r="AO39" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP39" s="12">
         <v>125</v>
@@ -6458,16 +7037,31 @@
         <v>18.100000000000001</v>
       </c>
       <c r="AR39" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS39" t="s">
         <v>43</v>
-      </c>
-      <c r="AS39" t="s">
-        <v>44</v>
       </c>
       <c r="AT39">
         <v>31</v>
       </c>
+      <c r="AU39" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
       <c r="D40">
         <v>2025</v>
       </c>
@@ -6478,34 +7072,34 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" t="s">
         <v>135</v>
       </c>
-      <c r="H40" t="s">
-        <v>136</v>
-      </c>
       <c r="I40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K40" t="s">
         <v>141</v>
-      </c>
-      <c r="J40" t="s">
-        <v>144</v>
-      </c>
-      <c r="K40" t="s">
-        <v>142</v>
       </c>
       <c r="L40">
         <v>11.5</v>
       </c>
       <c r="M40" t="s">
+        <v>46</v>
+      </c>
+      <c r="N40" t="s">
+        <v>46</v>
+      </c>
+      <c r="O40" t="s">
         <v>47</v>
       </c>
-      <c r="N40" t="s">
-        <v>47</v>
-      </c>
-      <c r="O40" t="s">
-        <v>48</v>
-      </c>
       <c r="P40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q40">
         <v>185</v>
@@ -6519,7 +7113,7 @@
         <v>16.086956521820554</v>
       </c>
       <c r="T40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U40">
         <v>19.350000000000001</v>
@@ -6588,7 +7182,7 @@
         <v>41.7</v>
       </c>
       <c r="AO40" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP40" s="12">
         <v>125</v>
@@ -6597,16 +7191,31 @@
         <v>34.1</v>
       </c>
       <c r="AR40" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AT40">
         <v>31</v>
       </c>
+      <c r="AU40" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV40" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
       <c r="D41">
         <v>2025</v>
       </c>
@@ -6617,34 +7226,34 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" t="s">
         <v>135</v>
       </c>
-      <c r="H41" t="s">
-        <v>136</v>
-      </c>
       <c r="I41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L41">
         <v>1.5</v>
       </c>
       <c r="M41" t="s">
+        <v>46</v>
+      </c>
+      <c r="N41" t="s">
+        <v>51</v>
+      </c>
+      <c r="O41" t="s">
         <v>47</v>
       </c>
-      <c r="N41" t="s">
-        <v>52</v>
-      </c>
-      <c r="O41" t="s">
-        <v>48</v>
-      </c>
       <c r="P41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q41">
         <v>23</v>
@@ -6658,7 +7267,7 @@
         <v>15.333333333333334</v>
       </c>
       <c r="T41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -6727,7 +7336,7 @@
         <v>42.7</v>
       </c>
       <c r="AO41" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP41" s="12">
         <v>125</v>
@@ -6736,16 +7345,31 @@
         <v>40.1</v>
       </c>
       <c r="AR41" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AT41">
         <v>31</v>
       </c>
+      <c r="AU41" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
       <c r="D42">
         <v>2025</v>
       </c>
@@ -6756,34 +7380,34 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
+        <v>134</v>
+      </c>
+      <c r="H42" t="s">
         <v>135</v>
       </c>
-      <c r="H42" t="s">
-        <v>136</v>
-      </c>
       <c r="I42" t="s">
+        <v>145</v>
+      </c>
+      <c r="J42" t="s">
+        <v>143</v>
+      </c>
+      <c r="K42" t="s">
         <v>146</v>
-      </c>
-      <c r="J42" t="s">
-        <v>144</v>
-      </c>
-      <c r="K42" t="s">
-        <v>147</v>
       </c>
       <c r="L42">
         <v>7.5</v>
       </c>
       <c r="M42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -6797,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U42">
         <v>0</v>
@@ -6866,7 +7490,7 @@
         <v>42.7</v>
       </c>
       <c r="AO42" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP42" s="12">
         <v>125</v>
@@ -6875,16 +7499,31 @@
         <v>40.1</v>
       </c>
       <c r="AR42" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AT42">
         <v>31</v>
       </c>
+      <c r="AU42" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
       <c r="D43">
         <v>2025</v>
       </c>
@@ -6895,34 +7534,34 @@
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I43" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K43" t="s">
         <v>149</v>
-      </c>
-      <c r="J43" t="s">
-        <v>157</v>
-      </c>
-      <c r="K43" t="s">
-        <v>150</v>
       </c>
       <c r="L43">
         <v>0.5</v>
       </c>
       <c r="M43" t="s">
+        <v>46</v>
+      </c>
+      <c r="N43" t="s">
+        <v>46</v>
+      </c>
+      <c r="O43" t="s">
         <v>47</v>
       </c>
-      <c r="N43" t="s">
-        <v>47</v>
-      </c>
-      <c r="O43" t="s">
-        <v>48</v>
-      </c>
       <c r="P43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q43">
         <v>5</v>
@@ -6936,7 +7575,7 @@
         <v>9.9999999988358468</v>
       </c>
       <c r="T43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -7005,7 +7644,7 @@
         <v>42.7</v>
       </c>
       <c r="AO43" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP43" s="12">
         <v>125</v>
@@ -7014,16 +7653,31 @@
         <v>42.1</v>
       </c>
       <c r="AR43" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AS43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AT43">
         <v>31</v>
       </c>
+      <c r="AU43" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
       <c r="D44">
         <v>2025</v>
       </c>
@@ -7034,34 +7688,34 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L44">
         <v>3</v>
       </c>
       <c r="M44" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" t="s">
+        <v>46</v>
+      </c>
+      <c r="O44" t="s">
         <v>47</v>
       </c>
-      <c r="N44" t="s">
-        <v>47</v>
-      </c>
-      <c r="O44" t="s">
-        <v>48</v>
-      </c>
       <c r="P44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q44">
         <v>67</v>
@@ -7075,7 +7729,7 @@
         <v>22.333333333333332</v>
       </c>
       <c r="T44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U44">
         <v>3.45</v>
@@ -7144,7 +7798,7 @@
         <v>44.1</v>
       </c>
       <c r="AO44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP44">
         <v>127</v>
@@ -7153,16 +7807,31 @@
         <v>53.3</v>
       </c>
       <c r="AR44" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS44" t="s">
         <v>43</v>
-      </c>
-      <c r="AS44" t="s">
-        <v>44</v>
       </c>
       <c r="AT44">
         <v>31</v>
       </c>
+      <c r="AU44" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
       <c r="D45">
         <v>2025</v>
       </c>
@@ -7173,34 +7842,34 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L45">
         <v>24</v>
       </c>
       <c r="M45" t="s">
+        <v>46</v>
+      </c>
+      <c r="N45" t="s">
+        <v>46</v>
+      </c>
+      <c r="O45" t="s">
         <v>47</v>
       </c>
-      <c r="N45" t="s">
-        <v>47</v>
-      </c>
-      <c r="O45" t="s">
-        <v>48</v>
-      </c>
       <c r="P45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q45">
         <v>380</v>
@@ -7214,7 +7883,7 @@
         <v>15.833333333333334</v>
       </c>
       <c r="T45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U45">
         <v>36.700000000000003</v>
@@ -7283,7 +7952,7 @@
         <v>53.1</v>
       </c>
       <c r="AO45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP45">
         <v>132</v>
@@ -7292,16 +7961,31 @@
         <v>37.700000000000003</v>
       </c>
       <c r="AR45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS45" t="s">
         <v>43</v>
-      </c>
-      <c r="AS45" t="s">
-        <v>44</v>
       </c>
       <c r="AT45">
         <v>31</v>
       </c>
+      <c r="AU45" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
       <c r="D46">
         <v>2025</v>
       </c>
@@ -7312,34 +7996,34 @@
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L46">
         <v>24</v>
       </c>
       <c r="M46" t="s">
+        <v>46</v>
+      </c>
+      <c r="N46" t="s">
+        <v>46</v>
+      </c>
+      <c r="O46" t="s">
         <v>47</v>
       </c>
-      <c r="N46" t="s">
-        <v>47</v>
-      </c>
-      <c r="O46" t="s">
-        <v>48</v>
-      </c>
       <c r="P46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q46">
         <v>397</v>
@@ -7353,7 +8037,7 @@
         <v>16.541666666666668</v>
       </c>
       <c r="T46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U46">
         <v>38.450000000000003</v>
@@ -7422,7 +8106,7 @@
         <v>42.5</v>
       </c>
       <c r="AO46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP46">
         <v>140</v>
@@ -7431,16 +8115,31 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="AR46" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS46" t="s">
         <v>43</v>
-      </c>
-      <c r="AS46" t="s">
-        <v>44</v>
       </c>
       <c r="AT46">
         <v>31</v>
       </c>
+      <c r="AU46" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
       <c r="D47">
         <v>2025</v>
       </c>
@@ -7451,34 +8150,34 @@
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L47">
         <v>24</v>
       </c>
       <c r="M47" t="s">
+        <v>46</v>
+      </c>
+      <c r="N47" t="s">
+        <v>46</v>
+      </c>
+      <c r="O47" t="s">
         <v>47</v>
       </c>
-      <c r="N47" t="s">
-        <v>47</v>
-      </c>
-      <c r="O47" t="s">
-        <v>48</v>
-      </c>
       <c r="P47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q47">
         <v>384</v>
@@ -7492,7 +8191,7 @@
         <v>16</v>
       </c>
       <c r="T47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U47">
         <v>37.700000000000003</v>
@@ -7561,7 +8260,7 @@
         <v>14.4</v>
       </c>
       <c r="AO47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP47">
         <v>147</v>
@@ -7570,16 +8269,31 @@
         <v>28.4</v>
       </c>
       <c r="AR47" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS47" t="s">
         <v>43</v>
-      </c>
-      <c r="AS47" t="s">
-        <v>44</v>
       </c>
       <c r="AT47">
         <v>31</v>
       </c>
+      <c r="AU47" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
       <c r="D48">
         <v>2025</v>
       </c>
@@ -7590,34 +8304,34 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s">
+        <v>155</v>
+      </c>
+      <c r="J48" t="s">
         <v>156</v>
       </c>
-      <c r="J48" t="s">
-        <v>157</v>
-      </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L48">
         <v>23</v>
       </c>
       <c r="M48" t="s">
+        <v>46</v>
+      </c>
+      <c r="N48" t="s">
+        <v>46</v>
+      </c>
+      <c r="O48" t="s">
         <v>47</v>
       </c>
-      <c r="N48" t="s">
-        <v>47</v>
-      </c>
-      <c r="O48" t="s">
-        <v>48</v>
-      </c>
       <c r="P48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q48">
         <v>369</v>
@@ -7631,7 +8345,7 @@
         <v>15.375</v>
       </c>
       <c r="T48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U48">
         <v>37.75</v>
@@ -7700,7 +8414,7 @@
         <v>22.1</v>
       </c>
       <c r="AO48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP48">
         <v>154</v>
@@ -7709,16 +8423,31 @@
         <v>26.8</v>
       </c>
       <c r="AR48" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS48" t="s">
         <v>43</v>
-      </c>
-      <c r="AS48" t="s">
-        <v>44</v>
       </c>
       <c r="AT48">
         <v>31</v>
       </c>
+      <c r="AU48" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="4:46" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
       <c r="D49">
         <v>2025</v>
       </c>
@@ -7729,34 +8458,34 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L49">
         <v>24</v>
       </c>
       <c r="M49" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49" t="s">
         <v>47</v>
       </c>
-      <c r="N49" t="s">
-        <v>47</v>
-      </c>
-      <c r="O49" t="s">
-        <v>48</v>
-      </c>
       <c r="P49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q49">
         <v>382</v>
@@ -7770,7 +8499,7 @@
         <v>15.916666666666666</v>
       </c>
       <c r="T49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U49">
         <v>38.1</v>
@@ -7839,7 +8568,7 @@
         <v>7.4</v>
       </c>
       <c r="AO49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP49">
         <v>161</v>
@@ -7848,13 +8577,19 @@
         <v>31.2</v>
       </c>
       <c r="AR49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS49" t="s">
         <v>43</v>
-      </c>
-      <c r="AS49" t="s">
-        <v>44</v>
       </c>
       <c r="AT49">
         <v>31</v>
+      </c>
+      <c r="AU49" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
